--- a/Wasser/3_Auswertung Photometrie.xlsx
+++ b/Wasser/3_Auswertung Photometrie.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Stefan\Desktop\Stefan\Projekte\Masterarbeiten MEES\Masterarbeit Nele Herzig, Alexandra Kornhaß\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alexandra\Documents\GitHub\Moore-Lichtenau-Meusebach\Wasser\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFA941DB-E8E6-4F0B-8939-4F59A96E1C41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B4A56BB-BECF-4E3C-ACF9-0007D7E21129}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="26.06.2025" sheetId="1" r:id="rId1"/>
@@ -1336,7 +1336,7 @@
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1391,10 +1391,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1403,10 +1415,25 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1415,16 +1442,25 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1433,49 +1469,10 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1484,7 +1481,9 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="20 % - Akzent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -14489,16 +14488,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="46" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
       <c r="I1" s="1"/>
     </row>
     <row r="2" spans="1:9" s="25" customFormat="1" x14ac:dyDescent="0.25">
@@ -14704,14 +14703,14 @@
       <c r="B55" s="6">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="C55" s="39">
+      <c r="C55" s="38">
         <v>1</v>
       </c>
-      <c r="D55" s="39"/>
-      <c r="E55" s="42">
+      <c r="D55" s="38"/>
+      <c r="E55" s="39">
         <v>0</v>
       </c>
-      <c r="F55" s="43"/>
+      <c r="F55" s="40"/>
       <c r="H55" s="18"/>
       <c r="I55" s="27"/>
       <c r="J55" s="18"/>
@@ -14723,15 +14722,15 @@
       <c r="B56" s="6">
         <v>1.6E-2</v>
       </c>
-      <c r="C56" s="39">
+      <c r="C56" s="38">
         <v>2.5</v>
       </c>
-      <c r="D56" s="39"/>
-      <c r="E56" s="42">
+      <c r="D56" s="38"/>
+      <c r="E56" s="39">
         <f t="shared" ref="E56" si="0">(B56-0.0164)/0.0093</f>
         <v>-4.3010752688172157E-2</v>
       </c>
-      <c r="F56" s="43"/>
+      <c r="F56" s="40"/>
       <c r="H56" s="18"/>
       <c r="I56" s="27"/>
       <c r="J56" s="18"/>
@@ -14743,15 +14742,15 @@
       <c r="B57" s="6">
         <v>0.04</v>
       </c>
-      <c r="C57" s="39">
+      <c r="C57" s="38">
         <v>5</v>
       </c>
-      <c r="D57" s="39"/>
-      <c r="E57" s="42">
+      <c r="D57" s="38"/>
+      <c r="E57" s="39">
         <f>(B57-0.0164)/0.0093</f>
         <v>2.5376344086021505</v>
       </c>
-      <c r="F57" s="43"/>
+      <c r="F57" s="40"/>
       <c r="H57" s="18">
         <f>C57/1000000</f>
         <v>5.0000000000000004E-6</v>
@@ -14772,15 +14771,15 @@
       <c r="B58" s="6">
         <v>8.4000000000000005E-2</v>
       </c>
-      <c r="C58" s="39">
+      <c r="C58" s="38">
         <v>10</v>
       </c>
-      <c r="D58" s="39"/>
-      <c r="E58" s="40">
+      <c r="D58" s="38"/>
+      <c r="E58" s="44">
         <f t="shared" ref="E58:E62" si="1">(B58-0.0164)/0.0093</f>
         <v>7.2688172043010768</v>
       </c>
-      <c r="F58" s="41"/>
+      <c r="F58" s="45"/>
       <c r="H58" s="18">
         <f>C58/1000000</f>
         <v>1.0000000000000001E-5</v>
@@ -14801,15 +14800,15 @@
       <c r="B59" s="6">
         <v>0.22800000000000001</v>
       </c>
-      <c r="C59" s="39">
+      <c r="C59" s="38">
         <v>25</v>
       </c>
-      <c r="D59" s="39"/>
-      <c r="E59" s="40">
+      <c r="D59" s="38"/>
+      <c r="E59" s="44">
         <f t="shared" si="1"/>
         <v>22.752688172043015</v>
       </c>
-      <c r="F59" s="41"/>
+      <c r="F59" s="45"/>
       <c r="H59" s="18"/>
       <c r="I59" s="18"/>
       <c r="J59" s="21"/>
@@ -14821,15 +14820,15 @@
       <c r="B60" s="6">
         <v>0.54300000000000004</v>
       </c>
-      <c r="C60" s="39">
+      <c r="C60" s="38">
         <v>50</v>
       </c>
-      <c r="D60" s="39"/>
-      <c r="E60" s="40">
+      <c r="D60" s="38"/>
+      <c r="E60" s="44">
         <f t="shared" si="1"/>
         <v>56.62365591397851</v>
       </c>
-      <c r="F60" s="41"/>
+      <c r="F60" s="45"/>
       <c r="H60" s="18">
         <f>C60/1000000</f>
         <v>5.0000000000000002E-5</v>
@@ -14850,15 +14849,15 @@
       <c r="B61" s="6">
         <v>0.98199999999999998</v>
       </c>
-      <c r="C61" s="39">
+      <c r="C61" s="38">
         <v>100</v>
       </c>
-      <c r="D61" s="39"/>
-      <c r="E61" s="40">
+      <c r="D61" s="38"/>
+      <c r="E61" s="44">
         <f t="shared" si="1"/>
         <v>103.82795698924733</v>
       </c>
-      <c r="F61" s="41"/>
+      <c r="F61" s="45"/>
       <c r="H61" s="18">
         <f>C61/1000000</f>
         <v>1E-4</v>
@@ -14879,15 +14878,15 @@
       <c r="B62" s="8">
         <v>1.8460000000000001</v>
       </c>
-      <c r="C62" s="48">
+      <c r="C62" s="47">
         <v>200</v>
       </c>
-      <c r="D62" s="49"/>
-      <c r="E62" s="50">
+      <c r="D62" s="48"/>
+      <c r="E62" s="62">
         <f t="shared" si="1"/>
         <v>196.73118279569894</v>
       </c>
-      <c r="F62" s="51"/>
+      <c r="F62" s="63"/>
       <c r="H62" s="19">
         <f>C62/1000000</f>
         <v>2.0000000000000001E-4</v>
@@ -14908,12 +14907,12 @@
       <c r="B63" s="9">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="C63" s="52"/>
-      <c r="D63" s="53"/>
-      <c r="E63" s="54">
+      <c r="C63" s="49"/>
+      <c r="D63" s="50"/>
+      <c r="E63" s="55">
         <v>0</v>
       </c>
-      <c r="F63" s="54"/>
+      <c r="F63" s="55"/>
       <c r="H63" s="18">
         <f t="shared" ref="H63:H70" si="4">E63/1000000</f>
         <v>0</v>
@@ -14934,12 +14933,12 @@
       <c r="B64" s="6">
         <v>2E-3</v>
       </c>
-      <c r="C64" s="46"/>
-      <c r="D64" s="47"/>
-      <c r="E64" s="42">
+      <c r="C64" s="41"/>
+      <c r="D64" s="42"/>
+      <c r="E64" s="39">
         <v>0</v>
       </c>
-      <c r="F64" s="42"/>
+      <c r="F64" s="39"/>
       <c r="H64" s="18">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -14960,12 +14959,12 @@
       <c r="B65" s="6">
         <v>2E-3</v>
       </c>
-      <c r="C65" s="46"/>
-      <c r="D65" s="47"/>
-      <c r="E65" s="42">
+      <c r="C65" s="41"/>
+      <c r="D65" s="42"/>
+      <c r="E65" s="39">
         <v>0</v>
       </c>
-      <c r="F65" s="42"/>
+      <c r="F65" s="39"/>
       <c r="H65" s="18">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -14986,12 +14985,12 @@
       <c r="B66" s="6">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="C66" s="46"/>
-      <c r="D66" s="47"/>
-      <c r="E66" s="42">
+      <c r="C66" s="41"/>
+      <c r="D66" s="42"/>
+      <c r="E66" s="39">
         <v>0</v>
       </c>
-      <c r="F66" s="42"/>
+      <c r="F66" s="39"/>
       <c r="H66" s="18">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -15012,13 +15011,13 @@
       <c r="B67" s="6">
         <v>0.109</v>
       </c>
-      <c r="C67" s="46"/>
-      <c r="D67" s="47"/>
-      <c r="E67" s="42">
+      <c r="C67" s="41"/>
+      <c r="D67" s="42"/>
+      <c r="E67" s="39">
         <f t="shared" ref="E67:E70" si="7">(B67-0.0164)/0.0093</f>
         <v>9.9569892473118298</v>
       </c>
-      <c r="F67" s="42"/>
+      <c r="F67" s="39"/>
       <c r="H67" s="18">
         <f t="shared" si="4"/>
         <v>9.9569892473118294E-6</v>
@@ -15039,13 +15038,13 @@
       <c r="B68" s="6">
         <v>0.36</v>
       </c>
-      <c r="C68" s="46"/>
-      <c r="D68" s="47"/>
-      <c r="E68" s="42">
+      <c r="C68" s="41"/>
+      <c r="D68" s="42"/>
+      <c r="E68" s="39">
         <f t="shared" si="7"/>
         <v>36.946236559139784</v>
       </c>
-      <c r="F68" s="42"/>
+      <c r="F68" s="39"/>
       <c r="H68" s="18">
         <f t="shared" si="4"/>
         <v>3.6946236559139785E-5</v>
@@ -15066,13 +15065,13 @@
       <c r="B69" s="6">
         <v>0.91300000000000003</v>
       </c>
-      <c r="C69" s="46"/>
-      <c r="D69" s="47"/>
-      <c r="E69" s="42">
+      <c r="C69" s="41"/>
+      <c r="D69" s="42"/>
+      <c r="E69" s="39">
         <f t="shared" si="7"/>
         <v>96.408602150537646</v>
       </c>
-      <c r="F69" s="42"/>
+      <c r="F69" s="39"/>
       <c r="H69" s="18">
         <f t="shared" si="4"/>
         <v>9.6408602150537646E-5</v>
@@ -15093,13 +15092,13 @@
       <c r="B70" s="6">
         <v>4.7E-2</v>
       </c>
-      <c r="C70" s="46"/>
-      <c r="D70" s="47"/>
-      <c r="E70" s="42">
+      <c r="C70" s="41"/>
+      <c r="D70" s="42"/>
+      <c r="E70" s="39">
         <f t="shared" si="7"/>
         <v>3.2903225806451615</v>
       </c>
-      <c r="F70" s="42"/>
+      <c r="F70" s="39"/>
       <c r="H70" s="18">
         <f t="shared" si="4"/>
         <v>3.2903225806451615E-6</v>
@@ -15185,11 +15184,11 @@
         <v>0.5</v>
       </c>
       <c r="D101" s="11"/>
-      <c r="E101" s="55">
+      <c r="E101" s="51">
         <f>(B101+0.0049)/0.0204</f>
         <v>0.28921568627450978</v>
       </c>
-      <c r="F101" s="56"/>
+      <c r="F101" s="52"/>
       <c r="I101" s="16">
         <f t="shared" ref="I101:I106" si="8">C101/1000000</f>
         <v>4.9999999999999998E-7</v>
@@ -15214,11 +15213,11 @@
         <v>1</v>
       </c>
       <c r="D102" s="13"/>
-      <c r="E102" s="42">
+      <c r="E102" s="39">
         <f t="shared" ref="E102:E106" si="10">(B102+0.0049)/0.0204</f>
         <v>1.0245098039215685</v>
       </c>
-      <c r="F102" s="43"/>
+      <c r="F102" s="40"/>
       <c r="I102" s="18">
         <f t="shared" si="8"/>
         <v>9.9999999999999995E-7</v>
@@ -15243,11 +15242,11 @@
         <v>5</v>
       </c>
       <c r="D103" s="13"/>
-      <c r="E103" s="42">
+      <c r="E103" s="39">
         <f t="shared" si="10"/>
         <v>4.6029411764705879</v>
       </c>
-      <c r="F103" s="43"/>
+      <c r="F103" s="40"/>
       <c r="I103" s="18">
         <f t="shared" si="8"/>
         <v>5.0000000000000004E-6</v>
@@ -15272,11 +15271,11 @@
         <v>10</v>
       </c>
       <c r="D104" s="13"/>
-      <c r="E104" s="42">
+      <c r="E104" s="39">
         <f t="shared" si="10"/>
         <v>10.877450980392155</v>
       </c>
-      <c r="F104" s="43"/>
+      <c r="F104" s="40"/>
       <c r="I104" s="18">
         <f t="shared" si="8"/>
         <v>1.0000000000000001E-5</v>
@@ -15301,11 +15300,11 @@
         <v>25</v>
       </c>
       <c r="D105" s="33"/>
-      <c r="E105" s="42">
+      <c r="E105" s="39">
         <f t="shared" si="10"/>
         <v>24.799019607843135</v>
       </c>
-      <c r="F105" s="43"/>
+      <c r="F105" s="40"/>
       <c r="I105" s="19">
         <f t="shared" si="8"/>
         <v>2.5000000000000001E-5</v>
@@ -15330,11 +15329,11 @@
         <v>50</v>
       </c>
       <c r="D106" s="15"/>
-      <c r="E106" s="44">
+      <c r="E106" s="53">
         <f t="shared" si="10"/>
         <v>37.446078431372548</v>
       </c>
-      <c r="F106" s="45"/>
+      <c r="F106" s="54"/>
       <c r="I106" s="18">
         <f t="shared" si="8"/>
         <v>5.0000000000000002E-5</v>
@@ -15355,13 +15354,13 @@
       <c r="B107" s="9">
         <v>0</v>
       </c>
-      <c r="C107" s="52"/>
-      <c r="D107" s="53"/>
-      <c r="E107" s="54">
+      <c r="C107" s="49"/>
+      <c r="D107" s="50"/>
+      <c r="E107" s="55">
         <f t="shared" ref="E107" si="12">(B107+0.0049)/0.0204</f>
         <v>0.24019607843137253</v>
       </c>
-      <c r="F107" s="54"/>
+      <c r="F107" s="55"/>
       <c r="I107" s="18">
         <f>E107/1000000</f>
         <v>2.4019607843137255E-7</v>
@@ -15382,13 +15381,13 @@
       <c r="B108" s="6">
         <v>0</v>
       </c>
-      <c r="C108" s="46"/>
-      <c r="D108" s="47"/>
-      <c r="E108" s="42">
+      <c r="C108" s="41"/>
+      <c r="D108" s="42"/>
+      <c r="E108" s="39">
         <f t="shared" ref="E108:E114" si="13">(B108+0.0049)/0.0204</f>
         <v>0.24019607843137253</v>
       </c>
-      <c r="F108" s="42"/>
+      <c r="F108" s="39"/>
       <c r="I108" s="18">
         <f t="shared" ref="I108:I114" si="14">E108/1000000</f>
         <v>2.4019607843137255E-7</v>
@@ -15409,13 +15408,13 @@
       <c r="B109" s="6">
         <v>0</v>
       </c>
-      <c r="C109" s="46"/>
-      <c r="D109" s="47"/>
-      <c r="E109" s="42">
+      <c r="C109" s="41"/>
+      <c r="D109" s="42"/>
+      <c r="E109" s="39">
         <f t="shared" si="13"/>
         <v>0.24019607843137253</v>
       </c>
-      <c r="F109" s="42"/>
+      <c r="F109" s="39"/>
       <c r="I109" s="18">
         <f t="shared" si="14"/>
         <v>2.4019607843137255E-7</v>
@@ -15436,13 +15435,13 @@
       <c r="B110" s="6">
         <v>0</v>
       </c>
-      <c r="C110" s="46"/>
-      <c r="D110" s="47"/>
-      <c r="E110" s="42">
+      <c r="C110" s="41"/>
+      <c r="D110" s="42"/>
+      <c r="E110" s="39">
         <f t="shared" si="13"/>
         <v>0.24019607843137253</v>
       </c>
-      <c r="F110" s="42"/>
+      <c r="F110" s="39"/>
       <c r="I110" s="18">
         <f t="shared" si="14"/>
         <v>2.4019607843137255E-7</v>
@@ -15463,13 +15462,13 @@
       <c r="B111" s="6">
         <v>1.4E-2</v>
       </c>
-      <c r="C111" s="46"/>
-      <c r="D111" s="47"/>
-      <c r="E111" s="42">
+      <c r="C111" s="41"/>
+      <c r="D111" s="42"/>
+      <c r="E111" s="39">
         <f t="shared" si="13"/>
         <v>0.92647058823529405</v>
       </c>
-      <c r="F111" s="42"/>
+      <c r="F111" s="39"/>
       <c r="I111" s="18">
         <f t="shared" si="14"/>
         <v>9.2647058823529408E-7</v>
@@ -15490,13 +15489,13 @@
       <c r="B112" s="6">
         <v>8.9999999999999993E-3</v>
       </c>
-      <c r="C112" s="46"/>
-      <c r="D112" s="47"/>
-      <c r="E112" s="42">
+      <c r="C112" s="41"/>
+      <c r="D112" s="42"/>
+      <c r="E112" s="39">
         <f t="shared" si="13"/>
         <v>0.68137254901960775</v>
       </c>
-      <c r="F112" s="42"/>
+      <c r="F112" s="39"/>
       <c r="I112" s="18">
         <f t="shared" si="14"/>
         <v>6.8137254901960776E-7</v>
@@ -15517,13 +15516,13 @@
       <c r="B113" s="6">
         <v>3.9E-2</v>
       </c>
-      <c r="C113" s="46"/>
-      <c r="D113" s="47"/>
-      <c r="E113" s="42">
+      <c r="C113" s="41"/>
+      <c r="D113" s="42"/>
+      <c r="E113" s="39">
         <f t="shared" si="13"/>
         <v>2.1519607843137254</v>
       </c>
-      <c r="F113" s="42"/>
+      <c r="F113" s="39"/>
       <c r="I113" s="18">
         <f t="shared" si="14"/>
         <v>2.1519607843137253E-6</v>
@@ -15544,13 +15543,13 @@
       <c r="B114" s="6">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="C114" s="46"/>
-      <c r="D114" s="47"/>
-      <c r="E114" s="42">
+      <c r="C114" s="41"/>
+      <c r="D114" s="42"/>
+      <c r="E114" s="39">
         <f t="shared" si="13"/>
         <v>0.53431372549019607</v>
       </c>
-      <c r="F114" s="42"/>
+      <c r="F114" s="39"/>
       <c r="I114" s="18">
         <f t="shared" si="14"/>
         <v>5.3431372549019611E-7</v>
@@ -15568,16 +15567,16 @@
       <c r="H119" s="24"/>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A120" s="38" t="s">
+      <c r="A120" s="46" t="s">
         <v>27</v>
       </c>
-      <c r="B120" s="38"/>
-      <c r="C120" s="38"/>
-      <c r="D120" s="38"/>
-      <c r="E120" s="38"/>
-      <c r="F120" s="38"/>
-      <c r="G120" s="38"/>
-      <c r="H120" s="38"/>
+      <c r="B120" s="46"/>
+      <c r="C120" s="46"/>
+      <c r="D120" s="46"/>
+      <c r="E120" s="46"/>
+      <c r="F120" s="46"/>
+      <c r="G120" s="46"/>
+      <c r="H120" s="46"/>
     </row>
     <row r="122" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
@@ -15603,14 +15602,14 @@
       <c r="B123" s="4">
         <v>0</v>
       </c>
-      <c r="C123" s="63">
+      <c r="C123" s="56">
         <v>2.5</v>
       </c>
-      <c r="D123" s="64"/>
-      <c r="E123" s="55">
+      <c r="D123" s="57"/>
+      <c r="E123" s="51">
         <v>0</v>
       </c>
-      <c r="F123" s="56"/>
+      <c r="F123" s="52"/>
       <c r="G123" s="36"/>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.25">
@@ -15620,15 +15619,15 @@
       <c r="B124" s="2">
         <v>1E-3</v>
       </c>
-      <c r="C124" s="61">
+      <c r="C124" s="58">
         <v>5</v>
       </c>
-      <c r="D124" s="62"/>
-      <c r="E124" s="40">
+      <c r="D124" s="59"/>
+      <c r="E124" s="44">
         <f t="shared" ref="E124:E130" si="17">(B124+0.0067)/0.0019</f>
         <v>4.0526315789473681</v>
       </c>
-      <c r="F124" s="41"/>
+      <c r="F124" s="45"/>
       <c r="G124" s="36"/>
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.25">
@@ -15638,15 +15637,15 @@
       <c r="B125" s="6">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="C125" s="46">
+      <c r="C125" s="41">
         <v>10</v>
       </c>
-      <c r="D125" s="60"/>
-      <c r="E125" s="40">
+      <c r="D125" s="43"/>
+      <c r="E125" s="44">
         <f t="shared" si="17"/>
         <v>7.7368421052631584</v>
       </c>
-      <c r="F125" s="41"/>
+      <c r="F125" s="45"/>
       <c r="G125" s="36"/>
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.25">
@@ -15656,15 +15655,15 @@
       <c r="B126" s="6">
         <v>4.1000000000000002E-2</v>
       </c>
-      <c r="C126" s="46">
+      <c r="C126" s="41">
         <v>25</v>
       </c>
-      <c r="D126" s="60"/>
-      <c r="E126" s="40">
+      <c r="D126" s="43"/>
+      <c r="E126" s="44">
         <f t="shared" si="17"/>
         <v>25.105263157894736</v>
       </c>
-      <c r="F126" s="41"/>
+      <c r="F126" s="45"/>
       <c r="G126" s="36"/>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.25">
@@ -15674,15 +15673,15 @@
       <c r="B127" s="6">
         <v>8.3000000000000004E-2</v>
       </c>
-      <c r="C127" s="46">
+      <c r="C127" s="41">
         <v>50</v>
       </c>
-      <c r="D127" s="60"/>
-      <c r="E127" s="40">
+      <c r="D127" s="43"/>
+      <c r="E127" s="44">
         <f t="shared" si="17"/>
         <v>47.210526315789473</v>
       </c>
-      <c r="F127" s="41"/>
+      <c r="F127" s="45"/>
       <c r="G127" s="36"/>
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.25">
@@ -15692,15 +15691,15 @@
       <c r="B128" s="6">
         <v>0.17499999999999999</v>
       </c>
-      <c r="C128" s="46">
+      <c r="C128" s="41">
         <v>100</v>
       </c>
-      <c r="D128" s="60"/>
-      <c r="E128" s="40">
+      <c r="D128" s="43"/>
+      <c r="E128" s="44">
         <f t="shared" si="17"/>
         <v>95.631578947368425</v>
       </c>
-      <c r="F128" s="41"/>
+      <c r="F128" s="45"/>
       <c r="G128" s="36"/>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
@@ -15710,15 +15709,15 @@
       <c r="B129" s="6">
         <v>0.375</v>
       </c>
-      <c r="C129" s="46">
+      <c r="C129" s="41">
         <v>200</v>
       </c>
-      <c r="D129" s="60"/>
-      <c r="E129" s="40">
+      <c r="D129" s="43"/>
+      <c r="E129" s="44">
         <f t="shared" si="17"/>
         <v>200.89473684210526</v>
       </c>
-      <c r="F129" s="41"/>
+      <c r="F129" s="45"/>
       <c r="G129" s="36"/>
     </row>
     <row r="130" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -15728,15 +15727,15 @@
       <c r="B130" s="8">
         <v>0.91500000000000004</v>
       </c>
-      <c r="C130" s="48">
+      <c r="C130" s="47">
         <v>500</v>
       </c>
-      <c r="D130" s="49"/>
-      <c r="E130" s="50">
+      <c r="D130" s="48"/>
+      <c r="E130" s="62">
         <f t="shared" si="17"/>
         <v>485.1052631578948</v>
       </c>
-      <c r="F130" s="51"/>
+      <c r="F130" s="63"/>
       <c r="G130" s="36"/>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
@@ -15746,13 +15745,13 @@
       <c r="B131" s="9">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="C131" s="52"/>
-      <c r="D131" s="57"/>
-      <c r="E131" s="58">
+      <c r="C131" s="49"/>
+      <c r="D131" s="60"/>
+      <c r="E131" s="64">
         <f t="shared" ref="E131:E138" si="18">(B131+0.0067)/0.0019</f>
         <v>9.3157894736842106</v>
       </c>
-      <c r="F131" s="59"/>
+      <c r="F131" s="65"/>
       <c r="G131" s="36"/>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
@@ -15762,12 +15761,12 @@
       <c r="B132" s="6">
         <v>0</v>
       </c>
-      <c r="C132" s="46"/>
-      <c r="D132" s="60"/>
-      <c r="E132" s="40">
+      <c r="C132" s="41"/>
+      <c r="D132" s="43"/>
+      <c r="E132" s="44">
         <v>0</v>
       </c>
-      <c r="F132" s="65"/>
+      <c r="F132" s="61"/>
       <c r="G132" s="36"/>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
@@ -15777,12 +15776,12 @@
       <c r="B133" s="6">
         <v>0</v>
       </c>
-      <c r="C133" s="46"/>
-      <c r="D133" s="60"/>
-      <c r="E133" s="40">
+      <c r="C133" s="41"/>
+      <c r="D133" s="43"/>
+      <c r="E133" s="44">
         <v>0</v>
       </c>
-      <c r="F133" s="65"/>
+      <c r="F133" s="61"/>
       <c r="G133" s="36"/>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
@@ -15792,12 +15791,12 @@
       <c r="B134" s="6">
         <v>0</v>
       </c>
-      <c r="C134" s="46"/>
-      <c r="D134" s="60"/>
-      <c r="E134" s="40">
+      <c r="C134" s="41"/>
+      <c r="D134" s="43"/>
+      <c r="E134" s="44">
         <v>0</v>
       </c>
-      <c r="F134" s="65"/>
+      <c r="F134" s="61"/>
       <c r="G134" s="36"/>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
@@ -15807,12 +15806,12 @@
       <c r="B135" s="6">
         <v>0</v>
       </c>
-      <c r="C135" s="46"/>
-      <c r="D135" s="60"/>
-      <c r="E135" s="40">
+      <c r="C135" s="41"/>
+      <c r="D135" s="43"/>
+      <c r="E135" s="44">
         <v>0</v>
       </c>
-      <c r="F135" s="65"/>
+      <c r="F135" s="61"/>
       <c r="G135" s="36"/>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
@@ -15822,13 +15821,13 @@
       <c r="B136" s="6">
         <v>1.7999999999999999E-2</v>
       </c>
-      <c r="C136" s="46"/>
-      <c r="D136" s="60"/>
-      <c r="E136" s="40">
+      <c r="C136" s="41"/>
+      <c r="D136" s="43"/>
+      <c r="E136" s="44">
         <f t="shared" si="18"/>
         <v>13</v>
       </c>
-      <c r="F136" s="65"/>
+      <c r="F136" s="61"/>
       <c r="G136" s="36"/>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
@@ -15838,13 +15837,13 @@
       <c r="B137" s="6">
         <v>2.8000000000000001E-2</v>
       </c>
-      <c r="C137" s="46"/>
-      <c r="D137" s="60"/>
-      <c r="E137" s="40">
+      <c r="C137" s="41"/>
+      <c r="D137" s="43"/>
+      <c r="E137" s="44">
         <f t="shared" si="18"/>
         <v>18.263157894736842</v>
       </c>
-      <c r="F137" s="65"/>
+      <c r="F137" s="61"/>
       <c r="G137" s="36"/>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
@@ -15854,37 +15853,69 @@
       <c r="B138" s="6">
         <v>2.7E-2</v>
       </c>
-      <c r="C138" s="46"/>
-      <c r="D138" s="60"/>
-      <c r="E138" s="40">
+      <c r="C138" s="41"/>
+      <c r="D138" s="43"/>
+      <c r="E138" s="44">
         <f t="shared" si="18"/>
         <v>17.736842105263158</v>
       </c>
-      <c r="F138" s="65"/>
+      <c r="F138" s="61"/>
       <c r="G138" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="88">
-    <mergeCell ref="C137:D137"/>
-    <mergeCell ref="E137:F137"/>
-    <mergeCell ref="C138:D138"/>
-    <mergeCell ref="E138:F138"/>
-    <mergeCell ref="C132:D132"/>
-    <mergeCell ref="E132:F132"/>
-    <mergeCell ref="C133:D133"/>
-    <mergeCell ref="E133:F133"/>
-    <mergeCell ref="C134:D134"/>
-    <mergeCell ref="E134:F134"/>
-    <mergeCell ref="C135:D135"/>
-    <mergeCell ref="E135:F135"/>
-    <mergeCell ref="C136:D136"/>
-    <mergeCell ref="E136:F136"/>
-    <mergeCell ref="C128:D128"/>
-    <mergeCell ref="E128:F128"/>
-    <mergeCell ref="C129:D129"/>
-    <mergeCell ref="E129:F129"/>
-    <mergeCell ref="C130:D130"/>
-    <mergeCell ref="E130:F130"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="C59:D59"/>
+    <mergeCell ref="E59:F59"/>
+    <mergeCell ref="C56:D56"/>
+    <mergeCell ref="C55:D55"/>
+    <mergeCell ref="E55:F55"/>
+    <mergeCell ref="E56:F56"/>
+    <mergeCell ref="E106:F106"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="C58:D58"/>
+    <mergeCell ref="E58:F58"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="E66:F66"/>
+    <mergeCell ref="C60:D60"/>
+    <mergeCell ref="E60:F60"/>
+    <mergeCell ref="C61:D61"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="E62:F62"/>
+    <mergeCell ref="C67:D67"/>
+    <mergeCell ref="E67:F67"/>
+    <mergeCell ref="C68:D68"/>
+    <mergeCell ref="E68:F68"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="E63:F63"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="E64:F64"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="E65:F65"/>
+    <mergeCell ref="C109:D109"/>
+    <mergeCell ref="E109:F109"/>
+    <mergeCell ref="C110:D110"/>
+    <mergeCell ref="E110:F110"/>
+    <mergeCell ref="C111:D111"/>
+    <mergeCell ref="E111:F111"/>
+    <mergeCell ref="E127:F127"/>
+    <mergeCell ref="E101:F101"/>
+    <mergeCell ref="E102:F102"/>
+    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="E69:F69"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="E70:F70"/>
+    <mergeCell ref="C112:D112"/>
+    <mergeCell ref="E112:F112"/>
+    <mergeCell ref="E103:F103"/>
+    <mergeCell ref="E104:F104"/>
+    <mergeCell ref="E105:F105"/>
+    <mergeCell ref="C107:D107"/>
+    <mergeCell ref="E107:F107"/>
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="E108:F108"/>
     <mergeCell ref="C113:D113"/>
     <mergeCell ref="E113:F113"/>
     <mergeCell ref="C114:D114"/>
@@ -15901,58 +15932,26 @@
     <mergeCell ref="C125:D125"/>
     <mergeCell ref="E125:F125"/>
     <mergeCell ref="C127:D127"/>
-    <mergeCell ref="E127:F127"/>
-    <mergeCell ref="E101:F101"/>
-    <mergeCell ref="E102:F102"/>
-    <mergeCell ref="C69:D69"/>
-    <mergeCell ref="E69:F69"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="E70:F70"/>
-    <mergeCell ref="C112:D112"/>
-    <mergeCell ref="E112:F112"/>
-    <mergeCell ref="E103:F103"/>
-    <mergeCell ref="E104:F104"/>
-    <mergeCell ref="E105:F105"/>
-    <mergeCell ref="C107:D107"/>
-    <mergeCell ref="E107:F107"/>
-    <mergeCell ref="C108:D108"/>
-    <mergeCell ref="E108:F108"/>
-    <mergeCell ref="C109:D109"/>
-    <mergeCell ref="E109:F109"/>
-    <mergeCell ref="C110:D110"/>
-    <mergeCell ref="E110:F110"/>
-    <mergeCell ref="C111:D111"/>
-    <mergeCell ref="E111:F111"/>
-    <mergeCell ref="E68:F68"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="E63:F63"/>
-    <mergeCell ref="C64:D64"/>
-    <mergeCell ref="E64:F64"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="E65:F65"/>
-    <mergeCell ref="E106:F106"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="E57:F57"/>
-    <mergeCell ref="C58:D58"/>
-    <mergeCell ref="E58:F58"/>
-    <mergeCell ref="C66:D66"/>
-    <mergeCell ref="E66:F66"/>
-    <mergeCell ref="C60:D60"/>
-    <mergeCell ref="E60:F60"/>
-    <mergeCell ref="C61:D61"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="C62:D62"/>
-    <mergeCell ref="E62:F62"/>
-    <mergeCell ref="C67:D67"/>
-    <mergeCell ref="E67:F67"/>
-    <mergeCell ref="C68:D68"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="C59:D59"/>
-    <mergeCell ref="E59:F59"/>
-    <mergeCell ref="C56:D56"/>
-    <mergeCell ref="C55:D55"/>
-    <mergeCell ref="E55:F55"/>
-    <mergeCell ref="E56:F56"/>
+    <mergeCell ref="C128:D128"/>
+    <mergeCell ref="E128:F128"/>
+    <mergeCell ref="C129:D129"/>
+    <mergeCell ref="E129:F129"/>
+    <mergeCell ref="C130:D130"/>
+    <mergeCell ref="E130:F130"/>
+    <mergeCell ref="C137:D137"/>
+    <mergeCell ref="E137:F137"/>
+    <mergeCell ref="C138:D138"/>
+    <mergeCell ref="E138:F138"/>
+    <mergeCell ref="C132:D132"/>
+    <mergeCell ref="E132:F132"/>
+    <mergeCell ref="C133:D133"/>
+    <mergeCell ref="E133:F133"/>
+    <mergeCell ref="C134:D134"/>
+    <mergeCell ref="E134:F134"/>
+    <mergeCell ref="C135:D135"/>
+    <mergeCell ref="E135:F135"/>
+    <mergeCell ref="C136:D136"/>
+    <mergeCell ref="E136:F136"/>
   </mergeCells>
   <pageMargins left="0.11458333333333333" right="1.0416666666666666E-2" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -15975,16 +15974,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="46" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
       <c r="I1" s="1"/>
     </row>
     <row r="2" spans="1:9" s="25" customFormat="1" x14ac:dyDescent="0.25">
@@ -16188,14 +16187,14 @@
         <v>34</v>
       </c>
       <c r="B55" s="6"/>
-      <c r="C55" s="39">
+      <c r="C55" s="38">
         <v>1</v>
       </c>
-      <c r="D55" s="39"/>
-      <c r="E55" s="42">
+      <c r="D55" s="38"/>
+      <c r="E55" s="39">
         <v>0</v>
       </c>
-      <c r="F55" s="43"/>
+      <c r="F55" s="40"/>
       <c r="H55" s="18"/>
       <c r="I55" s="27"/>
       <c r="J55" s="18"/>
@@ -16205,15 +16204,15 @@
         <v>35</v>
       </c>
       <c r="B56" s="6"/>
-      <c r="C56" s="39">
+      <c r="C56" s="38">
         <v>2.5</v>
       </c>
-      <c r="D56" s="39"/>
-      <c r="E56" s="42">
+      <c r="D56" s="38"/>
+      <c r="E56" s="39">
         <f t="shared" ref="E56" si="0">(B56-0.0164)/0.0093</f>
         <v>-1.763440860215054</v>
       </c>
-      <c r="F56" s="43"/>
+      <c r="F56" s="40"/>
       <c r="H56" s="18"/>
       <c r="I56" s="27"/>
       <c r="J56" s="18"/>
@@ -16225,15 +16224,15 @@
       <c r="B57" s="6">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="C57" s="39">
+      <c r="C57" s="38">
         <v>5</v>
       </c>
-      <c r="D57" s="39"/>
-      <c r="E57" s="42">
+      <c r="D57" s="38"/>
+      <c r="E57" s="39">
         <f>(B57-0.0164)/0.0093</f>
         <v>2.0000000000000004</v>
       </c>
-      <c r="F57" s="43"/>
+      <c r="F57" s="40"/>
       <c r="H57" s="18">
         <f>C57/1000000</f>
         <v>5.0000000000000004E-6</v>
@@ -16254,15 +16253,15 @@
       <c r="B58" s="6">
         <v>8.3000000000000004E-2</v>
       </c>
-      <c r="C58" s="39">
+      <c r="C58" s="38">
         <v>10</v>
       </c>
-      <c r="D58" s="39"/>
-      <c r="E58" s="40">
+      <c r="D58" s="38"/>
+      <c r="E58" s="44">
         <f t="shared" ref="E58:E62" si="1">(B58-0.0164)/0.0093</f>
         <v>7.1612903225806468</v>
       </c>
-      <c r="F58" s="41"/>
+      <c r="F58" s="45"/>
       <c r="H58" s="18">
         <f>C58/1000000</f>
         <v>1.0000000000000001E-5</v>
@@ -16281,15 +16280,15 @@
         <v>36</v>
       </c>
       <c r="B59" s="6"/>
-      <c r="C59" s="39">
+      <c r="C59" s="38">
         <v>25</v>
       </c>
-      <c r="D59" s="39"/>
-      <c r="E59" s="40">
+      <c r="D59" s="38"/>
+      <c r="E59" s="44">
         <f t="shared" si="1"/>
         <v>-1.763440860215054</v>
       </c>
-      <c r="F59" s="41"/>
+      <c r="F59" s="45"/>
       <c r="H59" s="18"/>
       <c r="I59" s="18"/>
       <c r="J59" s="21"/>
@@ -16301,15 +16300,15 @@
       <c r="B60" s="6">
         <v>0.48499999999999999</v>
       </c>
-      <c r="C60" s="39">
+      <c r="C60" s="38">
         <v>50</v>
       </c>
-      <c r="D60" s="39"/>
-      <c r="E60" s="40">
+      <c r="D60" s="38"/>
+      <c r="E60" s="44">
         <f t="shared" si="1"/>
         <v>50.387096774193552</v>
       </c>
-      <c r="F60" s="41"/>
+      <c r="F60" s="45"/>
       <c r="H60" s="18">
         <f>C60/1000000</f>
         <v>5.0000000000000002E-5</v>
@@ -16330,15 +16329,15 @@
       <c r="B61" s="6">
         <v>0.96499999999999997</v>
       </c>
-      <c r="C61" s="39">
+      <c r="C61" s="38">
         <v>100</v>
       </c>
-      <c r="D61" s="39"/>
-      <c r="E61" s="40">
+      <c r="D61" s="38"/>
+      <c r="E61" s="44">
         <f t="shared" si="1"/>
         <v>102.00000000000001</v>
       </c>
-      <c r="F61" s="41"/>
+      <c r="F61" s="45"/>
       <c r="H61" s="18">
         <f>C61/1000000</f>
         <v>1E-4</v>
@@ -16359,15 +16358,15 @@
       <c r="B62" s="8">
         <v>1.8340000000000001</v>
       </c>
-      <c r="C62" s="48">
+      <c r="C62" s="47">
         <v>200</v>
       </c>
-      <c r="D62" s="49"/>
-      <c r="E62" s="50">
+      <c r="D62" s="48"/>
+      <c r="E62" s="62">
         <f t="shared" si="1"/>
         <v>195.44086021505379</v>
       </c>
-      <c r="F62" s="51"/>
+      <c r="F62" s="63"/>
       <c r="H62" s="19">
         <f>C62/1000000</f>
         <v>2.0000000000000001E-4</v>
@@ -16388,12 +16387,12 @@
       <c r="B63" s="9">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="C63" s="52"/>
-      <c r="D63" s="53"/>
-      <c r="E63" s="54">
+      <c r="C63" s="49"/>
+      <c r="D63" s="50"/>
+      <c r="E63" s="55">
         <v>0</v>
       </c>
-      <c r="F63" s="54"/>
+      <c r="F63" s="55"/>
       <c r="H63" s="18">
         <f t="shared" ref="H63:H70" si="4">E63/1000000</f>
         <v>0</v>
@@ -16414,12 +16413,12 @@
       <c r="B64" s="6">
         <v>2E-3</v>
       </c>
-      <c r="C64" s="46"/>
-      <c r="D64" s="47"/>
-      <c r="E64" s="42">
+      <c r="C64" s="41"/>
+      <c r="D64" s="42"/>
+      <c r="E64" s="39">
         <v>0</v>
       </c>
-      <c r="F64" s="42"/>
+      <c r="F64" s="39"/>
       <c r="H64" s="18">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -16440,12 +16439,12 @@
       <c r="B65" s="6">
         <v>2E-3</v>
       </c>
-      <c r="C65" s="46"/>
-      <c r="D65" s="47"/>
-      <c r="E65" s="42">
+      <c r="C65" s="41"/>
+      <c r="D65" s="42"/>
+      <c r="E65" s="39">
         <v>0</v>
       </c>
-      <c r="F65" s="42"/>
+      <c r="F65" s="39"/>
       <c r="H65" s="18">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -16466,12 +16465,12 @@
       <c r="B66" s="6">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="C66" s="46"/>
-      <c r="D66" s="47"/>
-      <c r="E66" s="42">
+      <c r="C66" s="41"/>
+      <c r="D66" s="42"/>
+      <c r="E66" s="39">
         <v>0</v>
       </c>
-      <c r="F66" s="42"/>
+      <c r="F66" s="39"/>
       <c r="H66" s="18">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -16492,13 +16491,13 @@
       <c r="B67" s="6">
         <v>0.109</v>
       </c>
-      <c r="C67" s="46"/>
-      <c r="D67" s="47"/>
-      <c r="E67" s="42">
+      <c r="C67" s="41"/>
+      <c r="D67" s="42"/>
+      <c r="E67" s="39">
         <f t="shared" ref="E67:E70" si="7">(B67-0.0164)/0.0093</f>
         <v>9.9569892473118298</v>
       </c>
-      <c r="F67" s="42"/>
+      <c r="F67" s="39"/>
       <c r="H67" s="18">
         <f t="shared" si="4"/>
         <v>9.9569892473118294E-6</v>
@@ -16519,13 +16518,13 @@
       <c r="B68" s="6">
         <v>0.36</v>
       </c>
-      <c r="C68" s="46"/>
-      <c r="D68" s="47"/>
-      <c r="E68" s="42">
+      <c r="C68" s="41"/>
+      <c r="D68" s="42"/>
+      <c r="E68" s="39">
         <f t="shared" si="7"/>
         <v>36.946236559139784</v>
       </c>
-      <c r="F68" s="42"/>
+      <c r="F68" s="39"/>
       <c r="H68" s="18">
         <f t="shared" si="4"/>
         <v>3.6946236559139785E-5</v>
@@ -16546,13 +16545,13 @@
       <c r="B69" s="6">
         <v>0.91300000000000003</v>
       </c>
-      <c r="C69" s="46"/>
-      <c r="D69" s="47"/>
-      <c r="E69" s="42">
+      <c r="C69" s="41"/>
+      <c r="D69" s="42"/>
+      <c r="E69" s="39">
         <f t="shared" si="7"/>
         <v>96.408602150537646</v>
       </c>
-      <c r="F69" s="42"/>
+      <c r="F69" s="39"/>
       <c r="H69" s="18">
         <f t="shared" si="4"/>
         <v>9.6408602150537646E-5</v>
@@ -16573,13 +16572,13 @@
       <c r="B70" s="6">
         <v>4.7E-2</v>
       </c>
-      <c r="C70" s="46"/>
-      <c r="D70" s="47"/>
-      <c r="E70" s="42">
+      <c r="C70" s="41"/>
+      <c r="D70" s="42"/>
+      <c r="E70" s="39">
         <f t="shared" si="7"/>
         <v>3.2903225806451615</v>
       </c>
-      <c r="F70" s="42"/>
+      <c r="F70" s="39"/>
       <c r="H70" s="18">
         <f t="shared" si="4"/>
         <v>3.2903225806451615E-6</v>
@@ -16665,11 +16664,11 @@
         <v>0.5</v>
       </c>
       <c r="D101" s="11"/>
-      <c r="E101" s="55">
+      <c r="E101" s="51">
         <f>(B101+0.0049)/0.0204</f>
         <v>0.28921568627450978</v>
       </c>
-      <c r="F101" s="56"/>
+      <c r="F101" s="52"/>
       <c r="I101" s="16">
         <f t="shared" ref="I101:I106" si="8">C101/1000000</f>
         <v>4.9999999999999998E-7</v>
@@ -16694,11 +16693,11 @@
         <v>1</v>
       </c>
       <c r="D102" s="13"/>
-      <c r="E102" s="42">
+      <c r="E102" s="39">
         <f t="shared" ref="E102:E114" si="10">(B102+0.0049)/0.0204</f>
         <v>1.0245098039215685</v>
       </c>
-      <c r="F102" s="43"/>
+      <c r="F102" s="40"/>
       <c r="I102" s="18">
         <f t="shared" si="8"/>
         <v>9.9999999999999995E-7</v>
@@ -16723,11 +16722,11 @@
         <v>5</v>
       </c>
       <c r="D103" s="13"/>
-      <c r="E103" s="42">
+      <c r="E103" s="39">
         <f t="shared" si="10"/>
         <v>4.6029411764705879</v>
       </c>
-      <c r="F103" s="43"/>
+      <c r="F103" s="40"/>
       <c r="I103" s="18">
         <f t="shared" si="8"/>
         <v>5.0000000000000004E-6</v>
@@ -16752,11 +16751,11 @@
         <v>10</v>
       </c>
       <c r="D104" s="13"/>
-      <c r="E104" s="42">
+      <c r="E104" s="39">
         <f t="shared" si="10"/>
         <v>10.877450980392155</v>
       </c>
-      <c r="F104" s="43"/>
+      <c r="F104" s="40"/>
       <c r="I104" s="18">
         <f t="shared" si="8"/>
         <v>1.0000000000000001E-5</v>
@@ -16781,11 +16780,11 @@
         <v>25</v>
       </c>
       <c r="D105" s="33"/>
-      <c r="E105" s="42">
+      <c r="E105" s="39">
         <f t="shared" si="10"/>
         <v>24.799019607843135</v>
       </c>
-      <c r="F105" s="43"/>
+      <c r="F105" s="40"/>
       <c r="I105" s="19">
         <f t="shared" si="8"/>
         <v>2.5000000000000001E-5</v>
@@ -16810,11 +16809,11 @@
         <v>50</v>
       </c>
       <c r="D106" s="15"/>
-      <c r="E106" s="44">
+      <c r="E106" s="53">
         <f t="shared" si="10"/>
         <v>37.446078431372548</v>
       </c>
-      <c r="F106" s="45"/>
+      <c r="F106" s="54"/>
       <c r="I106" s="18">
         <f t="shared" si="8"/>
         <v>5.0000000000000002E-5</v>
@@ -16835,13 +16834,13 @@
       <c r="B107" s="9">
         <v>0</v>
       </c>
-      <c r="C107" s="52"/>
-      <c r="D107" s="53"/>
-      <c r="E107" s="54">
+      <c r="C107" s="49"/>
+      <c r="D107" s="50"/>
+      <c r="E107" s="55">
         <f t="shared" si="10"/>
         <v>0.24019607843137253</v>
       </c>
-      <c r="F107" s="54"/>
+      <c r="F107" s="55"/>
       <c r="I107" s="18">
         <f>E107/1000000</f>
         <v>2.4019607843137255E-7</v>
@@ -16862,13 +16861,13 @@
       <c r="B108" s="6">
         <v>0</v>
       </c>
-      <c r="C108" s="46"/>
-      <c r="D108" s="47"/>
-      <c r="E108" s="42">
+      <c r="C108" s="41"/>
+      <c r="D108" s="42"/>
+      <c r="E108" s="39">
         <f t="shared" si="10"/>
         <v>0.24019607843137253</v>
       </c>
-      <c r="F108" s="42"/>
+      <c r="F108" s="39"/>
       <c r="I108" s="18">
         <f t="shared" ref="I108:I114" si="12">E108/1000000</f>
         <v>2.4019607843137255E-7</v>
@@ -16889,13 +16888,13 @@
       <c r="B109" s="6">
         <v>0</v>
       </c>
-      <c r="C109" s="46"/>
-      <c r="D109" s="47"/>
-      <c r="E109" s="42">
+      <c r="C109" s="41"/>
+      <c r="D109" s="42"/>
+      <c r="E109" s="39">
         <f t="shared" si="10"/>
         <v>0.24019607843137253</v>
       </c>
-      <c r="F109" s="42"/>
+      <c r="F109" s="39"/>
       <c r="I109" s="18">
         <f t="shared" si="12"/>
         <v>2.4019607843137255E-7</v>
@@ -16916,13 +16915,13 @@
       <c r="B110" s="6">
         <v>0</v>
       </c>
-      <c r="C110" s="46"/>
-      <c r="D110" s="47"/>
-      <c r="E110" s="42">
+      <c r="C110" s="41"/>
+      <c r="D110" s="42"/>
+      <c r="E110" s="39">
         <f t="shared" si="10"/>
         <v>0.24019607843137253</v>
       </c>
-      <c r="F110" s="42"/>
+      <c r="F110" s="39"/>
       <c r="I110" s="18">
         <f t="shared" si="12"/>
         <v>2.4019607843137255E-7</v>
@@ -16943,13 +16942,13 @@
       <c r="B111" s="6">
         <v>1.4E-2</v>
       </c>
-      <c r="C111" s="46"/>
-      <c r="D111" s="47"/>
-      <c r="E111" s="42">
+      <c r="C111" s="41"/>
+      <c r="D111" s="42"/>
+      <c r="E111" s="39">
         <f t="shared" si="10"/>
         <v>0.92647058823529405</v>
       </c>
-      <c r="F111" s="42"/>
+      <c r="F111" s="39"/>
       <c r="I111" s="18">
         <f t="shared" si="12"/>
         <v>9.2647058823529408E-7</v>
@@ -16970,13 +16969,13 @@
       <c r="B112" s="6">
         <v>8.9999999999999993E-3</v>
       </c>
-      <c r="C112" s="46"/>
-      <c r="D112" s="47"/>
-      <c r="E112" s="42">
+      <c r="C112" s="41"/>
+      <c r="D112" s="42"/>
+      <c r="E112" s="39">
         <f t="shared" si="10"/>
         <v>0.68137254901960775</v>
       </c>
-      <c r="F112" s="42"/>
+      <c r="F112" s="39"/>
       <c r="I112" s="18">
         <f t="shared" si="12"/>
         <v>6.8137254901960776E-7</v>
@@ -16997,13 +16996,13 @@
       <c r="B113" s="6">
         <v>3.9E-2</v>
       </c>
-      <c r="C113" s="46"/>
-      <c r="D113" s="47"/>
-      <c r="E113" s="42">
+      <c r="C113" s="41"/>
+      <c r="D113" s="42"/>
+      <c r="E113" s="39">
         <f t="shared" si="10"/>
         <v>2.1519607843137254</v>
       </c>
-      <c r="F113" s="42"/>
+      <c r="F113" s="39"/>
       <c r="I113" s="18">
         <f t="shared" si="12"/>
         <v>2.1519607843137253E-6</v>
@@ -17024,13 +17023,13 @@
       <c r="B114" s="6">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="C114" s="46"/>
-      <c r="D114" s="47"/>
-      <c r="E114" s="42">
+      <c r="C114" s="41"/>
+      <c r="D114" s="42"/>
+      <c r="E114" s="39">
         <f t="shared" si="10"/>
         <v>0.53431372549019607</v>
       </c>
-      <c r="F114" s="42"/>
+      <c r="F114" s="39"/>
       <c r="I114" s="18">
         <f t="shared" si="12"/>
         <v>5.3431372549019611E-7</v>
@@ -17048,16 +17047,16 @@
       <c r="H119" s="24"/>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A120" s="38" t="s">
+      <c r="A120" s="46" t="s">
         <v>27</v>
       </c>
-      <c r="B120" s="38"/>
-      <c r="C120" s="38"/>
-      <c r="D120" s="38"/>
-      <c r="E120" s="38"/>
-      <c r="F120" s="38"/>
-      <c r="G120" s="38"/>
-      <c r="H120" s="38"/>
+      <c r="B120" s="46"/>
+      <c r="C120" s="46"/>
+      <c r="D120" s="46"/>
+      <c r="E120" s="46"/>
+      <c r="F120" s="46"/>
+      <c r="G120" s="46"/>
+      <c r="H120" s="46"/>
     </row>
     <row r="122" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
@@ -17083,14 +17082,14 @@
       <c r="B123" s="4">
         <v>0</v>
       </c>
-      <c r="C123" s="63">
+      <c r="C123" s="56">
         <v>2.5</v>
       </c>
-      <c r="D123" s="64"/>
-      <c r="E123" s="55">
+      <c r="D123" s="57"/>
+      <c r="E123" s="51">
         <v>0</v>
       </c>
-      <c r="F123" s="56"/>
+      <c r="F123" s="52"/>
       <c r="G123" s="36"/>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.25">
@@ -17100,15 +17099,15 @@
       <c r="B124" s="2">
         <v>1E-3</v>
       </c>
-      <c r="C124" s="61">
+      <c r="C124" s="58">
         <v>5</v>
       </c>
-      <c r="D124" s="62"/>
-      <c r="E124" s="40">
+      <c r="D124" s="59"/>
+      <c r="E124" s="44">
         <f t="shared" ref="E124:E138" si="15">(B124+0.0067)/0.0019</f>
         <v>4.0526315789473681</v>
       </c>
-      <c r="F124" s="41"/>
+      <c r="F124" s="45"/>
       <c r="G124" s="36"/>
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.25">
@@ -17118,15 +17117,15 @@
       <c r="B125" s="6">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="C125" s="46">
+      <c r="C125" s="41">
         <v>10</v>
       </c>
-      <c r="D125" s="60"/>
-      <c r="E125" s="40">
+      <c r="D125" s="43"/>
+      <c r="E125" s="44">
         <f t="shared" si="15"/>
         <v>7.7368421052631584</v>
       </c>
-      <c r="F125" s="41"/>
+      <c r="F125" s="45"/>
       <c r="G125" s="36"/>
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.25">
@@ -17136,15 +17135,15 @@
       <c r="B126" s="6">
         <v>4.1000000000000002E-2</v>
       </c>
-      <c r="C126" s="46">
+      <c r="C126" s="41">
         <v>25</v>
       </c>
-      <c r="D126" s="60"/>
-      <c r="E126" s="40">
+      <c r="D126" s="43"/>
+      <c r="E126" s="44">
         <f t="shared" si="15"/>
         <v>25.105263157894736</v>
       </c>
-      <c r="F126" s="41"/>
+      <c r="F126" s="45"/>
       <c r="G126" s="36"/>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.25">
@@ -17154,15 +17153,15 @@
       <c r="B127" s="6">
         <v>8.3000000000000004E-2</v>
       </c>
-      <c r="C127" s="46">
+      <c r="C127" s="41">
         <v>50</v>
       </c>
-      <c r="D127" s="60"/>
-      <c r="E127" s="40">
+      <c r="D127" s="43"/>
+      <c r="E127" s="44">
         <f t="shared" si="15"/>
         <v>47.210526315789473</v>
       </c>
-      <c r="F127" s="41"/>
+      <c r="F127" s="45"/>
       <c r="G127" s="36"/>
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.25">
@@ -17172,15 +17171,15 @@
       <c r="B128" s="6">
         <v>0.17499999999999999</v>
       </c>
-      <c r="C128" s="46">
+      <c r="C128" s="41">
         <v>100</v>
       </c>
-      <c r="D128" s="60"/>
-      <c r="E128" s="40">
+      <c r="D128" s="43"/>
+      <c r="E128" s="44">
         <f t="shared" si="15"/>
         <v>95.631578947368425</v>
       </c>
-      <c r="F128" s="41"/>
+      <c r="F128" s="45"/>
       <c r="G128" s="36"/>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
@@ -17190,15 +17189,15 @@
       <c r="B129" s="6">
         <v>0.375</v>
       </c>
-      <c r="C129" s="46">
+      <c r="C129" s="41">
         <v>200</v>
       </c>
-      <c r="D129" s="60"/>
-      <c r="E129" s="40">
+      <c r="D129" s="43"/>
+      <c r="E129" s="44">
         <f t="shared" si="15"/>
         <v>200.89473684210526</v>
       </c>
-      <c r="F129" s="41"/>
+      <c r="F129" s="45"/>
       <c r="G129" s="36"/>
     </row>
     <row r="130" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -17208,15 +17207,15 @@
       <c r="B130" s="8">
         <v>0.91500000000000004</v>
       </c>
-      <c r="C130" s="48">
+      <c r="C130" s="47">
         <v>500</v>
       </c>
-      <c r="D130" s="49"/>
-      <c r="E130" s="50">
+      <c r="D130" s="48"/>
+      <c r="E130" s="62">
         <f t="shared" si="15"/>
         <v>485.1052631578948</v>
       </c>
-      <c r="F130" s="51"/>
+      <c r="F130" s="63"/>
       <c r="G130" s="36"/>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
@@ -17226,13 +17225,13 @@
       <c r="B131" s="9">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="C131" s="52"/>
-      <c r="D131" s="57"/>
-      <c r="E131" s="58">
+      <c r="C131" s="49"/>
+      <c r="D131" s="60"/>
+      <c r="E131" s="64">
         <f t="shared" si="15"/>
         <v>9.3157894736842106</v>
       </c>
-      <c r="F131" s="59"/>
+      <c r="F131" s="65"/>
       <c r="G131" s="36"/>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
@@ -17242,12 +17241,12 @@
       <c r="B132" s="6">
         <v>0</v>
       </c>
-      <c r="C132" s="46"/>
-      <c r="D132" s="60"/>
-      <c r="E132" s="40">
+      <c r="C132" s="41"/>
+      <c r="D132" s="43"/>
+      <c r="E132" s="44">
         <v>0</v>
       </c>
-      <c r="F132" s="65"/>
+      <c r="F132" s="61"/>
       <c r="G132" s="36"/>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
@@ -17257,12 +17256,12 @@
       <c r="B133" s="6">
         <v>0</v>
       </c>
-      <c r="C133" s="46"/>
-      <c r="D133" s="60"/>
-      <c r="E133" s="40">
+      <c r="C133" s="41"/>
+      <c r="D133" s="43"/>
+      <c r="E133" s="44">
         <v>0</v>
       </c>
-      <c r="F133" s="65"/>
+      <c r="F133" s="61"/>
       <c r="G133" s="36"/>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
@@ -17272,12 +17271,12 @@
       <c r="B134" s="6">
         <v>0</v>
       </c>
-      <c r="C134" s="46"/>
-      <c r="D134" s="60"/>
-      <c r="E134" s="40">
+      <c r="C134" s="41"/>
+      <c r="D134" s="43"/>
+      <c r="E134" s="44">
         <v>0</v>
       </c>
-      <c r="F134" s="65"/>
+      <c r="F134" s="61"/>
       <c r="G134" s="36"/>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
@@ -17287,12 +17286,12 @@
       <c r="B135" s="6">
         <v>0</v>
       </c>
-      <c r="C135" s="46"/>
-      <c r="D135" s="60"/>
-      <c r="E135" s="40">
+      <c r="C135" s="41"/>
+      <c r="D135" s="43"/>
+      <c r="E135" s="44">
         <v>0</v>
       </c>
-      <c r="F135" s="65"/>
+      <c r="F135" s="61"/>
       <c r="G135" s="36"/>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
@@ -17302,13 +17301,13 @@
       <c r="B136" s="6">
         <v>1.7999999999999999E-2</v>
       </c>
-      <c r="C136" s="46"/>
-      <c r="D136" s="60"/>
-      <c r="E136" s="40">
+      <c r="C136" s="41"/>
+      <c r="D136" s="43"/>
+      <c r="E136" s="44">
         <f t="shared" si="15"/>
         <v>13</v>
       </c>
-      <c r="F136" s="65"/>
+      <c r="F136" s="61"/>
       <c r="G136" s="36"/>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
@@ -17318,13 +17317,13 @@
       <c r="B137" s="6">
         <v>2.8000000000000001E-2</v>
       </c>
-      <c r="C137" s="46"/>
-      <c r="D137" s="60"/>
-      <c r="E137" s="40">
+      <c r="C137" s="41"/>
+      <c r="D137" s="43"/>
+      <c r="E137" s="44">
         <f t="shared" si="15"/>
         <v>18.263157894736842</v>
       </c>
-      <c r="F137" s="65"/>
+      <c r="F137" s="61"/>
       <c r="G137" s="36"/>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
@@ -17334,43 +17333,66 @@
       <c r="B138" s="6">
         <v>2.7E-2</v>
       </c>
-      <c r="C138" s="46"/>
-      <c r="D138" s="60"/>
-      <c r="E138" s="40">
+      <c r="C138" s="41"/>
+      <c r="D138" s="43"/>
+      <c r="E138" s="44">
         <f t="shared" si="15"/>
         <v>17.736842105263158</v>
       </c>
-      <c r="F138" s="65"/>
+      <c r="F138" s="61"/>
       <c r="G138" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="88">
-    <mergeCell ref="C138:D138"/>
-    <mergeCell ref="E138:F138"/>
-    <mergeCell ref="C135:D135"/>
-    <mergeCell ref="E135:F135"/>
-    <mergeCell ref="C136:D136"/>
-    <mergeCell ref="E136:F136"/>
-    <mergeCell ref="C137:D137"/>
-    <mergeCell ref="E137:F137"/>
-    <mergeCell ref="C132:D132"/>
-    <mergeCell ref="E132:F132"/>
-    <mergeCell ref="C133:D133"/>
-    <mergeCell ref="E133:F133"/>
-    <mergeCell ref="C134:D134"/>
-    <mergeCell ref="E134:F134"/>
-    <mergeCell ref="C129:D129"/>
-    <mergeCell ref="E129:F129"/>
-    <mergeCell ref="C130:D130"/>
-    <mergeCell ref="E130:F130"/>
-    <mergeCell ref="C131:D131"/>
-    <mergeCell ref="E131:F131"/>
-    <mergeCell ref="C126:D126"/>
-    <mergeCell ref="E126:F126"/>
-    <mergeCell ref="C127:D127"/>
-    <mergeCell ref="E127:F127"/>
-    <mergeCell ref="C128:D128"/>
-    <mergeCell ref="E128:F128"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="C55:D55"/>
+    <mergeCell ref="E55:F55"/>
+    <mergeCell ref="C56:D56"/>
+    <mergeCell ref="E56:F56"/>
+    <mergeCell ref="C58:D58"/>
+    <mergeCell ref="E58:F58"/>
+    <mergeCell ref="C59:D59"/>
+    <mergeCell ref="E59:F59"/>
+    <mergeCell ref="C60:D60"/>
+    <mergeCell ref="E60:F60"/>
+    <mergeCell ref="C61:D61"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="E62:F62"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="E63:F63"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="E64:F64"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="E65:F65"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="E66:F66"/>
+    <mergeCell ref="E104:F104"/>
+    <mergeCell ref="C67:D67"/>
+    <mergeCell ref="E67:F67"/>
+    <mergeCell ref="C68:D68"/>
+    <mergeCell ref="E68:F68"/>
+    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="E69:F69"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="E70:F70"/>
+    <mergeCell ref="E101:F101"/>
+    <mergeCell ref="E102:F102"/>
+    <mergeCell ref="E103:F103"/>
+    <mergeCell ref="E105:F105"/>
+    <mergeCell ref="E106:F106"/>
+    <mergeCell ref="C107:D107"/>
+    <mergeCell ref="E107:F107"/>
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="E108:F108"/>
+    <mergeCell ref="C109:D109"/>
+    <mergeCell ref="E109:F109"/>
+    <mergeCell ref="C110:D110"/>
+    <mergeCell ref="E110:F110"/>
+    <mergeCell ref="C111:D111"/>
+    <mergeCell ref="E111:F111"/>
     <mergeCell ref="C125:D125"/>
     <mergeCell ref="E125:F125"/>
     <mergeCell ref="C112:D112"/>
@@ -17384,55 +17406,32 @@
     <mergeCell ref="E123:F123"/>
     <mergeCell ref="C124:D124"/>
     <mergeCell ref="E124:F124"/>
-    <mergeCell ref="C109:D109"/>
-    <mergeCell ref="E109:F109"/>
-    <mergeCell ref="C110:D110"/>
-    <mergeCell ref="E110:F110"/>
-    <mergeCell ref="C111:D111"/>
-    <mergeCell ref="E111:F111"/>
-    <mergeCell ref="E105:F105"/>
-    <mergeCell ref="E106:F106"/>
-    <mergeCell ref="C107:D107"/>
-    <mergeCell ref="E107:F107"/>
-    <mergeCell ref="C108:D108"/>
-    <mergeCell ref="E108:F108"/>
-    <mergeCell ref="E104:F104"/>
-    <mergeCell ref="C67:D67"/>
-    <mergeCell ref="E67:F67"/>
-    <mergeCell ref="C68:D68"/>
-    <mergeCell ref="E68:F68"/>
-    <mergeCell ref="C69:D69"/>
-    <mergeCell ref="E69:F69"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="E70:F70"/>
-    <mergeCell ref="E101:F101"/>
-    <mergeCell ref="E102:F102"/>
-    <mergeCell ref="E103:F103"/>
-    <mergeCell ref="C64:D64"/>
-    <mergeCell ref="E64:F64"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="E65:F65"/>
-    <mergeCell ref="C66:D66"/>
-    <mergeCell ref="E66:F66"/>
-    <mergeCell ref="C61:D61"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="C62:D62"/>
-    <mergeCell ref="E62:F62"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="E63:F63"/>
-    <mergeCell ref="C58:D58"/>
-    <mergeCell ref="E58:F58"/>
-    <mergeCell ref="C59:D59"/>
-    <mergeCell ref="E59:F59"/>
-    <mergeCell ref="C60:D60"/>
-    <mergeCell ref="E60:F60"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="E57:F57"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="C55:D55"/>
-    <mergeCell ref="E55:F55"/>
-    <mergeCell ref="C56:D56"/>
-    <mergeCell ref="E56:F56"/>
+    <mergeCell ref="C126:D126"/>
+    <mergeCell ref="E126:F126"/>
+    <mergeCell ref="C127:D127"/>
+    <mergeCell ref="E127:F127"/>
+    <mergeCell ref="C128:D128"/>
+    <mergeCell ref="E128:F128"/>
+    <mergeCell ref="C129:D129"/>
+    <mergeCell ref="E129:F129"/>
+    <mergeCell ref="C130:D130"/>
+    <mergeCell ref="E130:F130"/>
+    <mergeCell ref="C131:D131"/>
+    <mergeCell ref="E131:F131"/>
+    <mergeCell ref="C132:D132"/>
+    <mergeCell ref="E132:F132"/>
+    <mergeCell ref="C133:D133"/>
+    <mergeCell ref="E133:F133"/>
+    <mergeCell ref="C134:D134"/>
+    <mergeCell ref="E134:F134"/>
+    <mergeCell ref="C138:D138"/>
+    <mergeCell ref="E138:F138"/>
+    <mergeCell ref="C135:D135"/>
+    <mergeCell ref="E135:F135"/>
+    <mergeCell ref="C136:D136"/>
+    <mergeCell ref="E136:F136"/>
+    <mergeCell ref="C137:D137"/>
+    <mergeCell ref="E137:F137"/>
   </mergeCells>
   <pageMargins left="0.11458333333333333" right="1.0416666666666666E-2" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -17455,16 +17454,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="46" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
       <c r="I1" s="1"/>
     </row>
     <row r="2" spans="1:9" s="25" customFormat="1" x14ac:dyDescent="0.25">
@@ -17673,14 +17672,14 @@
         <v>34</v>
       </c>
       <c r="B56" s="6"/>
-      <c r="C56" s="39">
+      <c r="C56" s="38">
         <v>1</v>
       </c>
-      <c r="D56" s="39"/>
-      <c r="E56" s="42">
+      <c r="D56" s="38"/>
+      <c r="E56" s="39">
         <v>0</v>
       </c>
-      <c r="F56" s="43"/>
+      <c r="F56" s="40"/>
       <c r="H56" s="18"/>
       <c r="I56" s="27"/>
       <c r="J56" s="18"/>
@@ -17690,15 +17689,15 @@
         <v>35</v>
       </c>
       <c r="B57" s="6"/>
-      <c r="C57" s="39">
+      <c r="C57" s="38">
         <v>2.5</v>
       </c>
-      <c r="D57" s="39"/>
-      <c r="E57" s="42">
+      <c r="D57" s="38"/>
+      <c r="E57" s="39">
         <f>(B57+0.0048)/0.0096</f>
         <v>0.5</v>
       </c>
-      <c r="F57" s="43"/>
+      <c r="F57" s="40"/>
       <c r="H57" s="18"/>
       <c r="I57" s="27"/>
       <c r="J57" s="18"/>
@@ -17710,15 +17709,15 @@
       <c r="B58" s="6">
         <v>3.5999999999999997E-2</v>
       </c>
-      <c r="C58" s="39">
+      <c r="C58" s="38">
         <v>5</v>
       </c>
-      <c r="D58" s="39"/>
-      <c r="E58" s="42">
+      <c r="D58" s="38"/>
+      <c r="E58" s="39">
         <f>(B58+0.0048)/0.0096</f>
         <v>4.25</v>
       </c>
-      <c r="F58" s="43"/>
+      <c r="F58" s="40"/>
       <c r="H58" s="18">
         <f>C58/1000000</f>
         <v>5.0000000000000004E-6</v>
@@ -17739,15 +17738,15 @@
       <c r="B59" s="6">
         <v>0.08</v>
       </c>
-      <c r="C59" s="39">
+      <c r="C59" s="38">
         <v>10</v>
       </c>
-      <c r="D59" s="39"/>
-      <c r="E59" s="42">
+      <c r="D59" s="38"/>
+      <c r="E59" s="39">
         <f t="shared" ref="E59:E62" si="0">(B59+0.0048)/0.0096</f>
         <v>8.8333333333333339</v>
       </c>
-      <c r="F59" s="43"/>
+      <c r="F59" s="40"/>
       <c r="H59" s="18">
         <f>C59/1000000</f>
         <v>1.0000000000000001E-5</v>
@@ -17766,15 +17765,15 @@
         <v>36</v>
       </c>
       <c r="B60" s="6"/>
-      <c r="C60" s="39">
+      <c r="C60" s="38">
         <v>25</v>
       </c>
-      <c r="D60" s="39"/>
-      <c r="E60" s="42">
+      <c r="D60" s="38"/>
+      <c r="E60" s="39">
         <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
-      <c r="F60" s="43"/>
+      <c r="F60" s="40"/>
       <c r="H60" s="18"/>
       <c r="I60" s="18"/>
       <c r="J60" s="21"/>
@@ -17786,15 +17785,15 @@
       <c r="B61" s="6">
         <v>0.48399999999999999</v>
       </c>
-      <c r="C61" s="39">
+      <c r="C61" s="38">
         <v>50</v>
       </c>
-      <c r="D61" s="39"/>
-      <c r="E61" s="42">
+      <c r="D61" s="38"/>
+      <c r="E61" s="39">
         <f t="shared" si="0"/>
         <v>50.916666666666671</v>
       </c>
-      <c r="F61" s="43"/>
+      <c r="F61" s="40"/>
       <c r="H61" s="18">
         <f>C61/1000000</f>
         <v>5.0000000000000002E-5</v>
@@ -17815,15 +17814,15 @@
       <c r="B62" s="6">
         <v>0.97299999999999998</v>
       </c>
-      <c r="C62" s="39">
+      <c r="C62" s="38">
         <v>100</v>
       </c>
-      <c r="D62" s="39"/>
-      <c r="E62" s="42">
+      <c r="D62" s="38"/>
+      <c r="E62" s="39">
         <f t="shared" si="0"/>
         <v>101.85416666666667</v>
       </c>
-      <c r="F62" s="43"/>
+      <c r="F62" s="40"/>
       <c r="H62" s="18">
         <f>C62/1000000</f>
         <v>1E-4</v>
@@ -17844,15 +17843,15 @@
       <c r="B63" s="8">
         <v>1.899</v>
       </c>
-      <c r="C63" s="48">
+      <c r="C63" s="47">
         <v>200</v>
       </c>
-      <c r="D63" s="49"/>
-      <c r="E63" s="44">
+      <c r="D63" s="48"/>
+      <c r="E63" s="53">
         <f t="shared" ref="E63" si="3">(B63+0.0048)/0.0096</f>
         <v>198.3125</v>
       </c>
-      <c r="F63" s="45"/>
+      <c r="F63" s="54"/>
       <c r="H63" s="19">
         <f>C63/1000000</f>
         <v>2.0000000000000001E-4</v>
@@ -17873,13 +17872,13 @@
       <c r="B64" s="9">
         <v>1.25</v>
       </c>
-      <c r="C64" s="52"/>
-      <c r="D64" s="53"/>
-      <c r="E64" s="54">
+      <c r="C64" s="49"/>
+      <c r="D64" s="50"/>
+      <c r="E64" s="55">
         <f t="shared" ref="E64" si="4">(B64+0.0048)/0.0096</f>
         <v>130.70833333333334</v>
       </c>
-      <c r="F64" s="66"/>
+      <c r="F64" s="68"/>
       <c r="H64" s="18">
         <f t="shared" ref="H64:H71" si="5">E64/1000000</f>
         <v>1.3070833333333334E-4</v>
@@ -17900,13 +17899,13 @@
       <c r="B65" s="6">
         <v>1E-3</v>
       </c>
-      <c r="C65" s="46"/>
-      <c r="D65" s="47"/>
-      <c r="E65" s="54">
+      <c r="C65" s="41"/>
+      <c r="D65" s="42"/>
+      <c r="E65" s="55">
         <f t="shared" ref="E65:E71" si="6">(B65+0.0048)/0.0096</f>
         <v>0.60416666666666663</v>
       </c>
-      <c r="F65" s="66"/>
+      <c r="F65" s="68"/>
       <c r="H65" s="18">
         <f t="shared" si="5"/>
         <v>6.0416666666666667E-7</v>
@@ -17927,13 +17926,13 @@
       <c r="B66" s="6">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="C66" s="46"/>
-      <c r="D66" s="47"/>
-      <c r="E66" s="54">
+      <c r="C66" s="41"/>
+      <c r="D66" s="42"/>
+      <c r="E66" s="55">
         <f t="shared" si="6"/>
         <v>1.0208333333333335</v>
       </c>
-      <c r="F66" s="66"/>
+      <c r="F66" s="68"/>
       <c r="H66" s="18">
         <f t="shared" si="5"/>
         <v>1.0208333333333334E-6</v>
@@ -17954,13 +17953,13 @@
       <c r="B67" s="6">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="C67" s="46"/>
-      <c r="D67" s="47"/>
-      <c r="E67" s="54">
+      <c r="C67" s="41"/>
+      <c r="D67" s="42"/>
+      <c r="E67" s="55">
         <f t="shared" si="6"/>
         <v>1.3333333333333333</v>
       </c>
-      <c r="F67" s="66"/>
+      <c r="F67" s="68"/>
       <c r="H67" s="18">
         <f t="shared" si="5"/>
         <v>1.3333333333333332E-6</v>
@@ -17981,13 +17980,13 @@
       <c r="B68" s="6">
         <v>1.4E-2</v>
       </c>
-      <c r="C68" s="46"/>
-      <c r="D68" s="47"/>
-      <c r="E68" s="54">
+      <c r="C68" s="41"/>
+      <c r="D68" s="42"/>
+      <c r="E68" s="55">
         <f t="shared" si="6"/>
         <v>1.9583333333333335</v>
       </c>
-      <c r="F68" s="66"/>
+      <c r="F68" s="68"/>
       <c r="H68" s="18">
         <f t="shared" si="5"/>
         <v>1.9583333333333334E-6</v>
@@ -18008,13 +18007,13 @@
       <c r="B69" s="6">
         <v>2.4E-2</v>
       </c>
-      <c r="C69" s="46"/>
-      <c r="D69" s="47"/>
-      <c r="E69" s="54">
+      <c r="C69" s="41"/>
+      <c r="D69" s="42"/>
+      <c r="E69" s="55">
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="F69" s="66"/>
+      <c r="F69" s="68"/>
       <c r="H69" s="18">
         <f t="shared" si="5"/>
         <v>3.0000000000000001E-6</v>
@@ -18035,13 +18034,13 @@
       <c r="B70" s="6">
         <v>4.1000000000000002E-2</v>
       </c>
-      <c r="C70" s="46"/>
-      <c r="D70" s="47"/>
-      <c r="E70" s="54">
+      <c r="C70" s="41"/>
+      <c r="D70" s="42"/>
+      <c r="E70" s="55">
         <f t="shared" si="6"/>
         <v>4.7708333333333339</v>
       </c>
-      <c r="F70" s="66"/>
+      <c r="F70" s="68"/>
       <c r="H70" s="18">
         <f t="shared" si="5"/>
         <v>4.7708333333333335E-6</v>
@@ -18062,13 +18061,13 @@
       <c r="B71" s="6">
         <v>0.311</v>
       </c>
-      <c r="C71" s="46"/>
-      <c r="D71" s="47"/>
-      <c r="E71" s="54">
+      <c r="C71" s="41"/>
+      <c r="D71" s="42"/>
+      <c r="E71" s="55">
         <f t="shared" si="6"/>
         <v>32.895833333333336</v>
       </c>
-      <c r="F71" s="66"/>
+      <c r="F71" s="68"/>
       <c r="H71" s="18">
         <f t="shared" si="5"/>
         <v>3.2895833333333338E-5</v>
@@ -18154,11 +18153,11 @@
         <v>0.5</v>
       </c>
       <c r="D102" s="11"/>
-      <c r="E102" s="55">
+      <c r="E102" s="51">
         <f>(B102+0.001)/0.0211</f>
         <v>0.56872037914691942</v>
       </c>
-      <c r="F102" s="56"/>
+      <c r="F102" s="52"/>
       <c r="I102" s="16">
         <f t="shared" ref="I102:I107" si="9">C102/1000000</f>
         <v>4.9999999999999998E-7</v>
@@ -18183,11 +18182,11 @@
         <v>1</v>
       </c>
       <c r="D103" s="13"/>
-      <c r="E103" s="42">
+      <c r="E103" s="39">
         <f t="shared" ref="E103:E107" si="11">(B103+0.001)/0.0211</f>
         <v>1.0426540284360191</v>
       </c>
-      <c r="F103" s="43"/>
+      <c r="F103" s="40"/>
       <c r="I103" s="18">
         <f t="shared" si="9"/>
         <v>9.9999999999999995E-7</v>
@@ -18212,11 +18211,11 @@
         <v>5</v>
       </c>
       <c r="D104" s="13"/>
-      <c r="E104" s="42">
+      <c r="E104" s="39">
         <f t="shared" si="11"/>
         <v>5.0236966824644549</v>
       </c>
-      <c r="F104" s="43"/>
+      <c r="F104" s="40"/>
       <c r="I104" s="18">
         <f t="shared" si="9"/>
         <v>5.0000000000000004E-6</v>
@@ -18241,11 +18240,11 @@
         <v>10</v>
       </c>
       <c r="D105" s="13"/>
-      <c r="E105" s="42">
+      <c r="E105" s="39">
         <f t="shared" si="11"/>
         <v>10.284360189573459</v>
       </c>
-      <c r="F105" s="43"/>
+      <c r="F105" s="40"/>
       <c r="I105" s="18">
         <f t="shared" si="9"/>
         <v>1.0000000000000001E-5</v>
@@ -18270,11 +18269,11 @@
         <v>25</v>
       </c>
       <c r="D106" s="33"/>
-      <c r="E106" s="42">
+      <c r="E106" s="39">
         <f t="shared" si="11"/>
         <v>24.976303317535546</v>
       </c>
-      <c r="F106" s="43"/>
+      <c r="F106" s="40"/>
       <c r="I106" s="19">
         <f t="shared" si="9"/>
         <v>2.5000000000000001E-5</v>
@@ -18299,11 +18298,11 @@
         <v>50</v>
       </c>
       <c r="D107" s="15"/>
-      <c r="E107" s="44">
+      <c r="E107" s="53">
         <f t="shared" si="11"/>
         <v>78.436018957345965</v>
       </c>
-      <c r="F107" s="45"/>
+      <c r="F107" s="54"/>
       <c r="I107" s="18">
         <f t="shared" si="9"/>
         <v>5.0000000000000002E-5</v>
@@ -18324,13 +18323,13 @@
       <c r="B108" s="9">
         <v>0</v>
       </c>
-      <c r="C108" s="52"/>
-      <c r="D108" s="53"/>
-      <c r="E108" s="54">
+      <c r="C108" s="49"/>
+      <c r="D108" s="50"/>
+      <c r="E108" s="55">
         <f t="shared" ref="E108:E115" si="13">(B108+0.001)/0.0211</f>
         <v>4.7393364928909949E-2</v>
       </c>
-      <c r="F108" s="54"/>
+      <c r="F108" s="55"/>
       <c r="I108" s="18">
         <f>E108/1000000</f>
         <v>4.7393364928909948E-8</v>
@@ -18351,13 +18350,13 @@
       <c r="B109" s="6">
         <v>0</v>
       </c>
-      <c r="C109" s="46"/>
-      <c r="D109" s="47"/>
-      <c r="E109" s="42">
+      <c r="C109" s="41"/>
+      <c r="D109" s="42"/>
+      <c r="E109" s="39">
         <f t="shared" si="13"/>
         <v>4.7393364928909949E-2</v>
       </c>
-      <c r="F109" s="42"/>
+      <c r="F109" s="39"/>
       <c r="I109" s="18">
         <f t="shared" ref="I109:I115" si="14">E109/1000000</f>
         <v>4.7393364928909948E-8</v>
@@ -18378,13 +18377,13 @@
       <c r="B110" s="6">
         <v>0</v>
       </c>
-      <c r="C110" s="46"/>
-      <c r="D110" s="47"/>
-      <c r="E110" s="42">
+      <c r="C110" s="41"/>
+      <c r="D110" s="42"/>
+      <c r="E110" s="39">
         <f t="shared" si="13"/>
         <v>4.7393364928909949E-2</v>
       </c>
-      <c r="F110" s="42"/>
+      <c r="F110" s="39"/>
       <c r="I110" s="18">
         <f t="shared" si="14"/>
         <v>4.7393364928909948E-8</v>
@@ -18405,13 +18404,13 @@
       <c r="B111" s="6">
         <v>0</v>
       </c>
-      <c r="C111" s="46"/>
-      <c r="D111" s="47"/>
-      <c r="E111" s="42">
+      <c r="C111" s="41"/>
+      <c r="D111" s="42"/>
+      <c r="E111" s="39">
         <f t="shared" si="13"/>
         <v>4.7393364928909949E-2</v>
       </c>
-      <c r="F111" s="42"/>
+      <c r="F111" s="39"/>
       <c r="I111" s="18">
         <f t="shared" si="14"/>
         <v>4.7393364928909948E-8</v>
@@ -18432,13 +18431,13 @@
       <c r="B112" s="6">
         <v>1.4E-2</v>
       </c>
-      <c r="C112" s="46"/>
-      <c r="D112" s="47"/>
-      <c r="E112" s="42">
+      <c r="C112" s="41"/>
+      <c r="D112" s="42"/>
+      <c r="E112" s="39">
         <f t="shared" si="13"/>
         <v>0.71090047393364919</v>
       </c>
-      <c r="F112" s="42"/>
+      <c r="F112" s="39"/>
       <c r="I112" s="18">
         <f t="shared" si="14"/>
         <v>7.1090047393364923E-7</v>
@@ -18459,13 +18458,13 @@
       <c r="B113" s="6">
         <v>8.9999999999999993E-3</v>
       </c>
-      <c r="C113" s="46"/>
-      <c r="D113" s="47"/>
-      <c r="E113" s="42">
+      <c r="C113" s="41"/>
+      <c r="D113" s="42"/>
+      <c r="E113" s="39">
         <f t="shared" si="13"/>
         <v>0.47393364928909942</v>
       </c>
-      <c r="F113" s="42"/>
+      <c r="F113" s="39"/>
       <c r="I113" s="18">
         <f t="shared" si="14"/>
         <v>4.7393364928909945E-7</v>
@@ -18486,13 +18485,13 @@
       <c r="B114" s="6">
         <v>3.9E-2</v>
       </c>
-      <c r="C114" s="46"/>
-      <c r="D114" s="47"/>
-      <c r="E114" s="42">
+      <c r="C114" s="41"/>
+      <c r="D114" s="42"/>
+      <c r="E114" s="39">
         <f t="shared" si="13"/>
         <v>1.8957345971563981</v>
       </c>
-      <c r="F114" s="42"/>
+      <c r="F114" s="39"/>
       <c r="I114" s="18">
         <f t="shared" si="14"/>
         <v>1.8957345971563982E-6</v>
@@ -18513,13 +18512,13 @@
       <c r="B115" s="6">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="C115" s="46"/>
-      <c r="D115" s="47"/>
-      <c r="E115" s="42">
+      <c r="C115" s="41"/>
+      <c r="D115" s="42"/>
+      <c r="E115" s="39">
         <f t="shared" si="13"/>
         <v>0.33175355450236965</v>
       </c>
-      <c r="F115" s="42"/>
+      <c r="F115" s="39"/>
       <c r="I115" s="18">
         <f t="shared" si="14"/>
         <v>3.3175355450236965E-7</v>
@@ -18537,16 +18536,16 @@
       <c r="H120" s="24"/>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A121" s="38" t="s">
+      <c r="A121" s="46" t="s">
         <v>27</v>
       </c>
-      <c r="B121" s="38"/>
-      <c r="C121" s="38"/>
-      <c r="D121" s="38"/>
-      <c r="E121" s="38"/>
-      <c r="F121" s="38"/>
-      <c r="G121" s="38"/>
-      <c r="H121" s="38"/>
+      <c r="B121" s="46"/>
+      <c r="C121" s="46"/>
+      <c r="D121" s="46"/>
+      <c r="E121" s="46"/>
+      <c r="F121" s="46"/>
+      <c r="G121" s="46"/>
+      <c r="H121" s="46"/>
     </row>
     <row r="123" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
@@ -18570,14 +18569,14 @@
         <v>56</v>
       </c>
       <c r="B124" s="4"/>
-      <c r="C124" s="63">
+      <c r="C124" s="56">
         <v>2.5</v>
       </c>
-      <c r="D124" s="64"/>
-      <c r="E124" s="55">
+      <c r="D124" s="57"/>
+      <c r="E124" s="51">
         <v>0</v>
       </c>
-      <c r="F124" s="56"/>
+      <c r="F124" s="52"/>
       <c r="G124" s="36"/>
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.25">
@@ -18585,15 +18584,15 @@
         <v>11</v>
       </c>
       <c r="B125" s="2"/>
-      <c r="C125" s="61">
+      <c r="C125" s="58">
         <v>5</v>
       </c>
-      <c r="D125" s="62"/>
-      <c r="E125" s="40">
+      <c r="D125" s="59"/>
+      <c r="E125" s="44">
         <f>(B125+0.0053)/0.0019</f>
         <v>2.7894736842105265</v>
       </c>
-      <c r="F125" s="41"/>
+      <c r="F125" s="45"/>
       <c r="G125" s="36"/>
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.25">
@@ -18603,15 +18602,15 @@
       <c r="B126" s="6">
         <v>2.3E-2</v>
       </c>
-      <c r="C126" s="46">
+      <c r="C126" s="41">
         <v>10</v>
       </c>
-      <c r="D126" s="60"/>
-      <c r="E126" s="40">
+      <c r="D126" s="43"/>
+      <c r="E126" s="44">
         <f t="shared" ref="E126:E131" si="17">(B126+0.0053)/0.0019</f>
         <v>14.894736842105262</v>
       </c>
-      <c r="F126" s="41"/>
+      <c r="F126" s="45"/>
       <c r="G126" s="36"/>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.25">
@@ -18619,15 +18618,15 @@
         <v>12</v>
       </c>
       <c r="B127" s="6"/>
-      <c r="C127" s="46">
+      <c r="C127" s="41">
         <v>25</v>
       </c>
-      <c r="D127" s="60"/>
-      <c r="E127" s="40">
+      <c r="D127" s="43"/>
+      <c r="E127" s="44">
         <f t="shared" si="17"/>
         <v>2.7894736842105265</v>
       </c>
-      <c r="F127" s="41"/>
+      <c r="F127" s="45"/>
       <c r="G127" s="36"/>
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.25">
@@ -18637,15 +18636,15 @@
       <c r="B128" s="6">
         <v>9.6000000000000002E-2</v>
       </c>
-      <c r="C128" s="46">
+      <c r="C128" s="41">
         <v>50</v>
       </c>
-      <c r="D128" s="60"/>
-      <c r="E128" s="40">
+      <c r="D128" s="43"/>
+      <c r="E128" s="44">
         <f t="shared" si="17"/>
         <v>53.315789473684212</v>
       </c>
-      <c r="F128" s="41"/>
+      <c r="F128" s="45"/>
       <c r="G128" s="36"/>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
@@ -18655,15 +18654,15 @@
       <c r="B129" s="6">
         <v>0.20499999999999999</v>
       </c>
-      <c r="C129" s="46">
+      <c r="C129" s="41">
         <v>100</v>
       </c>
-      <c r="D129" s="60"/>
-      <c r="E129" s="40">
+      <c r="D129" s="43"/>
+      <c r="E129" s="44">
         <f t="shared" si="17"/>
         <v>110.68421052631578</v>
       </c>
-      <c r="F129" s="41"/>
+      <c r="F129" s="45"/>
       <c r="G129" s="36"/>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
@@ -18673,15 +18672,15 @@
       <c r="B130" s="6">
         <v>0.39500000000000002</v>
       </c>
-      <c r="C130" s="46">
+      <c r="C130" s="41">
         <v>200</v>
       </c>
-      <c r="D130" s="60"/>
-      <c r="E130" s="40">
+      <c r="D130" s="43"/>
+      <c r="E130" s="44">
         <f t="shared" si="17"/>
         <v>210.68421052631581</v>
       </c>
-      <c r="F130" s="41"/>
+      <c r="F130" s="45"/>
       <c r="G130" s="36"/>
     </row>
     <row r="131" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -18691,15 +18690,15 @@
       <c r="B131" s="8">
         <v>0.97</v>
       </c>
-      <c r="C131" s="48">
+      <c r="C131" s="47">
         <v>500</v>
       </c>
-      <c r="D131" s="49"/>
-      <c r="E131" s="50">
+      <c r="D131" s="48"/>
+      <c r="E131" s="62">
         <f t="shared" si="17"/>
         <v>513.31578947368416</v>
       </c>
-      <c r="F131" s="51"/>
+      <c r="F131" s="63"/>
       <c r="G131" s="36"/>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
@@ -18709,13 +18708,13 @@
       <c r="B132" s="9">
         <v>1.4E-2</v>
       </c>
-      <c r="C132" s="52"/>
-      <c r="D132" s="57"/>
-      <c r="E132" s="67">
+      <c r="C132" s="49"/>
+      <c r="D132" s="60"/>
+      <c r="E132" s="66">
         <f t="shared" ref="E132" si="18">(B132+0.0053)/0.0019</f>
         <v>10.157894736842106</v>
       </c>
-      <c r="F132" s="68"/>
+      <c r="F132" s="67"/>
       <c r="G132" s="36"/>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
@@ -18725,13 +18724,13 @@
       <c r="B133" s="6">
         <v>8.9999999999999993E-3</v>
       </c>
-      <c r="C133" s="46"/>
-      <c r="D133" s="60"/>
-      <c r="E133" s="40">
+      <c r="C133" s="41"/>
+      <c r="D133" s="43"/>
+      <c r="E133" s="44">
         <f t="shared" ref="E133" si="19">(B133+0.0053)/0.0019</f>
         <v>7.5263157894736841</v>
       </c>
-      <c r="F133" s="41"/>
+      <c r="F133" s="45"/>
       <c r="G133" s="36"/>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
@@ -18741,13 +18740,13 @@
       <c r="B134" s="6">
         <v>2E-3</v>
       </c>
-      <c r="C134" s="46"/>
-      <c r="D134" s="60"/>
-      <c r="E134" s="40">
+      <c r="C134" s="41"/>
+      <c r="D134" s="43"/>
+      <c r="E134" s="44">
         <f t="shared" ref="E134:E139" si="20">(B134+0.0053)/0.0019</f>
         <v>3.8421052631578947</v>
       </c>
-      <c r="F134" s="41"/>
+      <c r="F134" s="45"/>
       <c r="G134" s="36"/>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
@@ -18757,13 +18756,13 @@
       <c r="B135" s="6">
         <v>0</v>
       </c>
-      <c r="C135" s="46"/>
-      <c r="D135" s="60"/>
-      <c r="E135" s="40">
+      <c r="C135" s="41"/>
+      <c r="D135" s="43"/>
+      <c r="E135" s="44">
         <f t="shared" si="20"/>
         <v>2.7894736842105265</v>
       </c>
-      <c r="F135" s="41"/>
+      <c r="F135" s="45"/>
       <c r="G135" s="36"/>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
@@ -18773,13 +18772,13 @@
       <c r="B136" s="6">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="C136" s="46"/>
-      <c r="D136" s="60"/>
-      <c r="E136" s="40">
+      <c r="C136" s="41"/>
+      <c r="D136" s="43"/>
+      <c r="E136" s="44">
         <f t="shared" si="20"/>
         <v>5.9473684210526319</v>
       </c>
-      <c r="F136" s="41"/>
+      <c r="F136" s="45"/>
       <c r="G136" s="36"/>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
@@ -18789,13 +18788,13 @@
       <c r="B137" s="6">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="C137" s="46"/>
-      <c r="D137" s="60"/>
-      <c r="E137" s="40">
+      <c r="C137" s="41"/>
+      <c r="D137" s="43"/>
+      <c r="E137" s="44">
         <f t="shared" si="20"/>
         <v>15.947368421052632</v>
       </c>
-      <c r="F137" s="41"/>
+      <c r="F137" s="45"/>
       <c r="G137" s="36"/>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
@@ -18805,13 +18804,13 @@
       <c r="B138" s="6">
         <v>1.2999999999999999E-2</v>
       </c>
-      <c r="C138" s="46"/>
-      <c r="D138" s="60"/>
-      <c r="E138" s="40">
+      <c r="C138" s="41"/>
+      <c r="D138" s="43"/>
+      <c r="E138" s="44">
         <f t="shared" si="20"/>
         <v>9.6315789473684212</v>
       </c>
-      <c r="F138" s="41"/>
+      <c r="F138" s="45"/>
       <c r="G138" s="36"/>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
@@ -18821,43 +18820,66 @@
       <c r="B139" s="6">
         <v>1.4E-2</v>
       </c>
-      <c r="C139" s="46"/>
-      <c r="D139" s="60"/>
-      <c r="E139" s="40">
+      <c r="C139" s="41"/>
+      <c r="D139" s="43"/>
+      <c r="E139" s="44">
         <f t="shared" si="20"/>
         <v>10.157894736842106</v>
       </c>
-      <c r="F139" s="41"/>
+      <c r="F139" s="45"/>
       <c r="G139" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="88">
-    <mergeCell ref="C139:D139"/>
-    <mergeCell ref="E139:F139"/>
-    <mergeCell ref="C136:D136"/>
-    <mergeCell ref="E136:F136"/>
-    <mergeCell ref="C137:D137"/>
-    <mergeCell ref="E137:F137"/>
-    <mergeCell ref="C138:D138"/>
-    <mergeCell ref="E138:F138"/>
-    <mergeCell ref="C133:D133"/>
-    <mergeCell ref="E133:F133"/>
-    <mergeCell ref="C134:D134"/>
-    <mergeCell ref="E134:F134"/>
-    <mergeCell ref="C135:D135"/>
-    <mergeCell ref="E135:F135"/>
-    <mergeCell ref="C130:D130"/>
-    <mergeCell ref="E130:F130"/>
-    <mergeCell ref="C131:D131"/>
-    <mergeCell ref="E131:F131"/>
-    <mergeCell ref="C132:D132"/>
-    <mergeCell ref="E132:F132"/>
-    <mergeCell ref="C127:D127"/>
-    <mergeCell ref="E127:F127"/>
-    <mergeCell ref="C128:D128"/>
-    <mergeCell ref="E128:F128"/>
-    <mergeCell ref="C129:D129"/>
-    <mergeCell ref="E129:F129"/>
+    <mergeCell ref="C58:D58"/>
+    <mergeCell ref="E58:F58"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="C56:D56"/>
+    <mergeCell ref="E56:F56"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="C59:D59"/>
+    <mergeCell ref="E59:F59"/>
+    <mergeCell ref="C60:D60"/>
+    <mergeCell ref="E60:F60"/>
+    <mergeCell ref="C61:D61"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="E62:F62"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="E63:F63"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="E64:F64"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="E65:F65"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="E66:F66"/>
+    <mergeCell ref="C67:D67"/>
+    <mergeCell ref="E67:F67"/>
+    <mergeCell ref="E105:F105"/>
+    <mergeCell ref="C68:D68"/>
+    <mergeCell ref="E68:F68"/>
+    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="E69:F69"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="E70:F70"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="E71:F71"/>
+    <mergeCell ref="E102:F102"/>
+    <mergeCell ref="E103:F103"/>
+    <mergeCell ref="E104:F104"/>
+    <mergeCell ref="E106:F106"/>
+    <mergeCell ref="E107:F107"/>
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="E108:F108"/>
+    <mergeCell ref="C109:D109"/>
+    <mergeCell ref="E109:F109"/>
+    <mergeCell ref="C110:D110"/>
+    <mergeCell ref="E110:F110"/>
+    <mergeCell ref="C111:D111"/>
+    <mergeCell ref="E111:F111"/>
+    <mergeCell ref="C112:D112"/>
+    <mergeCell ref="E112:F112"/>
     <mergeCell ref="C126:D126"/>
     <mergeCell ref="E126:F126"/>
     <mergeCell ref="C113:D113"/>
@@ -18871,55 +18893,32 @@
     <mergeCell ref="E124:F124"/>
     <mergeCell ref="C125:D125"/>
     <mergeCell ref="E125:F125"/>
-    <mergeCell ref="C110:D110"/>
-    <mergeCell ref="E110:F110"/>
-    <mergeCell ref="C111:D111"/>
-    <mergeCell ref="E111:F111"/>
-    <mergeCell ref="C112:D112"/>
-    <mergeCell ref="E112:F112"/>
-    <mergeCell ref="E106:F106"/>
-    <mergeCell ref="E107:F107"/>
-    <mergeCell ref="C108:D108"/>
-    <mergeCell ref="E108:F108"/>
-    <mergeCell ref="C109:D109"/>
-    <mergeCell ref="E109:F109"/>
-    <mergeCell ref="E105:F105"/>
-    <mergeCell ref="C68:D68"/>
-    <mergeCell ref="E68:F68"/>
-    <mergeCell ref="C69:D69"/>
-    <mergeCell ref="E69:F69"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="E70:F70"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="E71:F71"/>
-    <mergeCell ref="E102:F102"/>
-    <mergeCell ref="E103:F103"/>
-    <mergeCell ref="E104:F104"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="E65:F65"/>
-    <mergeCell ref="C66:D66"/>
-    <mergeCell ref="E66:F66"/>
-    <mergeCell ref="C67:D67"/>
-    <mergeCell ref="E67:F67"/>
-    <mergeCell ref="C62:D62"/>
-    <mergeCell ref="E62:F62"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="E63:F63"/>
-    <mergeCell ref="C64:D64"/>
-    <mergeCell ref="E64:F64"/>
-    <mergeCell ref="C59:D59"/>
-    <mergeCell ref="E59:F59"/>
-    <mergeCell ref="C60:D60"/>
-    <mergeCell ref="E60:F60"/>
-    <mergeCell ref="C61:D61"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="C58:D58"/>
-    <mergeCell ref="E58:F58"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="C56:D56"/>
-    <mergeCell ref="E56:F56"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="C127:D127"/>
+    <mergeCell ref="E127:F127"/>
+    <mergeCell ref="C128:D128"/>
+    <mergeCell ref="E128:F128"/>
+    <mergeCell ref="C129:D129"/>
+    <mergeCell ref="E129:F129"/>
+    <mergeCell ref="C130:D130"/>
+    <mergeCell ref="E130:F130"/>
+    <mergeCell ref="C131:D131"/>
+    <mergeCell ref="E131:F131"/>
+    <mergeCell ref="C132:D132"/>
+    <mergeCell ref="E132:F132"/>
+    <mergeCell ref="C133:D133"/>
+    <mergeCell ref="E133:F133"/>
+    <mergeCell ref="C134:D134"/>
+    <mergeCell ref="E134:F134"/>
+    <mergeCell ref="C135:D135"/>
+    <mergeCell ref="E135:F135"/>
+    <mergeCell ref="C139:D139"/>
+    <mergeCell ref="E139:F139"/>
+    <mergeCell ref="C136:D136"/>
+    <mergeCell ref="E136:F136"/>
+    <mergeCell ref="C137:D137"/>
+    <mergeCell ref="E137:F137"/>
+    <mergeCell ref="C138:D138"/>
+    <mergeCell ref="E138:F138"/>
   </mergeCells>
   <pageMargins left="0.11458333333333333" right="1.0416666666666666E-2" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -18942,16 +18941,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="46" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
       <c r="I1" s="1"/>
     </row>
     <row r="2" spans="1:9" s="25" customFormat="1" x14ac:dyDescent="0.25">
@@ -19166,14 +19165,14 @@
       <c r="B57" s="6">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="C57" s="39">
+      <c r="C57" s="38">
         <v>1</v>
       </c>
-      <c r="D57" s="39"/>
-      <c r="E57" s="42">
+      <c r="D57" s="38"/>
+      <c r="E57" s="39">
         <v>0</v>
       </c>
-      <c r="F57" s="43"/>
+      <c r="F57" s="40"/>
       <c r="H57" s="18"/>
       <c r="I57" s="27"/>
       <c r="J57" s="18"/>
@@ -19185,15 +19184,15 @@
       <c r="B58" s="6">
         <v>1.7999999999999999E-2</v>
       </c>
-      <c r="C58" s="39">
+      <c r="C58" s="38">
         <v>2.5</v>
       </c>
-      <c r="D58" s="39"/>
-      <c r="E58" s="42">
+      <c r="D58" s="38"/>
+      <c r="E58" s="39">
         <f>(B58-0.0099)/0.0098</f>
         <v>0.82653061224489777</v>
       </c>
-      <c r="F58" s="43"/>
+      <c r="F58" s="40"/>
       <c r="H58" s="18"/>
       <c r="I58" s="27"/>
       <c r="J58" s="18"/>
@@ -19205,15 +19204,15 @@
       <c r="B59" s="6">
         <v>4.2999999999999997E-2</v>
       </c>
-      <c r="C59" s="39">
+      <c r="C59" s="38">
         <v>5</v>
       </c>
-      <c r="D59" s="39"/>
-      <c r="E59" s="42">
+      <c r="D59" s="38"/>
+      <c r="E59" s="39">
         <f t="shared" ref="E59:E64" si="0">(B59-0.0099)/0.0098</f>
         <v>3.3775510204081631</v>
       </c>
-      <c r="F59" s="43"/>
+      <c r="F59" s="40"/>
       <c r="H59" s="18">
         <f>C59/1000000</f>
         <v>5.0000000000000004E-6</v>
@@ -19234,15 +19233,15 @@
       <c r="B60" s="6">
         <v>9.4E-2</v>
       </c>
-      <c r="C60" s="39">
+      <c r="C60" s="38">
         <v>10</v>
       </c>
-      <c r="D60" s="39"/>
-      <c r="E60" s="42">
+      <c r="D60" s="38"/>
+      <c r="E60" s="39">
         <f t="shared" si="0"/>
         <v>8.5816326530612237</v>
       </c>
-      <c r="F60" s="43"/>
+      <c r="F60" s="40"/>
       <c r="H60" s="18">
         <f>C60/1000000</f>
         <v>1.0000000000000001E-5</v>
@@ -19263,15 +19262,15 @@
       <c r="B61" s="6">
         <v>0.25</v>
       </c>
-      <c r="C61" s="39">
+      <c r="C61" s="38">
         <v>25</v>
       </c>
-      <c r="D61" s="39"/>
-      <c r="E61" s="42">
+      <c r="D61" s="38"/>
+      <c r="E61" s="39">
         <f t="shared" si="0"/>
         <v>24.5</v>
       </c>
-      <c r="F61" s="43"/>
+      <c r="F61" s="40"/>
       <c r="H61" s="18"/>
       <c r="I61" s="18"/>
       <c r="J61" s="21"/>
@@ -19283,15 +19282,15 @@
       <c r="B62" s="6">
         <v>0.52</v>
       </c>
-      <c r="C62" s="39">
+      <c r="C62" s="38">
         <v>50</v>
       </c>
-      <c r="D62" s="39"/>
-      <c r="E62" s="42">
+      <c r="D62" s="38"/>
+      <c r="E62" s="39">
         <f t="shared" si="0"/>
         <v>52.051020408163268</v>
       </c>
-      <c r="F62" s="43"/>
+      <c r="F62" s="40"/>
       <c r="H62" s="18">
         <f>C62/1000000</f>
         <v>5.0000000000000002E-5</v>
@@ -19312,15 +19311,15 @@
       <c r="B63" s="6">
         <v>1.028</v>
       </c>
-      <c r="C63" s="39">
+      <c r="C63" s="38">
         <v>100</v>
       </c>
-      <c r="D63" s="39"/>
-      <c r="E63" s="42">
+      <c r="D63" s="38"/>
+      <c r="E63" s="39">
         <f t="shared" si="0"/>
         <v>103.88775510204081</v>
       </c>
-      <c r="F63" s="43"/>
+      <c r="F63" s="40"/>
       <c r="H63" s="18">
         <f>C63/1000000</f>
         <v>1E-4</v>
@@ -19341,15 +19340,15 @@
       <c r="B64" s="8">
         <v>1.95</v>
       </c>
-      <c r="C64" s="48">
+      <c r="C64" s="47">
         <v>200</v>
       </c>
-      <c r="D64" s="49"/>
-      <c r="E64" s="42">
+      <c r="D64" s="48"/>
+      <c r="E64" s="39">
         <f t="shared" si="0"/>
         <v>197.96938775510205</v>
       </c>
-      <c r="F64" s="43"/>
+      <c r="F64" s="40"/>
       <c r="H64" s="19">
         <f>C64/1000000</f>
         <v>2.0000000000000001E-4</v>
@@ -19370,15 +19369,15 @@
       <c r="B65" s="9">
         <v>0.224</v>
       </c>
-      <c r="C65" s="52"/>
-      <c r="D65" s="53"/>
-      <c r="E65" s="42">
+      <c r="C65" s="49"/>
+      <c r="D65" s="50"/>
+      <c r="E65" s="39">
         <f t="shared" ref="E65:E73" si="3">(B65-0.0099)/0.0098</f>
         <v>21.846938775510207</v>
       </c>
-      <c r="F65" s="43"/>
+      <c r="F65" s="40"/>
       <c r="H65" s="18">
-        <f t="shared" ref="H65:H72" si="4">E65/1000000</f>
+        <f t="shared" ref="H65:H73" si="4">E65/1000000</f>
         <v>2.1846938775510207E-5</v>
       </c>
       <c r="I65" s="18">
@@ -19397,23 +19396,23 @@
       <c r="B66" s="6">
         <v>2.9000000000000001E-2</v>
       </c>
-      <c r="C66" s="46"/>
-      <c r="D66" s="47"/>
-      <c r="E66" s="42">
+      <c r="C66" s="41"/>
+      <c r="D66" s="42"/>
+      <c r="E66" s="39">
         <f t="shared" si="3"/>
         <v>1.9489795918367347</v>
       </c>
-      <c r="F66" s="43"/>
+      <c r="F66" s="40"/>
       <c r="H66" s="18">
         <f t="shared" si="4"/>
         <v>1.9489795918367348E-6</v>
       </c>
       <c r="I66" s="18">
-        <f t="shared" ref="I66:I72" si="5">$J$51*H66*$J$52</f>
+        <f t="shared" ref="I66:I73" si="5">$J$51*H66*$J$52</f>
         <v>3.515659040816327E-8</v>
       </c>
       <c r="J66" s="21">
-        <f t="shared" ref="J66:J72" si="6">I66*1000000</f>
+        <f t="shared" ref="J66:J73" si="6">I66*1000000</f>
         <v>3.5156590408163269E-2</v>
       </c>
     </row>
@@ -19424,13 +19423,13 @@
       <c r="B67" s="6">
         <v>2.4E-2</v>
       </c>
-      <c r="C67" s="46"/>
-      <c r="D67" s="47"/>
-      <c r="E67" s="42">
+      <c r="C67" s="41"/>
+      <c r="D67" s="42"/>
+      <c r="E67" s="39">
         <f t="shared" si="3"/>
         <v>1.4387755102040816</v>
       </c>
-      <c r="F67" s="43"/>
+      <c r="F67" s="40"/>
       <c r="H67" s="18">
         <f t="shared" si="4"/>
         <v>1.4387755102040816E-6</v>
@@ -19451,13 +19450,13 @@
       <c r="B68" s="6">
         <v>7.9000000000000001E-2</v>
       </c>
-      <c r="C68" s="46"/>
-      <c r="D68" s="47"/>
-      <c r="E68" s="42">
+      <c r="C68" s="41"/>
+      <c r="D68" s="42"/>
+      <c r="E68" s="39">
         <f t="shared" si="3"/>
         <v>7.0510204081632653</v>
       </c>
-      <c r="F68" s="43"/>
+      <c r="F68" s="40"/>
       <c r="H68" s="18">
         <f t="shared" si="4"/>
         <v>7.051020408163265E-6</v>
@@ -19478,13 +19477,13 @@
       <c r="B69" s="6">
         <v>4.1000000000000002E-2</v>
       </c>
-      <c r="C69" s="46"/>
-      <c r="D69" s="47"/>
-      <c r="E69" s="42">
+      <c r="C69" s="41"/>
+      <c r="D69" s="42"/>
+      <c r="E69" s="39">
         <f t="shared" si="3"/>
         <v>3.1734693877551026</v>
       </c>
-      <c r="F69" s="43"/>
+      <c r="F69" s="40"/>
       <c r="H69" s="18">
         <f t="shared" si="4"/>
         <v>3.1734693877551026E-6</v>
@@ -19505,13 +19504,13 @@
       <c r="B70" s="6">
         <v>0.224</v>
       </c>
-      <c r="C70" s="46"/>
-      <c r="D70" s="47"/>
-      <c r="E70" s="42">
+      <c r="C70" s="41"/>
+      <c r="D70" s="42"/>
+      <c r="E70" s="39">
         <f t="shared" si="3"/>
         <v>21.846938775510207</v>
       </c>
-      <c r="F70" s="43"/>
+      <c r="F70" s="40"/>
       <c r="H70" s="18">
         <f t="shared" si="4"/>
         <v>2.1846938775510207E-5</v>
@@ -19532,13 +19531,13 @@
       <c r="B71" s="6">
         <v>0.221</v>
       </c>
-      <c r="C71" s="46"/>
-      <c r="D71" s="47"/>
-      <c r="E71" s="42">
+      <c r="C71" s="41"/>
+      <c r="D71" s="42"/>
+      <c r="E71" s="39">
         <f t="shared" si="3"/>
         <v>21.540816326530614</v>
       </c>
-      <c r="F71" s="43"/>
+      <c r="F71" s="40"/>
       <c r="H71" s="18">
         <f t="shared" si="4"/>
         <v>2.1540816326530614E-5</v>
@@ -19559,13 +19558,13 @@
       <c r="B72" s="6">
         <v>0.11700000000000001</v>
       </c>
-      <c r="C72" s="46"/>
-      <c r="D72" s="47"/>
-      <c r="E72" s="42">
+      <c r="C72" s="41"/>
+      <c r="D72" s="42"/>
+      <c r="E72" s="39">
         <f t="shared" si="3"/>
         <v>10.928571428571429</v>
       </c>
-      <c r="F72" s="43"/>
+      <c r="F72" s="40"/>
       <c r="H72" s="18">
         <f t="shared" si="4"/>
         <v>1.0928571428571429E-5</v>
@@ -19586,13 +19585,25 @@
       <c r="B73" s="6">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="C73" s="46"/>
-      <c r="D73" s="47"/>
-      <c r="E73" s="42">
+      <c r="C73" s="41"/>
+      <c r="D73" s="42"/>
+      <c r="E73" s="39">
         <f t="shared" si="3"/>
         <v>2.5612244897959191</v>
       </c>
-      <c r="F73" s="43"/>
+      <c r="F73" s="40"/>
+      <c r="H73" s="18">
+        <f t="shared" si="4"/>
+        <v>2.5612244897959191E-6</v>
+      </c>
+      <c r="I73" s="18">
+        <f t="shared" si="5"/>
+        <v>4.6200545510204097E-8</v>
+      </c>
+      <c r="J73" s="21">
+        <f t="shared" si="6"/>
+        <v>4.6200545510204097E-2</v>
+      </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
       <c r="I98" t="s">
@@ -19666,11 +19677,11 @@
         <v>0.5</v>
       </c>
       <c r="D103" s="11"/>
-      <c r="E103" s="55">
+      <c r="E103" s="51">
         <f>(B103+0.001)/0.0201</f>
         <v>4.975124378109453E-2</v>
       </c>
-      <c r="F103" s="56"/>
+      <c r="F103" s="52"/>
       <c r="I103" s="16">
         <f t="shared" ref="I103:I108" si="7">C103/1000000</f>
         <v>4.9999999999999998E-7</v>
@@ -19695,11 +19706,11 @@
         <v>1</v>
       </c>
       <c r="D104" s="13"/>
-      <c r="E104" s="42">
+      <c r="E104" s="39">
         <f t="shared" ref="E104:E108" si="9">(B104+0.001)/0.0201</f>
         <v>0.54726368159203975</v>
       </c>
-      <c r="F104" s="43"/>
+      <c r="F104" s="40"/>
       <c r="I104" s="18">
         <f t="shared" si="7"/>
         <v>9.9999999999999995E-7</v>
@@ -19724,11 +19735,11 @@
         <v>5</v>
       </c>
       <c r="D105" s="13"/>
-      <c r="E105" s="42">
+      <c r="E105" s="39">
         <f t="shared" si="9"/>
         <v>4.1293532338308463</v>
       </c>
-      <c r="F105" s="43"/>
+      <c r="F105" s="40"/>
       <c r="I105" s="18">
         <f t="shared" si="7"/>
         <v>5.0000000000000004E-6</v>
@@ -19753,11 +19764,11 @@
         <v>10</v>
       </c>
       <c r="D106" s="13"/>
-      <c r="E106" s="42">
+      <c r="E106" s="39">
         <f t="shared" si="9"/>
         <v>10.149253731343284</v>
       </c>
-      <c r="F106" s="43"/>
+      <c r="F106" s="40"/>
       <c r="I106" s="18">
         <f t="shared" si="7"/>
         <v>1.0000000000000001E-5</v>
@@ -19782,11 +19793,11 @@
         <v>25</v>
       </c>
       <c r="D107" s="33"/>
-      <c r="E107" s="42">
+      <c r="E107" s="39">
         <f t="shared" si="9"/>
         <v>24.427860696517413</v>
       </c>
-      <c r="F107" s="43"/>
+      <c r="F107" s="40"/>
       <c r="I107" s="19">
         <f t="shared" si="7"/>
         <v>2.5000000000000001E-5</v>
@@ -19809,11 +19820,11 @@
         <v>50</v>
       </c>
       <c r="D108" s="15"/>
-      <c r="E108" s="44">
+      <c r="E108" s="53">
         <f t="shared" si="9"/>
         <v>4.975124378109453E-2</v>
       </c>
-      <c r="F108" s="45"/>
+      <c r="F108" s="54"/>
       <c r="I108" s="18">
         <f t="shared" si="7"/>
         <v>5.0000000000000002E-5</v>
@@ -19834,13 +19845,13 @@
       <c r="B109" s="9">
         <v>0</v>
       </c>
-      <c r="C109" s="52"/>
-      <c r="D109" s="53"/>
-      <c r="E109" s="54">
+      <c r="C109" s="49"/>
+      <c r="D109" s="50"/>
+      <c r="E109" s="55">
         <f t="shared" ref="E109" si="11">(B109+0.001)/0.0201</f>
         <v>4.975124378109453E-2</v>
       </c>
-      <c r="F109" s="54"/>
+      <c r="F109" s="55"/>
       <c r="I109" s="18">
         <f>E109/1000000</f>
         <v>4.9751243781094531E-8</v>
@@ -19861,19 +19872,19 @@
       <c r="B110" s="6">
         <v>0</v>
       </c>
-      <c r="C110" s="46"/>
-      <c r="D110" s="47"/>
-      <c r="E110" s="42">
+      <c r="C110" s="41"/>
+      <c r="D110" s="42"/>
+      <c r="E110" s="39">
         <f t="shared" ref="E110:E117" si="12">(B110+0.001)/0.0201</f>
         <v>4.975124378109453E-2</v>
       </c>
-      <c r="F110" s="42"/>
+      <c r="F110" s="39"/>
       <c r="I110" s="18">
-        <f t="shared" ref="I110:I116" si="13">E110/1000000</f>
+        <f t="shared" ref="I110:I117" si="13">E110/1000000</f>
         <v>4.9751243781094531E-8</v>
       </c>
       <c r="J110" s="18">
-        <f t="shared" ref="J110:J116" si="14">$J$51*I110*$J$52</f>
+        <f t="shared" ref="J110:J117" si="14">$J$51*I110*$J$52</f>
         <v>8.9743582089552253E-10</v>
       </c>
       <c r="K110" s="21">
@@ -19888,13 +19899,13 @@
       <c r="B111" s="6">
         <v>0</v>
       </c>
-      <c r="C111" s="46"/>
-      <c r="D111" s="47"/>
-      <c r="E111" s="42">
+      <c r="C111" s="41"/>
+      <c r="D111" s="42"/>
+      <c r="E111" s="39">
         <f t="shared" si="12"/>
         <v>4.975124378109453E-2</v>
       </c>
-      <c r="F111" s="42"/>
+      <c r="F111" s="39"/>
       <c r="I111" s="18">
         <f t="shared" si="13"/>
         <v>4.9751243781094531E-8</v>
@@ -19904,7 +19915,7 @@
         <v>8.9743582089552253E-10</v>
       </c>
       <c r="K111" s="21">
-        <f t="shared" ref="K111:K116" si="15">J111*1000000</f>
+        <f t="shared" ref="K111:K117" si="15">J111*1000000</f>
         <v>8.9743582089552249E-4</v>
       </c>
     </row>
@@ -19915,13 +19926,13 @@
       <c r="B112" s="6">
         <v>0</v>
       </c>
-      <c r="C112" s="46"/>
-      <c r="D112" s="47"/>
-      <c r="E112" s="42">
+      <c r="C112" s="41"/>
+      <c r="D112" s="42"/>
+      <c r="E112" s="39">
         <f t="shared" si="12"/>
         <v>4.975124378109453E-2</v>
       </c>
-      <c r="F112" s="42"/>
+      <c r="F112" s="39"/>
       <c r="I112" s="18">
         <f t="shared" si="13"/>
         <v>4.9751243781094531E-8</v>
@@ -19942,13 +19953,13 @@
       <c r="B113" s="6">
         <v>0</v>
       </c>
-      <c r="C113" s="46"/>
-      <c r="D113" s="47"/>
-      <c r="E113" s="42">
+      <c r="C113" s="41"/>
+      <c r="D113" s="42"/>
+      <c r="E113" s="39">
         <f t="shared" si="12"/>
         <v>4.975124378109453E-2</v>
       </c>
-      <c r="F113" s="42"/>
+      <c r="F113" s="39"/>
       <c r="I113" s="18">
         <f t="shared" si="13"/>
         <v>4.9751243781094531E-8</v>
@@ -19969,13 +19980,13 @@
       <c r="B114" s="6">
         <v>2E-3</v>
       </c>
-      <c r="C114" s="46"/>
-      <c r="D114" s="47"/>
-      <c r="E114" s="42">
+      <c r="C114" s="41"/>
+      <c r="D114" s="42"/>
+      <c r="E114" s="39">
         <f t="shared" si="12"/>
         <v>0.1492537313432836</v>
       </c>
-      <c r="F114" s="42"/>
+      <c r="F114" s="39"/>
       <c r="I114" s="18">
         <f t="shared" si="13"/>
         <v>1.492537313432836E-7</v>
@@ -19996,13 +20007,13 @@
       <c r="B115" s="6">
         <v>0.01</v>
       </c>
-      <c r="C115" s="46"/>
-      <c r="D115" s="47"/>
-      <c r="E115" s="42">
+      <c r="C115" s="41"/>
+      <c r="D115" s="42"/>
+      <c r="E115" s="39">
         <f t="shared" si="12"/>
         <v>0.54726368159203975</v>
       </c>
-      <c r="F115" s="42"/>
+      <c r="F115" s="39"/>
       <c r="I115" s="18">
         <f t="shared" si="13"/>
         <v>5.4726368159203972E-7</v>
@@ -20023,13 +20034,13 @@
       <c r="B116" s="6">
         <v>0</v>
       </c>
-      <c r="C116" s="46"/>
-      <c r="D116" s="47"/>
-      <c r="E116" s="42">
+      <c r="C116" s="41"/>
+      <c r="D116" s="42"/>
+      <c r="E116" s="39">
         <f t="shared" si="12"/>
         <v>4.975124378109453E-2</v>
       </c>
-      <c r="F116" s="42"/>
+      <c r="F116" s="39"/>
       <c r="I116" s="18">
         <f t="shared" si="13"/>
         <v>4.9751243781094531E-8</v>
@@ -20047,31 +20058,43 @@
       <c r="A117" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="B117" s="69">
+      <c r="B117" s="6">
         <v>0</v>
       </c>
-      <c r="C117" s="46"/>
-      <c r="D117" s="47"/>
-      <c r="E117" s="42">
+      <c r="C117" s="41"/>
+      <c r="D117" s="42"/>
+      <c r="E117" s="39">
         <f t="shared" si="12"/>
         <v>4.975124378109453E-2</v>
       </c>
-      <c r="F117" s="42"/>
+      <c r="F117" s="39"/>
+      <c r="I117" s="18">
+        <f t="shared" si="13"/>
+        <v>4.9751243781094531E-8</v>
+      </c>
+      <c r="J117" s="18">
+        <f t="shared" si="14"/>
+        <v>8.9743582089552253E-10</v>
+      </c>
+      <c r="K117" s="21">
+        <f t="shared" si="15"/>
+        <v>8.9743582089552249E-4</v>
+      </c>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.25">
       <c r="H121" s="24"/>
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A122" s="38" t="s">
+      <c r="A122" s="46" t="s">
         <v>27</v>
       </c>
-      <c r="B122" s="38"/>
-      <c r="C122" s="38"/>
-      <c r="D122" s="38"/>
-      <c r="E122" s="38"/>
-      <c r="F122" s="38"/>
-      <c r="G122" s="38"/>
-      <c r="H122" s="38"/>
+      <c r="B122" s="46"/>
+      <c r="C122" s="46"/>
+      <c r="D122" s="46"/>
+      <c r="E122" s="46"/>
+      <c r="F122" s="46"/>
+      <c r="G122" s="46"/>
+      <c r="H122" s="46"/>
     </row>
     <row r="124" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
@@ -20095,14 +20118,14 @@
         <v>56</v>
       </c>
       <c r="B125" s="4"/>
-      <c r="C125" s="63">
+      <c r="C125" s="56">
         <v>2.5</v>
       </c>
-      <c r="D125" s="64"/>
-      <c r="E125" s="55">
+      <c r="D125" s="57"/>
+      <c r="E125" s="51">
         <v>0</v>
       </c>
-      <c r="F125" s="56"/>
+      <c r="F125" s="52"/>
       <c r="G125" s="36"/>
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.25">
@@ -20110,15 +20133,15 @@
         <v>11</v>
       </c>
       <c r="B126" s="2"/>
-      <c r="C126" s="61">
+      <c r="C126" s="58">
         <v>5</v>
       </c>
-      <c r="D126" s="62"/>
-      <c r="E126" s="40">
+      <c r="D126" s="59"/>
+      <c r="E126" s="44">
         <f>(B126-0.0011)/0.0019</f>
         <v>-0.57894736842105265</v>
       </c>
-      <c r="F126" s="41"/>
+      <c r="F126" s="45"/>
       <c r="G126" s="36"/>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.25">
@@ -20128,15 +20151,15 @@
       <c r="B127" s="6">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="C127" s="46">
+      <c r="C127" s="41">
         <v>10</v>
       </c>
-      <c r="D127" s="60"/>
-      <c r="E127" s="40">
+      <c r="D127" s="43"/>
+      <c r="E127" s="44">
         <f t="shared" ref="E127:E141" si="16">(B127-0.0011)/0.0019</f>
         <v>11</v>
       </c>
-      <c r="F127" s="41"/>
+      <c r="F127" s="45"/>
       <c r="G127" s="36"/>
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.25">
@@ -20144,15 +20167,15 @@
         <v>12</v>
       </c>
       <c r="B128" s="6"/>
-      <c r="C128" s="46">
+      <c r="C128" s="41">
         <v>25</v>
       </c>
-      <c r="D128" s="60"/>
-      <c r="E128" s="40">
+      <c r="D128" s="43"/>
+      <c r="E128" s="44">
         <f t="shared" si="16"/>
         <v>-0.57894736842105265</v>
       </c>
-      <c r="F128" s="41"/>
+      <c r="F128" s="45"/>
       <c r="G128" s="36"/>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
@@ -20162,15 +20185,15 @@
       <c r="B129" s="6">
         <v>0.10199999999999999</v>
       </c>
-      <c r="C129" s="46">
+      <c r="C129" s="41">
         <v>50</v>
       </c>
-      <c r="D129" s="60"/>
-      <c r="E129" s="40">
+      <c r="D129" s="43"/>
+      <c r="E129" s="44">
         <f t="shared" si="16"/>
         <v>53.105263157894733</v>
       </c>
-      <c r="F129" s="41"/>
+      <c r="F129" s="45"/>
       <c r="G129" s="36"/>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
@@ -20180,15 +20203,15 @@
       <c r="B130" s="6">
         <v>0.19400000000000001</v>
       </c>
-      <c r="C130" s="46">
+      <c r="C130" s="41">
         <v>100</v>
       </c>
-      <c r="D130" s="60"/>
-      <c r="E130" s="40">
+      <c r="D130" s="43"/>
+      <c r="E130" s="44">
         <f t="shared" si="16"/>
         <v>101.5263157894737</v>
       </c>
-      <c r="F130" s="41"/>
+      <c r="F130" s="45"/>
       <c r="G130" s="36"/>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
@@ -20198,15 +20221,15 @@
       <c r="B131" s="6">
         <v>0.376</v>
       </c>
-      <c r="C131" s="46">
+      <c r="C131" s="41">
         <v>200</v>
       </c>
-      <c r="D131" s="60"/>
-      <c r="E131" s="40">
+      <c r="D131" s="43"/>
+      <c r="E131" s="44">
         <f t="shared" si="16"/>
         <v>197.31578947368422</v>
       </c>
-      <c r="F131" s="41"/>
+      <c r="F131" s="45"/>
       <c r="G131" s="36"/>
     </row>
     <row r="132" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -20216,15 +20239,15 @@
       <c r="B132" s="8">
         <v>0.96699999999999997</v>
       </c>
-      <c r="C132" s="48">
+      <c r="C132" s="47">
         <v>500</v>
       </c>
-      <c r="D132" s="49"/>
-      <c r="E132" s="40">
+      <c r="D132" s="48"/>
+      <c r="E132" s="44">
         <f t="shared" si="16"/>
         <v>508.36842105263156</v>
       </c>
-      <c r="F132" s="41"/>
+      <c r="F132" s="45"/>
       <c r="G132" s="36"/>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
@@ -20234,13 +20257,13 @@
       <c r="B133" s="9">
         <v>8.9999999999999993E-3</v>
       </c>
-      <c r="C133" s="52"/>
-      <c r="D133" s="57"/>
-      <c r="E133" s="40">
+      <c r="C133" s="49"/>
+      <c r="D133" s="60"/>
+      <c r="E133" s="44">
         <f t="shared" si="16"/>
         <v>4.1578947368421044</v>
       </c>
-      <c r="F133" s="41"/>
+      <c r="F133" s="45"/>
       <c r="G133" s="36"/>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
@@ -20250,13 +20273,13 @@
       <c r="B134" s="6">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="C134" s="46"/>
-      <c r="D134" s="60"/>
-      <c r="E134" s="40">
+      <c r="C134" s="41"/>
+      <c r="D134" s="43"/>
+      <c r="E134" s="44">
         <f t="shared" si="16"/>
         <v>2.5789473684210527</v>
       </c>
-      <c r="F134" s="41"/>
+      <c r="F134" s="45"/>
       <c r="G134" s="36"/>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
@@ -20266,13 +20289,13 @@
       <c r="B135" s="6">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="C135" s="46"/>
-      <c r="D135" s="60"/>
-      <c r="E135" s="40">
+      <c r="C135" s="41"/>
+      <c r="D135" s="43"/>
+      <c r="E135" s="44">
         <f t="shared" si="16"/>
         <v>5.2105263157894735</v>
       </c>
-      <c r="F135" s="41"/>
+      <c r="F135" s="45"/>
       <c r="G135" s="36"/>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
@@ -20282,13 +20305,13 @@
       <c r="B136" s="6">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="C136" s="46"/>
-      <c r="D136" s="60"/>
-      <c r="E136" s="40">
+      <c r="C136" s="41"/>
+      <c r="D136" s="43"/>
+      <c r="E136" s="44">
         <f t="shared" si="16"/>
         <v>3.1052631578947367</v>
       </c>
-      <c r="F136" s="41"/>
+      <c r="F136" s="45"/>
       <c r="G136" s="36"/>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
@@ -20298,13 +20321,13 @@
       <c r="B137" s="6">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="C137" s="46"/>
-      <c r="D137" s="60"/>
-      <c r="E137" s="40">
+      <c r="C137" s="41"/>
+      <c r="D137" s="43"/>
+      <c r="E137" s="44">
         <f t="shared" si="16"/>
         <v>2.5789473684210527</v>
       </c>
-      <c r="F137" s="41"/>
+      <c r="F137" s="45"/>
       <c r="G137" s="36"/>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
@@ -20314,13 +20337,13 @@
       <c r="B138" s="6">
         <v>4.4999999999999998E-2</v>
       </c>
-      <c r="C138" s="46"/>
-      <c r="D138" s="60"/>
-      <c r="E138" s="40">
+      <c r="C138" s="41"/>
+      <c r="D138" s="43"/>
+      <c r="E138" s="44">
         <f t="shared" si="16"/>
         <v>23.105263157894736</v>
       </c>
-      <c r="F138" s="41"/>
+      <c r="F138" s="45"/>
       <c r="G138" s="36"/>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
@@ -20330,13 +20353,13 @@
       <c r="B139" s="6">
         <v>3.5999999999999997E-2</v>
       </c>
-      <c r="C139" s="46"/>
-      <c r="D139" s="60"/>
-      <c r="E139" s="40">
+      <c r="C139" s="41"/>
+      <c r="D139" s="43"/>
+      <c r="E139" s="44">
         <f t="shared" si="16"/>
         <v>18.368421052631579</v>
       </c>
-      <c r="F139" s="41"/>
+      <c r="F139" s="45"/>
       <c r="G139" s="36"/>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
@@ -20346,59 +20369,83 @@
       <c r="B140" s="6">
         <v>2.5999999999999999E-2</v>
       </c>
-      <c r="C140" s="46"/>
-      <c r="D140" s="60"/>
-      <c r="E140" s="40">
+      <c r="C140" s="41"/>
+      <c r="D140" s="43"/>
+      <c r="E140" s="44">
         <f t="shared" si="16"/>
         <v>13.105263157894736</v>
       </c>
-      <c r="F140" s="41"/>
+      <c r="F140" s="45"/>
       <c r="G140" s="36"/>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="B141" s="69">
+      <c r="B141" s="6">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="C141" s="46"/>
-      <c r="D141" s="60"/>
-      <c r="E141" s="40">
+      <c r="C141" s="41"/>
+      <c r="D141" s="43"/>
+      <c r="E141" s="44">
         <f t="shared" si="16"/>
         <v>1</v>
       </c>
-      <c r="F141" s="41"/>
+      <c r="F141" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="94">
-    <mergeCell ref="C59:D59"/>
-    <mergeCell ref="E59:F59"/>
-    <mergeCell ref="E73:F73"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="C141:D141"/>
-    <mergeCell ref="E141:F141"/>
-    <mergeCell ref="C117:D117"/>
-    <mergeCell ref="E117:F117"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="E57:F57"/>
-    <mergeCell ref="C58:D58"/>
-    <mergeCell ref="E58:F58"/>
-    <mergeCell ref="C60:D60"/>
-    <mergeCell ref="E60:F60"/>
-    <mergeCell ref="C61:D61"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="C62:D62"/>
-    <mergeCell ref="E62:F62"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="E63:F63"/>
-    <mergeCell ref="C64:D64"/>
-    <mergeCell ref="E64:F64"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="E65:F65"/>
-    <mergeCell ref="C66:D66"/>
-    <mergeCell ref="E66:F66"/>
+    <mergeCell ref="C140:D140"/>
+    <mergeCell ref="E140:F140"/>
+    <mergeCell ref="C137:D137"/>
+    <mergeCell ref="E137:F137"/>
+    <mergeCell ref="C138:D138"/>
+    <mergeCell ref="E138:F138"/>
+    <mergeCell ref="C139:D139"/>
+    <mergeCell ref="E139:F139"/>
+    <mergeCell ref="C134:D134"/>
+    <mergeCell ref="E134:F134"/>
+    <mergeCell ref="C135:D135"/>
+    <mergeCell ref="E135:F135"/>
+    <mergeCell ref="C136:D136"/>
+    <mergeCell ref="E136:F136"/>
+    <mergeCell ref="C131:D131"/>
+    <mergeCell ref="E131:F131"/>
+    <mergeCell ref="C132:D132"/>
+    <mergeCell ref="E132:F132"/>
+    <mergeCell ref="C133:D133"/>
+    <mergeCell ref="E133:F133"/>
+    <mergeCell ref="C128:D128"/>
+    <mergeCell ref="E128:F128"/>
+    <mergeCell ref="C129:D129"/>
+    <mergeCell ref="E129:F129"/>
+    <mergeCell ref="C130:D130"/>
+    <mergeCell ref="E130:F130"/>
+    <mergeCell ref="C127:D127"/>
+    <mergeCell ref="E127:F127"/>
+    <mergeCell ref="C114:D114"/>
+    <mergeCell ref="E114:F114"/>
+    <mergeCell ref="C115:D115"/>
+    <mergeCell ref="E115:F115"/>
+    <mergeCell ref="C116:D116"/>
+    <mergeCell ref="E116:F116"/>
+    <mergeCell ref="A122:H122"/>
+    <mergeCell ref="C125:D125"/>
+    <mergeCell ref="E125:F125"/>
+    <mergeCell ref="C126:D126"/>
+    <mergeCell ref="E126:F126"/>
+    <mergeCell ref="C111:D111"/>
+    <mergeCell ref="E111:F111"/>
+    <mergeCell ref="C112:D112"/>
+    <mergeCell ref="E112:F112"/>
+    <mergeCell ref="C113:D113"/>
+    <mergeCell ref="E113:F113"/>
+    <mergeCell ref="E107:F107"/>
+    <mergeCell ref="E108:F108"/>
+    <mergeCell ref="C109:D109"/>
+    <mergeCell ref="E109:F109"/>
+    <mergeCell ref="C110:D110"/>
+    <mergeCell ref="E110:F110"/>
     <mergeCell ref="C67:D67"/>
     <mergeCell ref="E67:F67"/>
     <mergeCell ref="C68:D68"/>
@@ -20415,57 +20462,33 @@
     <mergeCell ref="E103:F103"/>
     <mergeCell ref="E104:F104"/>
     <mergeCell ref="E105:F105"/>
-    <mergeCell ref="E107:F107"/>
-    <mergeCell ref="E108:F108"/>
-    <mergeCell ref="C109:D109"/>
-    <mergeCell ref="E109:F109"/>
-    <mergeCell ref="C110:D110"/>
-    <mergeCell ref="E110:F110"/>
-    <mergeCell ref="C111:D111"/>
-    <mergeCell ref="E111:F111"/>
-    <mergeCell ref="C112:D112"/>
-    <mergeCell ref="E112:F112"/>
-    <mergeCell ref="C113:D113"/>
-    <mergeCell ref="E113:F113"/>
-    <mergeCell ref="C127:D127"/>
-    <mergeCell ref="E127:F127"/>
-    <mergeCell ref="C114:D114"/>
-    <mergeCell ref="E114:F114"/>
-    <mergeCell ref="C115:D115"/>
-    <mergeCell ref="E115:F115"/>
-    <mergeCell ref="C116:D116"/>
-    <mergeCell ref="E116:F116"/>
-    <mergeCell ref="A122:H122"/>
-    <mergeCell ref="C125:D125"/>
-    <mergeCell ref="E125:F125"/>
-    <mergeCell ref="C126:D126"/>
-    <mergeCell ref="E126:F126"/>
-    <mergeCell ref="C128:D128"/>
-    <mergeCell ref="E128:F128"/>
-    <mergeCell ref="C129:D129"/>
-    <mergeCell ref="E129:F129"/>
-    <mergeCell ref="C130:D130"/>
-    <mergeCell ref="E130:F130"/>
-    <mergeCell ref="C131:D131"/>
-    <mergeCell ref="E131:F131"/>
-    <mergeCell ref="C132:D132"/>
-    <mergeCell ref="E132:F132"/>
-    <mergeCell ref="C133:D133"/>
-    <mergeCell ref="E133:F133"/>
-    <mergeCell ref="C134:D134"/>
-    <mergeCell ref="E134:F134"/>
-    <mergeCell ref="C135:D135"/>
-    <mergeCell ref="E135:F135"/>
-    <mergeCell ref="C136:D136"/>
-    <mergeCell ref="E136:F136"/>
-    <mergeCell ref="C140:D140"/>
-    <mergeCell ref="E140:F140"/>
-    <mergeCell ref="C137:D137"/>
-    <mergeCell ref="E137:F137"/>
-    <mergeCell ref="C138:D138"/>
-    <mergeCell ref="E138:F138"/>
-    <mergeCell ref="C139:D139"/>
-    <mergeCell ref="E139:F139"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="E64:F64"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="E65:F65"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="E66:F66"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="C58:D58"/>
+    <mergeCell ref="E58:F58"/>
+    <mergeCell ref="C59:D59"/>
+    <mergeCell ref="E59:F59"/>
+    <mergeCell ref="E73:F73"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="C141:D141"/>
+    <mergeCell ref="E141:F141"/>
+    <mergeCell ref="C117:D117"/>
+    <mergeCell ref="E117:F117"/>
+    <mergeCell ref="C60:D60"/>
+    <mergeCell ref="E60:F60"/>
+    <mergeCell ref="C61:D61"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="E62:F62"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="E63:F63"/>
   </mergeCells>
   <pageMargins left="0.11458333333333333" right="1.0416666666666666E-2" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Wasser/3_Auswertung Photometrie.xlsx
+++ b/Wasser/3_Auswertung Photometrie.xlsx
@@ -8,15 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alexandra\Documents\GitHub\Moore-Lichtenau-Meusebach\Wasser\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B4A56BB-BECF-4E3C-ACF9-0007D7E21129}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{575AF7B4-8B3E-4F48-B5EE-31147E37FD75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="26.06.2025" sheetId="1" r:id="rId1"/>
     <sheet name="23.07.2025" sheetId="2" r:id="rId2"/>
     <sheet name="31.08.2025" sheetId="3" r:id="rId3"/>
     <sheet name="24.09.2025" sheetId="5" r:id="rId4"/>
+    <sheet name="Ammonium" sheetId="7" r:id="rId5"/>
+    <sheet name="Phosphat" sheetId="6" r:id="rId6"/>
+    <sheet name="Nitrat" sheetId="8" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="114">
   <si>
     <t>sample</t>
   </si>
@@ -352,6 +355,36 @@
   <si>
     <t xml:space="preserve">&gt; 29.09.25 Photometrische Messung </t>
   </si>
+  <si>
+    <t>Nitrat</t>
+  </si>
+  <si>
+    <t>MT</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>MN</t>
+  </si>
+  <si>
+    <t>Standort</t>
+  </si>
+  <si>
+    <t>Messpunkt</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Datum </t>
+  </si>
+  <si>
+    <t>Phosphat</t>
+  </si>
+  <si>
+    <t>Ammonium</t>
+  </si>
 </sst>
 </file>
 
@@ -511,7 +544,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -691,8 +724,14 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="48">
+  <borders count="56">
     <border>
       <left/>
       <right/>
@@ -1260,15 +1299,6 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
@@ -1285,6 +1315,121 @@
       </right>
       <top/>
       <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -1336,7 +1481,7 @@
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1384,26 +1529,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1415,13 +1560,64 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1430,58 +1626,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="54" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -13522,16 +13691,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>220115</xdr:colOff>
-      <xdr:row>119</xdr:row>
-      <xdr:rowOff>24332</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>820190</xdr:colOff>
+      <xdr:row>139</xdr:row>
+      <xdr:rowOff>5282</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>215314</xdr:colOff>
-      <xdr:row>128</xdr:row>
-      <xdr:rowOff>132869</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>939214</xdr:colOff>
+      <xdr:row>148</xdr:row>
+      <xdr:rowOff>123344</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -13739,15 +13908,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>220115</xdr:colOff>
-      <xdr:row>119</xdr:row>
-      <xdr:rowOff>24332</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>353465</xdr:colOff>
+      <xdr:row>139</xdr:row>
+      <xdr:rowOff>14807</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>215314</xdr:colOff>
-      <xdr:row>128</xdr:row>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>472489</xdr:colOff>
+      <xdr:row>148</xdr:row>
       <xdr:rowOff>132869</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -13956,15 +14125,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>220115</xdr:colOff>
-      <xdr:row>120</xdr:row>
-      <xdr:rowOff>24332</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>543965</xdr:colOff>
+      <xdr:row>140</xdr:row>
+      <xdr:rowOff>14807</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>215314</xdr:colOff>
-      <xdr:row>129</xdr:row>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>662989</xdr:colOff>
+      <xdr:row>149</xdr:row>
       <xdr:rowOff>132869</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -14173,16 +14342,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>220115</xdr:colOff>
-      <xdr:row>121</xdr:row>
-      <xdr:rowOff>24332</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>534440</xdr:colOff>
+      <xdr:row>141</xdr:row>
+      <xdr:rowOff>176732</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>215314</xdr:colOff>
-      <xdr:row>130</xdr:row>
-      <xdr:rowOff>132869</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>653464</xdr:colOff>
+      <xdr:row>151</xdr:row>
+      <xdr:rowOff>104294</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -14488,16 +14657,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="70" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
       <c r="I1" s="1"/>
     </row>
     <row r="2" spans="1:9" s="25" customFormat="1" x14ac:dyDescent="0.25">
@@ -14675,7 +14844,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="28" t="s">
         <v>0</v>
       </c>
@@ -14697,20 +14866,20 @@
       <c r="J54" s="16"/>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A55" s="5" t="s">
+      <c r="A55" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B55" s="6">
+      <c r="B55" s="4">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="C55" s="38">
+      <c r="C55" s="77">
         <v>1</v>
       </c>
-      <c r="D55" s="38"/>
-      <c r="E55" s="39">
+      <c r="D55" s="77"/>
+      <c r="E55" s="68">
         <v>0</v>
       </c>
-      <c r="F55" s="40"/>
+      <c r="F55" s="69"/>
       <c r="H55" s="18"/>
       <c r="I55" s="27"/>
       <c r="J55" s="18"/>
@@ -14722,15 +14891,15 @@
       <c r="B56" s="6">
         <v>1.6E-2</v>
       </c>
-      <c r="C56" s="38">
+      <c r="C56" s="76">
         <v>2.5</v>
       </c>
-      <c r="D56" s="38"/>
-      <c r="E56" s="39">
+      <c r="D56" s="76"/>
+      <c r="E56" s="57">
         <f t="shared" ref="E56" si="0">(B56-0.0164)/0.0093</f>
         <v>-4.3010752688172157E-2</v>
       </c>
-      <c r="F56" s="40"/>
+      <c r="F56" s="58"/>
       <c r="H56" s="18"/>
       <c r="I56" s="27"/>
       <c r="J56" s="18"/>
@@ -14742,15 +14911,15 @@
       <c r="B57" s="6">
         <v>0.04</v>
       </c>
-      <c r="C57" s="38">
+      <c r="C57" s="76">
         <v>5</v>
       </c>
-      <c r="D57" s="38"/>
-      <c r="E57" s="39">
+      <c r="D57" s="76"/>
+      <c r="E57" s="57">
         <f>(B57-0.0164)/0.0093</f>
         <v>2.5376344086021505</v>
       </c>
-      <c r="F57" s="40"/>
+      <c r="F57" s="58"/>
       <c r="H57" s="18">
         <f>C57/1000000</f>
         <v>5.0000000000000004E-6</v>
@@ -14771,15 +14940,15 @@
       <c r="B58" s="6">
         <v>8.4000000000000005E-2</v>
       </c>
-      <c r="C58" s="38">
+      <c r="C58" s="76">
         <v>10</v>
       </c>
-      <c r="D58" s="38"/>
-      <c r="E58" s="44">
+      <c r="D58" s="76"/>
+      <c r="E58" s="50">
         <f t="shared" ref="E58:E62" si="1">(B58-0.0164)/0.0093</f>
         <v>7.2688172043010768</v>
       </c>
-      <c r="F58" s="45"/>
+      <c r="F58" s="51"/>
       <c r="H58" s="18">
         <f>C58/1000000</f>
         <v>1.0000000000000001E-5</v>
@@ -14800,15 +14969,15 @@
       <c r="B59" s="6">
         <v>0.22800000000000001</v>
       </c>
-      <c r="C59" s="38">
+      <c r="C59" s="76">
         <v>25</v>
       </c>
-      <c r="D59" s="38"/>
-      <c r="E59" s="44">
+      <c r="D59" s="76"/>
+      <c r="E59" s="50">
         <f t="shared" si="1"/>
         <v>22.752688172043015</v>
       </c>
-      <c r="F59" s="45"/>
+      <c r="F59" s="51"/>
       <c r="H59" s="18"/>
       <c r="I59" s="18"/>
       <c r="J59" s="21"/>
@@ -14820,15 +14989,15 @@
       <c r="B60" s="6">
         <v>0.54300000000000004</v>
       </c>
-      <c r="C60" s="38">
+      <c r="C60" s="76">
         <v>50</v>
       </c>
-      <c r="D60" s="38"/>
-      <c r="E60" s="44">
+      <c r="D60" s="76"/>
+      <c r="E60" s="50">
         <f t="shared" si="1"/>
         <v>56.62365591397851</v>
       </c>
-      <c r="F60" s="45"/>
+      <c r="F60" s="51"/>
       <c r="H60" s="18">
         <f>C60/1000000</f>
         <v>5.0000000000000002E-5</v>
@@ -14849,15 +15018,15 @@
       <c r="B61" s="6">
         <v>0.98199999999999998</v>
       </c>
-      <c r="C61" s="38">
+      <c r="C61" s="76">
         <v>100</v>
       </c>
-      <c r="D61" s="38"/>
-      <c r="E61" s="44">
+      <c r="D61" s="76"/>
+      <c r="E61" s="50">
         <f t="shared" si="1"/>
         <v>103.82795698924733</v>
       </c>
-      <c r="F61" s="45"/>
+      <c r="F61" s="51"/>
       <c r="H61" s="18">
         <f>C61/1000000</f>
         <v>1E-4</v>
@@ -14878,15 +15047,15 @@
       <c r="B62" s="8">
         <v>1.8460000000000001</v>
       </c>
-      <c r="C62" s="47">
+      <c r="C62" s="52">
         <v>200</v>
       </c>
-      <c r="D62" s="48"/>
-      <c r="E62" s="62">
+      <c r="D62" s="53"/>
+      <c r="E62" s="54">
         <f t="shared" si="1"/>
         <v>196.73118279569894</v>
       </c>
-      <c r="F62" s="63"/>
+      <c r="F62" s="55"/>
       <c r="H62" s="19">
         <f>C62/1000000</f>
         <v>2.0000000000000001E-4</v>
@@ -14901,18 +15070,18 @@
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A63" s="9" t="s">
+      <c r="A63" s="41" t="s">
         <v>46</v>
       </c>
       <c r="B63" s="9">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="C63" s="49"/>
-      <c r="D63" s="50"/>
-      <c r="E63" s="55">
+      <c r="C63" s="72"/>
+      <c r="D63" s="73"/>
+      <c r="E63" s="74">
         <v>0</v>
       </c>
-      <c r="F63" s="55"/>
+      <c r="F63" s="75"/>
       <c r="H63" s="18">
         <f t="shared" ref="H63:H70" si="4">E63/1000000</f>
         <v>0</v>
@@ -14927,18 +15096,18 @@
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A64" s="6" t="s">
+      <c r="A64" s="5" t="s">
         <v>47</v>
       </c>
       <c r="B64" s="6">
         <v>2E-3</v>
       </c>
-      <c r="C64" s="41"/>
-      <c r="D64" s="42"/>
-      <c r="E64" s="39">
+      <c r="C64" s="48"/>
+      <c r="D64" s="56"/>
+      <c r="E64" s="57">
         <v>0</v>
       </c>
-      <c r="F64" s="39"/>
+      <c r="F64" s="58"/>
       <c r="H64" s="18">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -14953,18 +15122,18 @@
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A65" s="6" t="s">
+      <c r="A65" s="5" t="s">
         <v>48</v>
       </c>
       <c r="B65" s="6">
         <v>2E-3</v>
       </c>
-      <c r="C65" s="41"/>
-      <c r="D65" s="42"/>
-      <c r="E65" s="39">
+      <c r="C65" s="48"/>
+      <c r="D65" s="56"/>
+      <c r="E65" s="57">
         <v>0</v>
       </c>
-      <c r="F65" s="39"/>
+      <c r="F65" s="58"/>
       <c r="H65" s="18">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -14979,18 +15148,18 @@
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A66" s="6" t="s">
+      <c r="A66" s="5" t="s">
         <v>49</v>
       </c>
       <c r="B66" s="6">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="C66" s="41"/>
-      <c r="D66" s="42"/>
-      <c r="E66" s="39">
+      <c r="C66" s="48"/>
+      <c r="D66" s="56"/>
+      <c r="E66" s="57">
         <v>0</v>
       </c>
-      <c r="F66" s="39"/>
+      <c r="F66" s="58"/>
       <c r="H66" s="18">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -15005,19 +15174,19 @@
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A67" s="6" t="s">
+      <c r="A67" s="5" t="s">
         <v>50</v>
       </c>
       <c r="B67" s="6">
         <v>0.109</v>
       </c>
-      <c r="C67" s="41"/>
-      <c r="D67" s="42"/>
-      <c r="E67" s="39">
+      <c r="C67" s="48"/>
+      <c r="D67" s="56"/>
+      <c r="E67" s="57">
         <f t="shared" ref="E67:E70" si="7">(B67-0.0164)/0.0093</f>
         <v>9.9569892473118298</v>
       </c>
-      <c r="F67" s="39"/>
+      <c r="F67" s="58"/>
       <c r="H67" s="18">
         <f t="shared" si="4"/>
         <v>9.9569892473118294E-6</v>
@@ -15032,19 +15201,19 @@
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A68" s="6" t="s">
+      <c r="A68" s="5" t="s">
         <v>51</v>
       </c>
       <c r="B68" s="6">
         <v>0.36</v>
       </c>
-      <c r="C68" s="41"/>
-      <c r="D68" s="42"/>
-      <c r="E68" s="39">
+      <c r="C68" s="48"/>
+      <c r="D68" s="56"/>
+      <c r="E68" s="57">
         <f t="shared" si="7"/>
         <v>36.946236559139784</v>
       </c>
-      <c r="F68" s="39"/>
+      <c r="F68" s="58"/>
       <c r="H68" s="18">
         <f t="shared" si="4"/>
         <v>3.6946236559139785E-5</v>
@@ -15059,19 +15228,19 @@
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A69" s="6" t="s">
+      <c r="A69" s="5" t="s">
         <v>52</v>
       </c>
       <c r="B69" s="6">
         <v>0.91300000000000003</v>
       </c>
-      <c r="C69" s="41"/>
-      <c r="D69" s="42"/>
-      <c r="E69" s="39">
+      <c r="C69" s="48"/>
+      <c r="D69" s="56"/>
+      <c r="E69" s="57">
         <f t="shared" si="7"/>
         <v>96.408602150537646</v>
       </c>
-      <c r="F69" s="39"/>
+      <c r="F69" s="58"/>
       <c r="H69" s="18">
         <f t="shared" si="4"/>
         <v>9.6408602150537646E-5</v>
@@ -15085,20 +15254,20 @@
         <v>1.7390627135483876</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A70" s="6" t="s">
+    <row r="70" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="B70" s="6">
+      <c r="B70" s="8">
         <v>4.7E-2</v>
       </c>
-      <c r="C70" s="41"/>
-      <c r="D70" s="42"/>
-      <c r="E70" s="39">
+      <c r="C70" s="52"/>
+      <c r="D70" s="59"/>
+      <c r="E70" s="60">
         <f t="shared" si="7"/>
         <v>3.2903225806451615</v>
       </c>
-      <c r="F70" s="39"/>
+      <c r="F70" s="61"/>
       <c r="H70" s="18">
         <f t="shared" si="4"/>
         <v>3.2903225806451615E-6</v>
@@ -15136,7 +15305,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="I99" s="16" t="s">
         <v>22</v>
       </c>
@@ -15148,28 +15317,27 @@
       </c>
     </row>
     <row r="100" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="2" t="s">
+      <c r="A100" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B100" s="2" t="s">
+      <c r="B100" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="C100" s="2" t="s">
+      <c r="C100" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="D100" s="2"/>
-      <c r="E100" s="2" t="s">
+      <c r="D100" s="39"/>
+      <c r="E100" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="F100" s="2"/>
-      <c r="G100" s="35"/>
-      <c r="I100" s="17" t="s">
+      <c r="F100" s="40"/>
+      <c r="I100" s="27" t="s">
         <v>15</v>
       </c>
       <c r="J100" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="K100" s="17" t="s">
+      <c r="K100" s="27" t="s">
         <v>21</v>
       </c>
     </row>
@@ -15184,16 +15352,16 @@
         <v>0.5</v>
       </c>
       <c r="D101" s="11"/>
-      <c r="E101" s="51">
+      <c r="E101" s="68">
         <f>(B101+0.0049)/0.0204</f>
         <v>0.28921568627450978</v>
       </c>
-      <c r="F101" s="52"/>
+      <c r="F101" s="69"/>
       <c r="I101" s="16">
         <f t="shared" ref="I101:I106" si="8">C101/1000000</f>
         <v>4.9999999999999998E-7</v>
       </c>
-      <c r="J101" s="16">
+      <c r="J101" s="36">
         <f t="shared" ref="J101:J106" si="9">$K$96*I101</f>
         <v>4.74865E-5</v>
       </c>
@@ -15213,16 +15381,16 @@
         <v>1</v>
       </c>
       <c r="D102" s="13"/>
-      <c r="E102" s="39">
+      <c r="E102" s="57">
         <f t="shared" ref="E102:E106" si="10">(B102+0.0049)/0.0204</f>
         <v>1.0245098039215685</v>
       </c>
-      <c r="F102" s="40"/>
+      <c r="F102" s="58"/>
       <c r="I102" s="18">
         <f t="shared" si="8"/>
         <v>9.9999999999999995E-7</v>
       </c>
-      <c r="J102" s="18">
+      <c r="J102">
         <f t="shared" si="9"/>
         <v>9.4973E-5</v>
       </c>
@@ -15242,16 +15410,16 @@
         <v>5</v>
       </c>
       <c r="D103" s="13"/>
-      <c r="E103" s="39">
+      <c r="E103" s="57">
         <f t="shared" si="10"/>
         <v>4.6029411764705879</v>
       </c>
-      <c r="F103" s="40"/>
+      <c r="F103" s="58"/>
       <c r="I103" s="18">
         <f t="shared" si="8"/>
         <v>5.0000000000000004E-6</v>
       </c>
-      <c r="J103" s="18">
+      <c r="J103">
         <f t="shared" si="9"/>
         <v>4.7486500000000004E-4</v>
       </c>
@@ -15271,16 +15439,16 @@
         <v>10</v>
       </c>
       <c r="D104" s="13"/>
-      <c r="E104" s="39">
+      <c r="E104" s="57">
         <f t="shared" si="10"/>
         <v>10.877450980392155</v>
       </c>
-      <c r="F104" s="40"/>
+      <c r="F104" s="58"/>
       <c r="I104" s="18">
         <f t="shared" si="8"/>
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="J104" s="18">
+      <c r="J104">
         <f t="shared" si="9"/>
         <v>9.4973000000000008E-4</v>
       </c>
@@ -15289,7 +15457,7 @@
         <v>0.94973000000000007</v>
       </c>
     </row>
-    <row r="105" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A105" s="31" t="s">
         <v>12</v>
       </c>
@@ -15300,20 +15468,20 @@
         <v>25</v>
       </c>
       <c r="D105" s="33"/>
-      <c r="E105" s="39">
+      <c r="E105" s="57">
         <f t="shared" si="10"/>
         <v>24.799019607843135</v>
       </c>
-      <c r="F105" s="40"/>
-      <c r="I105" s="19">
+      <c r="F105" s="58"/>
+      <c r="I105" s="18">
         <f t="shared" si="8"/>
         <v>2.5000000000000001E-5</v>
       </c>
-      <c r="J105" s="19">
+      <c r="J105">
         <f t="shared" si="9"/>
         <v>2.374325E-3</v>
       </c>
-      <c r="K105" s="22">
+      <c r="K105" s="21">
         <f t="shared" si="11"/>
         <v>2.3743250000000002</v>
       </c>
@@ -15329,38 +15497,38 @@
         <v>50</v>
       </c>
       <c r="D106" s="15"/>
-      <c r="E106" s="53">
+      <c r="E106" s="60">
         <f t="shared" si="10"/>
         <v>37.446078431372548</v>
       </c>
-      <c r="F106" s="54"/>
-      <c r="I106" s="18">
+      <c r="F106" s="61"/>
+      <c r="I106" s="19">
         <f t="shared" si="8"/>
         <v>5.0000000000000002E-5</v>
       </c>
-      <c r="J106" s="18">
+      <c r="J106" s="37">
         <f t="shared" si="9"/>
         <v>4.7486500000000001E-3</v>
       </c>
-      <c r="K106" s="21">
+      <c r="K106" s="22">
         <f t="shared" si="11"/>
         <v>4.7486500000000005</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A107" s="9" t="s">
+      <c r="A107" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B107" s="9">
+      <c r="B107" s="4">
         <v>0</v>
       </c>
-      <c r="C107" s="49"/>
-      <c r="D107" s="50"/>
-      <c r="E107" s="55">
+      <c r="C107" s="62"/>
+      <c r="D107" s="71"/>
+      <c r="E107" s="68">
         <f t="shared" ref="E107" si="12">(B107+0.0049)/0.0204</f>
         <v>0.24019607843137253</v>
       </c>
-      <c r="F107" s="55"/>
+      <c r="F107" s="69"/>
       <c r="I107" s="18">
         <f>E107/1000000</f>
         <v>2.4019607843137255E-7</v>
@@ -15375,19 +15543,19 @@
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A108" s="6" t="s">
+      <c r="A108" s="5" t="s">
         <v>47</v>
       </c>
       <c r="B108" s="6">
         <v>0</v>
       </c>
-      <c r="C108" s="41"/>
-      <c r="D108" s="42"/>
-      <c r="E108" s="39">
+      <c r="C108" s="48"/>
+      <c r="D108" s="56"/>
+      <c r="E108" s="57">
         <f t="shared" ref="E108:E114" si="13">(B108+0.0049)/0.0204</f>
         <v>0.24019607843137253</v>
       </c>
-      <c r="F108" s="39"/>
+      <c r="F108" s="58"/>
       <c r="I108" s="18">
         <f t="shared" ref="I108:I114" si="14">E108/1000000</f>
         <v>2.4019607843137255E-7</v>
@@ -15402,19 +15570,19 @@
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A109" s="6" t="s">
+      <c r="A109" s="5" t="s">
         <v>48</v>
       </c>
       <c r="B109" s="6">
         <v>0</v>
       </c>
-      <c r="C109" s="41"/>
-      <c r="D109" s="42"/>
-      <c r="E109" s="39">
+      <c r="C109" s="48"/>
+      <c r="D109" s="56"/>
+      <c r="E109" s="57">
         <f t="shared" si="13"/>
         <v>0.24019607843137253</v>
       </c>
-      <c r="F109" s="39"/>
+      <c r="F109" s="58"/>
       <c r="I109" s="18">
         <f t="shared" si="14"/>
         <v>2.4019607843137255E-7</v>
@@ -15429,19 +15597,19 @@
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A110" s="6" t="s">
+      <c r="A110" s="5" t="s">
         <v>49</v>
       </c>
       <c r="B110" s="6">
         <v>0</v>
       </c>
-      <c r="C110" s="41"/>
-      <c r="D110" s="42"/>
-      <c r="E110" s="39">
+      <c r="C110" s="48"/>
+      <c r="D110" s="56"/>
+      <c r="E110" s="57">
         <f t="shared" si="13"/>
         <v>0.24019607843137253</v>
       </c>
-      <c r="F110" s="39"/>
+      <c r="F110" s="58"/>
       <c r="I110" s="18">
         <f t="shared" si="14"/>
         <v>2.4019607843137255E-7</v>
@@ -15456,19 +15624,19 @@
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A111" s="6" t="s">
+      <c r="A111" s="5" t="s">
         <v>50</v>
       </c>
       <c r="B111" s="6">
         <v>1.4E-2</v>
       </c>
-      <c r="C111" s="41"/>
-      <c r="D111" s="42"/>
-      <c r="E111" s="39">
+      <c r="C111" s="48"/>
+      <c r="D111" s="56"/>
+      <c r="E111" s="57">
         <f t="shared" si="13"/>
         <v>0.92647058823529405</v>
       </c>
-      <c r="F111" s="39"/>
+      <c r="F111" s="58"/>
       <c r="I111" s="18">
         <f t="shared" si="14"/>
         <v>9.2647058823529408E-7</v>
@@ -15483,19 +15651,19 @@
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A112" s="6" t="s">
+      <c r="A112" s="5" t="s">
         <v>51</v>
       </c>
       <c r="B112" s="6">
         <v>8.9999999999999993E-3</v>
       </c>
-      <c r="C112" s="41"/>
-      <c r="D112" s="42"/>
-      <c r="E112" s="39">
+      <c r="C112" s="48"/>
+      <c r="D112" s="56"/>
+      <c r="E112" s="57">
         <f t="shared" si="13"/>
         <v>0.68137254901960775</v>
       </c>
-      <c r="F112" s="39"/>
+      <c r="F112" s="58"/>
       <c r="I112" s="18">
         <f t="shared" si="14"/>
         <v>6.8137254901960776E-7</v>
@@ -15510,19 +15678,19 @@
       </c>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A113" s="6" t="s">
+      <c r="A113" s="5" t="s">
         <v>52</v>
       </c>
       <c r="B113" s="6">
         <v>3.9E-2</v>
       </c>
-      <c r="C113" s="41"/>
-      <c r="D113" s="42"/>
-      <c r="E113" s="39">
+      <c r="C113" s="48"/>
+      <c r="D113" s="56"/>
+      <c r="E113" s="57">
         <f t="shared" si="13"/>
         <v>2.1519607843137254</v>
       </c>
-      <c r="F113" s="39"/>
+      <c r="F113" s="58"/>
       <c r="I113" s="18">
         <f t="shared" si="14"/>
         <v>2.1519607843137253E-6</v>
@@ -15536,20 +15704,20 @@
         <v>3.881805852941176E-2</v>
       </c>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A114" s="6" t="s">
+    <row r="114" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A114" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="B114" s="6">
+      <c r="B114" s="8">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="C114" s="41"/>
-      <c r="D114" s="42"/>
-      <c r="E114" s="39">
+      <c r="C114" s="52"/>
+      <c r="D114" s="59"/>
+      <c r="E114" s="60">
         <f t="shared" si="13"/>
         <v>0.53431372549019607</v>
       </c>
-      <c r="F114" s="39"/>
+      <c r="F114" s="61"/>
       <c r="I114" s="18">
         <f t="shared" si="14"/>
         <v>5.3431372549019611E-7</v>
@@ -15563,37 +15731,71 @@
         <v>9.6381967647058819E-3</v>
       </c>
     </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="I118" t="s">
+        <v>25</v>
+      </c>
+      <c r="K118">
+        <v>62.005400000000002</v>
+      </c>
+    </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.25">
       <c r="H119" s="24"/>
-    </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A120" s="46" t="s">
+      <c r="I119" t="s">
+        <v>16</v>
+      </c>
+      <c r="K119">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A120" s="70" t="s">
         <v>27</v>
       </c>
-      <c r="B120" s="46"/>
-      <c r="C120" s="46"/>
-      <c r="D120" s="46"/>
-      <c r="E120" s="46"/>
-      <c r="F120" s="46"/>
-      <c r="G120" s="46"/>
-      <c r="H120" s="46"/>
+      <c r="B120" s="70"/>
+      <c r="C120" s="70"/>
+      <c r="D120" s="70"/>
+      <c r="E120" s="70"/>
+      <c r="F120" s="70"/>
+      <c r="G120" s="70"/>
+      <c r="H120" s="70"/>
+    </row>
+    <row r="121" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I121" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="J121" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K121" s="20" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="122" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="2" t="s">
+      <c r="A122" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B122" s="2" t="s">
+      <c r="B122" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="C122" s="2" t="s">
+      <c r="C122" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="D122" s="2"/>
-      <c r="E122" s="2" t="s">
+      <c r="D122" s="39"/>
+      <c r="E122" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="F122" s="2"/>
-      <c r="G122" s="37"/>
+      <c r="F122" s="40"/>
+      <c r="G122" s="35"/>
+      <c r="I122" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="J122" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="K122" s="17" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A123" s="3" t="s">
@@ -15602,15 +15804,27 @@
       <c r="B123" s="4">
         <v>0</v>
       </c>
-      <c r="C123" s="56">
+      <c r="C123" s="62">
         <v>2.5</v>
       </c>
-      <c r="D123" s="57"/>
-      <c r="E123" s="51">
+      <c r="D123" s="63"/>
+      <c r="E123" s="68">
         <v>0</v>
       </c>
-      <c r="F123" s="52"/>
-      <c r="G123" s="36"/>
+      <c r="F123" s="69"/>
+      <c r="G123" s="35"/>
+      <c r="I123" s="16">
+        <f t="shared" ref="I123:I130" si="17">C123/1000000</f>
+        <v>2.5000000000000002E-6</v>
+      </c>
+      <c r="J123" s="16">
+        <f>$K$118*I123</f>
+        <v>1.5501350000000002E-4</v>
+      </c>
+      <c r="K123" s="23">
+        <f>J123*1000</f>
+        <v>0.15501350000000003</v>
+      </c>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A124" s="31" t="s">
@@ -15619,16 +15833,28 @@
       <c r="B124" s="2">
         <v>1E-3</v>
       </c>
-      <c r="C124" s="58">
+      <c r="C124" s="66">
         <v>5</v>
       </c>
-      <c r="D124" s="59"/>
-      <c r="E124" s="44">
-        <f t="shared" ref="E124:E130" si="17">(B124+0.0067)/0.0019</f>
+      <c r="D124" s="67"/>
+      <c r="E124" s="50">
+        <f t="shared" ref="E124:E130" si="18">(B124+0.0067)/0.0019</f>
         <v>4.0526315789473681</v>
       </c>
-      <c r="F124" s="45"/>
-      <c r="G124" s="36"/>
+      <c r="F124" s="51"/>
+      <c r="G124" s="35"/>
+      <c r="I124" s="18">
+        <f t="shared" si="17"/>
+        <v>5.0000000000000004E-6</v>
+      </c>
+      <c r="J124" s="18">
+        <f>$K$118*I124</f>
+        <v>3.1002700000000005E-4</v>
+      </c>
+      <c r="K124" s="21">
+        <f t="shared" ref="K124:K130" si="19">J124*1000</f>
+        <v>0.31002700000000005</v>
+      </c>
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A125" s="5" t="s">
@@ -15637,16 +15863,28 @@
       <c r="B125" s="6">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="C125" s="41">
+      <c r="C125" s="48">
         <v>10</v>
       </c>
-      <c r="D125" s="43"/>
-      <c r="E125" s="44">
+      <c r="D125" s="49"/>
+      <c r="E125" s="50">
+        <f t="shared" si="18"/>
+        <v>7.7368421052631584</v>
+      </c>
+      <c r="F125" s="51"/>
+      <c r="G125" s="35"/>
+      <c r="I125" s="18">
         <f t="shared" si="17"/>
-        <v>7.7368421052631584</v>
-      </c>
-      <c r="F125" s="45"/>
-      <c r="G125" s="36"/>
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="J125" s="18">
+        <f t="shared" ref="J125:J130" si="20">$K$118*I125</f>
+        <v>6.2005400000000009E-4</v>
+      </c>
+      <c r="K125" s="21">
+        <f t="shared" si="19"/>
+        <v>0.62005400000000011</v>
+      </c>
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A126" s="5" t="s">
@@ -15655,16 +15893,28 @@
       <c r="B126" s="6">
         <v>4.1000000000000002E-2</v>
       </c>
-      <c r="C126" s="41">
+      <c r="C126" s="48">
         <v>25</v>
       </c>
-      <c r="D126" s="43"/>
-      <c r="E126" s="44">
+      <c r="D126" s="49"/>
+      <c r="E126" s="50">
+        <f t="shared" si="18"/>
+        <v>25.105263157894736</v>
+      </c>
+      <c r="F126" s="51"/>
+      <c r="G126" s="35"/>
+      <c r="I126" s="18">
         <f t="shared" si="17"/>
-        <v>25.105263157894736</v>
-      </c>
-      <c r="F126" s="45"/>
-      <c r="G126" s="36"/>
+        <v>2.5000000000000001E-5</v>
+      </c>
+      <c r="J126" s="18">
+        <f t="shared" si="20"/>
+        <v>1.550135E-3</v>
+      </c>
+      <c r="K126" s="21">
+        <f t="shared" si="19"/>
+        <v>1.550135</v>
+      </c>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A127" s="5" t="s">
@@ -15673,16 +15923,28 @@
       <c r="B127" s="6">
         <v>8.3000000000000004E-2</v>
       </c>
-      <c r="C127" s="41">
+      <c r="C127" s="48">
         <v>50</v>
       </c>
-      <c r="D127" s="43"/>
-      <c r="E127" s="44">
+      <c r="D127" s="49"/>
+      <c r="E127" s="50">
+        <f t="shared" si="18"/>
+        <v>47.210526315789473</v>
+      </c>
+      <c r="F127" s="51"/>
+      <c r="G127" s="35"/>
+      <c r="I127" s="18">
         <f t="shared" si="17"/>
-        <v>47.210526315789473</v>
-      </c>
-      <c r="F127" s="45"/>
-      <c r="G127" s="36"/>
+        <v>5.0000000000000002E-5</v>
+      </c>
+      <c r="J127" s="18">
+        <f t="shared" si="20"/>
+        <v>3.10027E-3</v>
+      </c>
+      <c r="K127" s="21">
+        <f t="shared" si="19"/>
+        <v>3.1002700000000001</v>
+      </c>
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A128" s="5" t="s">
@@ -15691,176 +15953,308 @@
       <c r="B128" s="6">
         <v>0.17499999999999999</v>
       </c>
-      <c r="C128" s="41">
+      <c r="C128" s="48">
         <v>100</v>
       </c>
-      <c r="D128" s="43"/>
-      <c r="E128" s="44">
+      <c r="D128" s="49"/>
+      <c r="E128" s="50">
+        <f t="shared" si="18"/>
+        <v>95.631578947368425</v>
+      </c>
+      <c r="F128" s="51"/>
+      <c r="G128" s="35"/>
+      <c r="I128" s="18">
         <f t="shared" si="17"/>
-        <v>95.631578947368425</v>
-      </c>
-      <c r="F128" s="45"/>
-      <c r="G128" s="36"/>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+        <v>1E-4</v>
+      </c>
+      <c r="J128" s="18">
+        <f t="shared" si="20"/>
+        <v>6.20054E-3</v>
+      </c>
+      <c r="K128" s="21">
+        <f t="shared" si="19"/>
+        <v>6.2005400000000002</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A129" s="5" t="s">
         <v>5</v>
       </c>
       <c r="B129" s="6">
         <v>0.375</v>
       </c>
-      <c r="C129" s="41">
+      <c r="C129" s="48">
         <v>200</v>
       </c>
-      <c r="D129" s="43"/>
-      <c r="E129" s="44">
+      <c r="D129" s="49"/>
+      <c r="E129" s="50">
+        <f t="shared" si="18"/>
+        <v>200.89473684210526</v>
+      </c>
+      <c r="F129" s="51"/>
+      <c r="G129" s="35"/>
+      <c r="I129" s="18">
         <f t="shared" si="17"/>
-        <v>200.89473684210526</v>
-      </c>
-      <c r="F129" s="45"/>
-      <c r="G129" s="36"/>
-    </row>
-    <row r="130" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="J129" s="18">
+        <f t="shared" si="20"/>
+        <v>1.240108E-2</v>
+      </c>
+      <c r="K129" s="21">
+        <f t="shared" si="19"/>
+        <v>12.40108</v>
+      </c>
+    </row>
+    <row r="130" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A130" s="7" t="s">
         <v>6</v>
       </c>
       <c r="B130" s="8">
         <v>0.91500000000000004</v>
       </c>
-      <c r="C130" s="47">
+      <c r="C130" s="52">
         <v>500</v>
       </c>
-      <c r="D130" s="48"/>
-      <c r="E130" s="62">
+      <c r="D130" s="53"/>
+      <c r="E130" s="54">
+        <f t="shared" si="18"/>
+        <v>485.1052631578948</v>
+      </c>
+      <c r="F130" s="55"/>
+      <c r="G130" s="35"/>
+      <c r="I130" s="19">
         <f t="shared" si="17"/>
-        <v>485.1052631578948</v>
-      </c>
-      <c r="F130" s="63"/>
-      <c r="G130" s="36"/>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A131" s="9" t="s">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="J130" s="19">
+        <f t="shared" si="20"/>
+        <v>3.1002700000000001E-2</v>
+      </c>
+      <c r="K130" s="22">
+        <f t="shared" si="19"/>
+        <v>31.002700000000001</v>
+      </c>
+    </row>
+    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A131" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B131" s="9">
+      <c r="B131" s="4">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="C131" s="49"/>
-      <c r="D131" s="60"/>
+      <c r="C131" s="62"/>
+      <c r="D131" s="63"/>
       <c r="E131" s="64">
-        <f t="shared" ref="E131:E138" si="18">(B131+0.0067)/0.0019</f>
+        <f t="shared" ref="E131:E138" si="21">(B131+0.0067)/0.0019</f>
         <v>9.3157894736842106</v>
       </c>
       <c r="F131" s="65"/>
-      <c r="G131" s="36"/>
-    </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A132" s="6" t="s">
+      <c r="G131" s="35"/>
+      <c r="I131" s="18">
+        <f>E131/1000000</f>
+        <v>9.3157894736842104E-6</v>
+      </c>
+      <c r="J131" s="18">
+        <f>$K$118*I131*$K$119</f>
+        <v>5.776292526315789E-7</v>
+      </c>
+      <c r="K131" s="21">
+        <f t="shared" ref="K131:K138" si="22">J131*1000000</f>
+        <v>0.57762925263157894</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A132" s="5" t="s">
         <v>47</v>
       </c>
       <c r="B132" s="6">
         <v>0</v>
       </c>
-      <c r="C132" s="41"/>
-      <c r="D132" s="43"/>
-      <c r="E132" s="44">
+      <c r="C132" s="48"/>
+      <c r="D132" s="49"/>
+      <c r="E132" s="50">
         <v>0</v>
       </c>
-      <c r="F132" s="61"/>
-      <c r="G132" s="36"/>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A133" s="6" t="s">
+      <c r="F132" s="51"/>
+      <c r="G132" s="35"/>
+      <c r="I132" s="18">
+        <f>E132/1000000</f>
+        <v>0</v>
+      </c>
+      <c r="J132" s="18">
+        <f t="shared" ref="J132:J138" si="23">$K$118*I132*$K$119</f>
+        <v>0</v>
+      </c>
+      <c r="K132" s="21">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A133" s="5" t="s">
         <v>48</v>
       </c>
       <c r="B133" s="6">
         <v>0</v>
       </c>
-      <c r="C133" s="41"/>
-      <c r="D133" s="43"/>
-      <c r="E133" s="44">
+      <c r="C133" s="48"/>
+      <c r="D133" s="49"/>
+      <c r="E133" s="50">
         <v>0</v>
       </c>
-      <c r="F133" s="61"/>
-      <c r="G133" s="36"/>
-    </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A134" s="6" t="s">
+      <c r="F133" s="51"/>
+      <c r="G133" s="35"/>
+      <c r="I133" s="18">
+        <f t="shared" ref="I133:I138" si="24">E133/1000000</f>
+        <v>0</v>
+      </c>
+      <c r="J133" s="18">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="K133" s="21">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A134" s="5" t="s">
         <v>49</v>
       </c>
       <c r="B134" s="6">
         <v>0</v>
       </c>
-      <c r="C134" s="41"/>
-      <c r="D134" s="43"/>
-      <c r="E134" s="44">
+      <c r="C134" s="48"/>
+      <c r="D134" s="49"/>
+      <c r="E134" s="50">
         <v>0</v>
       </c>
-      <c r="F134" s="61"/>
-      <c r="G134" s="36"/>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A135" s="6" t="s">
+      <c r="F134" s="51"/>
+      <c r="G134" s="35"/>
+      <c r="I134" s="18">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="J134" s="18">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="K134" s="21">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A135" s="5" t="s">
         <v>50</v>
       </c>
       <c r="B135" s="6">
         <v>0</v>
       </c>
-      <c r="C135" s="41"/>
-      <c r="D135" s="43"/>
-      <c r="E135" s="44">
+      <c r="C135" s="48"/>
+      <c r="D135" s="49"/>
+      <c r="E135" s="50">
         <v>0</v>
       </c>
-      <c r="F135" s="61"/>
-      <c r="G135" s="36"/>
-    </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A136" s="6" t="s">
+      <c r="F135" s="51"/>
+      <c r="G135" s="35"/>
+      <c r="I135" s="18">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="J135" s="18">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="K135" s="21">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A136" s="5" t="s">
         <v>51</v>
       </c>
       <c r="B136" s="6">
         <v>1.7999999999999999E-2</v>
       </c>
-      <c r="C136" s="41"/>
-      <c r="D136" s="43"/>
-      <c r="E136" s="44">
-        <f t="shared" si="18"/>
+      <c r="C136" s="48"/>
+      <c r="D136" s="49"/>
+      <c r="E136" s="50">
+        <f t="shared" si="21"/>
         <v>13</v>
       </c>
-      <c r="F136" s="61"/>
-      <c r="G136" s="36"/>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A137" s="6" t="s">
+      <c r="F136" s="51"/>
+      <c r="G136" s="35"/>
+      <c r="I136" s="18">
+        <f t="shared" si="24"/>
+        <v>1.2999999999999999E-5</v>
+      </c>
+      <c r="J136" s="18">
+        <f t="shared" si="23"/>
+        <v>8.060702E-7</v>
+      </c>
+      <c r="K136" s="21">
+        <f t="shared" si="22"/>
+        <v>0.80607019999999996</v>
+      </c>
+    </row>
+    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A137" s="5" t="s">
         <v>52</v>
       </c>
       <c r="B137" s="6">
         <v>2.8000000000000001E-2</v>
       </c>
-      <c r="C137" s="41"/>
-      <c r="D137" s="43"/>
-      <c r="E137" s="44">
-        <f t="shared" si="18"/>
+      <c r="C137" s="48"/>
+      <c r="D137" s="49"/>
+      <c r="E137" s="50">
+        <f t="shared" si="21"/>
         <v>18.263157894736842</v>
       </c>
-      <c r="F137" s="61"/>
-      <c r="G137" s="36"/>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A138" s="6" t="s">
+      <c r="F137" s="51"/>
+      <c r="G137" s="35"/>
+      <c r="I137" s="18">
+        <f t="shared" si="24"/>
+        <v>1.8263157894736844E-5</v>
+      </c>
+      <c r="J137" s="18">
+        <f t="shared" si="23"/>
+        <v>1.1324144105263159E-6</v>
+      </c>
+      <c r="K137" s="21">
+        <f t="shared" si="22"/>
+        <v>1.1324144105263159</v>
+      </c>
+    </row>
+    <row r="138" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A138" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="B138" s="6">
+      <c r="B138" s="8">
         <v>2.7E-2</v>
       </c>
-      <c r="C138" s="41"/>
-      <c r="D138" s="43"/>
-      <c r="E138" s="44">
-        <f t="shared" si="18"/>
+      <c r="C138" s="52"/>
+      <c r="D138" s="53"/>
+      <c r="E138" s="54">
+        <f t="shared" si="21"/>
         <v>17.736842105263158</v>
       </c>
-      <c r="F138" s="61"/>
-      <c r="G138" s="36"/>
+      <c r="F138" s="55"/>
+      <c r="G138" s="35"/>
+      <c r="I138" s="18">
+        <f t="shared" si="24"/>
+        <v>1.7736842105263157E-5</v>
+      </c>
+      <c r="J138" s="18">
+        <f t="shared" si="23"/>
+        <v>1.0997799894736841E-6</v>
+      </c>
+      <c r="K138" s="21">
+        <f t="shared" si="22"/>
+        <v>1.0997799894736842</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="88">
@@ -15974,16 +16368,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="70" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
       <c r="I1" s="1"/>
     </row>
     <row r="2" spans="1:9" s="25" customFormat="1" x14ac:dyDescent="0.25">
@@ -16161,7 +16555,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="28" t="s">
         <v>0</v>
       </c>
@@ -16183,18 +16577,18 @@
       <c r="J54" s="16"/>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A55" s="5" t="s">
+      <c r="A55" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B55" s="6"/>
-      <c r="C55" s="38">
+      <c r="B55" s="4"/>
+      <c r="C55" s="77">
         <v>1</v>
       </c>
-      <c r="D55" s="38"/>
-      <c r="E55" s="39">
+      <c r="D55" s="77"/>
+      <c r="E55" s="68">
         <v>0</v>
       </c>
-      <c r="F55" s="40"/>
+      <c r="F55" s="69"/>
       <c r="H55" s="18"/>
       <c r="I55" s="27"/>
       <c r="J55" s="18"/>
@@ -16204,15 +16598,15 @@
         <v>35</v>
       </c>
       <c r="B56" s="6"/>
-      <c r="C56" s="38">
+      <c r="C56" s="76">
         <v>2.5</v>
       </c>
-      <c r="D56" s="38"/>
-      <c r="E56" s="39">
+      <c r="D56" s="76"/>
+      <c r="E56" s="57">
         <f t="shared" ref="E56" si="0">(B56-0.0164)/0.0093</f>
         <v>-1.763440860215054</v>
       </c>
-      <c r="F56" s="40"/>
+      <c r="F56" s="58"/>
       <c r="H56" s="18"/>
       <c r="I56" s="27"/>
       <c r="J56" s="18"/>
@@ -16224,15 +16618,15 @@
       <c r="B57" s="6">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="C57" s="38">
+      <c r="C57" s="76">
         <v>5</v>
       </c>
-      <c r="D57" s="38"/>
-      <c r="E57" s="39">
+      <c r="D57" s="76"/>
+      <c r="E57" s="57">
         <f>(B57-0.0164)/0.0093</f>
         <v>2.0000000000000004</v>
       </c>
-      <c r="F57" s="40"/>
+      <c r="F57" s="58"/>
       <c r="H57" s="18">
         <f>C57/1000000</f>
         <v>5.0000000000000004E-6</v>
@@ -16253,15 +16647,15 @@
       <c r="B58" s="6">
         <v>8.3000000000000004E-2</v>
       </c>
-      <c r="C58" s="38">
+      <c r="C58" s="76">
         <v>10</v>
       </c>
-      <c r="D58" s="38"/>
-      <c r="E58" s="44">
+      <c r="D58" s="76"/>
+      <c r="E58" s="50">
         <f t="shared" ref="E58:E62" si="1">(B58-0.0164)/0.0093</f>
         <v>7.1612903225806468</v>
       </c>
-      <c r="F58" s="45"/>
+      <c r="F58" s="51"/>
       <c r="H58" s="18">
         <f>C58/1000000</f>
         <v>1.0000000000000001E-5</v>
@@ -16280,15 +16674,15 @@
         <v>36</v>
       </c>
       <c r="B59" s="6"/>
-      <c r="C59" s="38">
+      <c r="C59" s="76">
         <v>25</v>
       </c>
-      <c r="D59" s="38"/>
-      <c r="E59" s="44">
+      <c r="D59" s="76"/>
+      <c r="E59" s="50">
         <f t="shared" si="1"/>
         <v>-1.763440860215054</v>
       </c>
-      <c r="F59" s="45"/>
+      <c r="F59" s="51"/>
       <c r="H59" s="18"/>
       <c r="I59" s="18"/>
       <c r="J59" s="21"/>
@@ -16300,15 +16694,15 @@
       <c r="B60" s="6">
         <v>0.48499999999999999</v>
       </c>
-      <c r="C60" s="38">
+      <c r="C60" s="76">
         <v>50</v>
       </c>
-      <c r="D60" s="38"/>
-      <c r="E60" s="44">
+      <c r="D60" s="76"/>
+      <c r="E60" s="50">
         <f t="shared" si="1"/>
         <v>50.387096774193552</v>
       </c>
-      <c r="F60" s="45"/>
+      <c r="F60" s="51"/>
       <c r="H60" s="18">
         <f>C60/1000000</f>
         <v>5.0000000000000002E-5</v>
@@ -16329,15 +16723,15 @@
       <c r="B61" s="6">
         <v>0.96499999999999997</v>
       </c>
-      <c r="C61" s="38">
+      <c r="C61" s="76">
         <v>100</v>
       </c>
-      <c r="D61" s="38"/>
-      <c r="E61" s="44">
+      <c r="D61" s="76"/>
+      <c r="E61" s="50">
         <f t="shared" si="1"/>
         <v>102.00000000000001</v>
       </c>
-      <c r="F61" s="45"/>
+      <c r="F61" s="51"/>
       <c r="H61" s="18">
         <f>C61/1000000</f>
         <v>1E-4</v>
@@ -16358,15 +16752,15 @@
       <c r="B62" s="8">
         <v>1.8340000000000001</v>
       </c>
-      <c r="C62" s="47">
+      <c r="C62" s="52">
         <v>200</v>
       </c>
-      <c r="D62" s="48"/>
-      <c r="E62" s="62">
+      <c r="D62" s="53"/>
+      <c r="E62" s="54">
         <f t="shared" si="1"/>
         <v>195.44086021505379</v>
       </c>
-      <c r="F62" s="63"/>
+      <c r="F62" s="55"/>
       <c r="H62" s="19">
         <f>C62/1000000</f>
         <v>2.0000000000000001E-4</v>
@@ -16381,18 +16775,18 @@
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A63" s="9" t="s">
+      <c r="A63" s="41" t="s">
         <v>77</v>
       </c>
       <c r="B63" s="9">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="C63" s="49"/>
-      <c r="D63" s="50"/>
-      <c r="E63" s="55">
+      <c r="C63" s="72"/>
+      <c r="D63" s="73"/>
+      <c r="E63" s="74">
         <v>0</v>
       </c>
-      <c r="F63" s="55"/>
+      <c r="F63" s="75"/>
       <c r="H63" s="18">
         <f t="shared" ref="H63:H70" si="4">E63/1000000</f>
         <v>0</v>
@@ -16407,18 +16801,18 @@
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A64" s="6" t="s">
+      <c r="A64" s="5" t="s">
         <v>78</v>
       </c>
       <c r="B64" s="6">
         <v>2E-3</v>
       </c>
-      <c r="C64" s="41"/>
-      <c r="D64" s="42"/>
-      <c r="E64" s="39">
+      <c r="C64" s="48"/>
+      <c r="D64" s="56"/>
+      <c r="E64" s="57">
         <v>0</v>
       </c>
-      <c r="F64" s="39"/>
+      <c r="F64" s="58"/>
       <c r="H64" s="18">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -16433,18 +16827,18 @@
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A65" s="6" t="s">
+      <c r="A65" s="5" t="s">
         <v>79</v>
       </c>
       <c r="B65" s="6">
         <v>2E-3</v>
       </c>
-      <c r="C65" s="41"/>
-      <c r="D65" s="42"/>
-      <c r="E65" s="39">
+      <c r="C65" s="48"/>
+      <c r="D65" s="56"/>
+      <c r="E65" s="57">
         <v>0</v>
       </c>
-      <c r="F65" s="39"/>
+      <c r="F65" s="58"/>
       <c r="H65" s="18">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -16459,18 +16853,18 @@
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A66" s="6" t="s">
+      <c r="A66" s="5" t="s">
         <v>80</v>
       </c>
       <c r="B66" s="6">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="C66" s="41"/>
-      <c r="D66" s="42"/>
-      <c r="E66" s="39">
+      <c r="C66" s="48"/>
+      <c r="D66" s="56"/>
+      <c r="E66" s="57">
         <v>0</v>
       </c>
-      <c r="F66" s="39"/>
+      <c r="F66" s="58"/>
       <c r="H66" s="18">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -16485,19 +16879,19 @@
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A67" s="6" t="s">
+      <c r="A67" s="5" t="s">
         <v>81</v>
       </c>
       <c r="B67" s="6">
         <v>0.109</v>
       </c>
-      <c r="C67" s="41"/>
-      <c r="D67" s="42"/>
-      <c r="E67" s="39">
+      <c r="C67" s="48"/>
+      <c r="D67" s="56"/>
+      <c r="E67" s="57">
         <f t="shared" ref="E67:E70" si="7">(B67-0.0164)/0.0093</f>
         <v>9.9569892473118298</v>
       </c>
-      <c r="F67" s="39"/>
+      <c r="F67" s="58"/>
       <c r="H67" s="18">
         <f t="shared" si="4"/>
         <v>9.9569892473118294E-6</v>
@@ -16512,19 +16906,19 @@
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A68" s="6" t="s">
+      <c r="A68" s="5" t="s">
         <v>82</v>
       </c>
       <c r="B68" s="6">
         <v>0.36</v>
       </c>
-      <c r="C68" s="41"/>
-      <c r="D68" s="42"/>
-      <c r="E68" s="39">
+      <c r="C68" s="48"/>
+      <c r="D68" s="56"/>
+      <c r="E68" s="57">
         <f t="shared" si="7"/>
         <v>36.946236559139784</v>
       </c>
-      <c r="F68" s="39"/>
+      <c r="F68" s="58"/>
       <c r="H68" s="18">
         <f t="shared" si="4"/>
         <v>3.6946236559139785E-5</v>
@@ -16539,19 +16933,19 @@
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A69" s="6" t="s">
+      <c r="A69" s="5" t="s">
         <v>83</v>
       </c>
       <c r="B69" s="6">
         <v>0.91300000000000003</v>
       </c>
-      <c r="C69" s="41"/>
-      <c r="D69" s="42"/>
-      <c r="E69" s="39">
+      <c r="C69" s="48"/>
+      <c r="D69" s="56"/>
+      <c r="E69" s="57">
         <f t="shared" si="7"/>
         <v>96.408602150537646</v>
       </c>
-      <c r="F69" s="39"/>
+      <c r="F69" s="58"/>
       <c r="H69" s="18">
         <f t="shared" si="4"/>
         <v>9.6408602150537646E-5</v>
@@ -16565,20 +16959,20 @@
         <v>1.7390627135483876</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A70" s="6" t="s">
+    <row r="70" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="B70" s="6">
+      <c r="B70" s="8">
         <v>4.7E-2</v>
       </c>
-      <c r="C70" s="41"/>
-      <c r="D70" s="42"/>
-      <c r="E70" s="39">
+      <c r="C70" s="52"/>
+      <c r="D70" s="59"/>
+      <c r="E70" s="60">
         <f t="shared" si="7"/>
         <v>3.2903225806451615</v>
       </c>
-      <c r="F70" s="39"/>
+      <c r="F70" s="61"/>
       <c r="H70" s="18">
         <f t="shared" si="4"/>
         <v>3.2903225806451615E-6</v>
@@ -16616,7 +17010,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="I99" s="16" t="s">
         <v>22</v>
       </c>
@@ -16628,28 +17022,27 @@
       </c>
     </row>
     <row r="100" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="2" t="s">
+      <c r="A100" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B100" s="2" t="s">
+      <c r="B100" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C100" s="2" t="s">
+      <c r="C100" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="D100" s="2"/>
-      <c r="E100" s="2" t="s">
+      <c r="D100" s="29"/>
+      <c r="E100" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="F100" s="2"/>
-      <c r="G100" s="35"/>
-      <c r="I100" s="17" t="s">
+      <c r="F100" s="30"/>
+      <c r="I100" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="J100" s="17" t="s">
+      <c r="J100" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="K100" s="17" t="s">
+      <c r="K100" s="27" t="s">
         <v>21</v>
       </c>
     </row>
@@ -16664,11 +17057,11 @@
         <v>0.5</v>
       </c>
       <c r="D101" s="11"/>
-      <c r="E101" s="51">
+      <c r="E101" s="68">
         <f>(B101+0.0049)/0.0204</f>
         <v>0.28921568627450978</v>
       </c>
-      <c r="F101" s="52"/>
+      <c r="F101" s="69"/>
       <c r="I101" s="16">
         <f t="shared" ref="I101:I106" si="8">C101/1000000</f>
         <v>4.9999999999999998E-7</v>
@@ -16693,11 +17086,11 @@
         <v>1</v>
       </c>
       <c r="D102" s="13"/>
-      <c r="E102" s="39">
+      <c r="E102" s="57">
         <f t="shared" ref="E102:E114" si="10">(B102+0.0049)/0.0204</f>
         <v>1.0245098039215685</v>
       </c>
-      <c r="F102" s="40"/>
+      <c r="F102" s="58"/>
       <c r="I102" s="18">
         <f t="shared" si="8"/>
         <v>9.9999999999999995E-7</v>
@@ -16722,11 +17115,11 @@
         <v>5</v>
       </c>
       <c r="D103" s="13"/>
-      <c r="E103" s="39">
+      <c r="E103" s="57">
         <f t="shared" si="10"/>
         <v>4.6029411764705879</v>
       </c>
-      <c r="F103" s="40"/>
+      <c r="F103" s="58"/>
       <c r="I103" s="18">
         <f t="shared" si="8"/>
         <v>5.0000000000000004E-6</v>
@@ -16751,11 +17144,11 @@
         <v>10</v>
       </c>
       <c r="D104" s="13"/>
-      <c r="E104" s="39">
+      <c r="E104" s="57">
         <f t="shared" si="10"/>
         <v>10.877450980392155</v>
       </c>
-      <c r="F104" s="40"/>
+      <c r="F104" s="58"/>
       <c r="I104" s="18">
         <f t="shared" si="8"/>
         <v>1.0000000000000001E-5</v>
@@ -16769,7 +17162,7 @@
         <v>0.94973000000000007</v>
       </c>
     </row>
-    <row r="105" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A105" s="31" t="s">
         <v>12</v>
       </c>
@@ -16780,20 +17173,20 @@
         <v>25</v>
       </c>
       <c r="D105" s="33"/>
-      <c r="E105" s="39">
+      <c r="E105" s="57">
         <f t="shared" si="10"/>
         <v>24.799019607843135</v>
       </c>
-      <c r="F105" s="40"/>
-      <c r="I105" s="19">
+      <c r="F105" s="58"/>
+      <c r="I105" s="18">
         <f t="shared" si="8"/>
         <v>2.5000000000000001E-5</v>
       </c>
-      <c r="J105" s="19">
+      <c r="J105" s="18">
         <f t="shared" si="9"/>
         <v>2.374325E-3</v>
       </c>
-      <c r="K105" s="22">
+      <c r="K105" s="21">
         <f t="shared" si="11"/>
         <v>2.3743250000000002</v>
       </c>
@@ -16809,38 +17202,38 @@
         <v>50</v>
       </c>
       <c r="D106" s="15"/>
-      <c r="E106" s="53">
+      <c r="E106" s="60">
         <f t="shared" si="10"/>
         <v>37.446078431372548</v>
       </c>
-      <c r="F106" s="54"/>
-      <c r="I106" s="18">
+      <c r="F106" s="61"/>
+      <c r="I106" s="19">
         <f t="shared" si="8"/>
         <v>5.0000000000000002E-5</v>
       </c>
-      <c r="J106" s="18">
+      <c r="J106" s="19">
         <f t="shared" si="9"/>
         <v>4.7486500000000001E-3</v>
       </c>
-      <c r="K106" s="21">
+      <c r="K106" s="22">
         <f t="shared" si="11"/>
         <v>4.7486500000000005</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A107" s="9" t="s">
+      <c r="A107" s="41" t="s">
         <v>77</v>
       </c>
       <c r="B107" s="9">
         <v>0</v>
       </c>
-      <c r="C107" s="49"/>
-      <c r="D107" s="50"/>
-      <c r="E107" s="55">
+      <c r="C107" s="72"/>
+      <c r="D107" s="73"/>
+      <c r="E107" s="74">
         <f t="shared" si="10"/>
         <v>0.24019607843137253</v>
       </c>
-      <c r="F107" s="55"/>
+      <c r="F107" s="75"/>
       <c r="I107" s="18">
         <f>E107/1000000</f>
         <v>2.4019607843137255E-7</v>
@@ -16855,19 +17248,19 @@
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A108" s="6" t="s">
+      <c r="A108" s="5" t="s">
         <v>78</v>
       </c>
       <c r="B108" s="6">
         <v>0</v>
       </c>
-      <c r="C108" s="41"/>
-      <c r="D108" s="42"/>
-      <c r="E108" s="39">
+      <c r="C108" s="48"/>
+      <c r="D108" s="56"/>
+      <c r="E108" s="57">
         <f t="shared" si="10"/>
         <v>0.24019607843137253</v>
       </c>
-      <c r="F108" s="39"/>
+      <c r="F108" s="58"/>
       <c r="I108" s="18">
         <f t="shared" ref="I108:I114" si="12">E108/1000000</f>
         <v>2.4019607843137255E-7</v>
@@ -16882,19 +17275,19 @@
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A109" s="6" t="s">
+      <c r="A109" s="5" t="s">
         <v>79</v>
       </c>
       <c r="B109" s="6">
         <v>0</v>
       </c>
-      <c r="C109" s="41"/>
-      <c r="D109" s="42"/>
-      <c r="E109" s="39">
+      <c r="C109" s="48"/>
+      <c r="D109" s="56"/>
+      <c r="E109" s="57">
         <f t="shared" si="10"/>
         <v>0.24019607843137253</v>
       </c>
-      <c r="F109" s="39"/>
+      <c r="F109" s="58"/>
       <c r="I109" s="18">
         <f t="shared" si="12"/>
         <v>2.4019607843137255E-7</v>
@@ -16909,19 +17302,19 @@
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A110" s="6" t="s">
+      <c r="A110" s="5" t="s">
         <v>80</v>
       </c>
       <c r="B110" s="6">
         <v>0</v>
       </c>
-      <c r="C110" s="41"/>
-      <c r="D110" s="42"/>
-      <c r="E110" s="39">
+      <c r="C110" s="48"/>
+      <c r="D110" s="56"/>
+      <c r="E110" s="57">
         <f t="shared" si="10"/>
         <v>0.24019607843137253</v>
       </c>
-      <c r="F110" s="39"/>
+      <c r="F110" s="58"/>
       <c r="I110" s="18">
         <f t="shared" si="12"/>
         <v>2.4019607843137255E-7</v>
@@ -16936,19 +17329,19 @@
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A111" s="6" t="s">
+      <c r="A111" s="5" t="s">
         <v>81</v>
       </c>
       <c r="B111" s="6">
         <v>1.4E-2</v>
       </c>
-      <c r="C111" s="41"/>
-      <c r="D111" s="42"/>
-      <c r="E111" s="39">
+      <c r="C111" s="48"/>
+      <c r="D111" s="56"/>
+      <c r="E111" s="57">
         <f t="shared" si="10"/>
         <v>0.92647058823529405</v>
       </c>
-      <c r="F111" s="39"/>
+      <c r="F111" s="58"/>
       <c r="I111" s="18">
         <f t="shared" si="12"/>
         <v>9.2647058823529408E-7</v>
@@ -16963,19 +17356,19 @@
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A112" s="6" t="s">
+      <c r="A112" s="5" t="s">
         <v>82</v>
       </c>
       <c r="B112" s="6">
         <v>8.9999999999999993E-3</v>
       </c>
-      <c r="C112" s="41"/>
-      <c r="D112" s="42"/>
-      <c r="E112" s="39">
+      <c r="C112" s="48"/>
+      <c r="D112" s="56"/>
+      <c r="E112" s="57">
         <f t="shared" si="10"/>
         <v>0.68137254901960775</v>
       </c>
-      <c r="F112" s="39"/>
+      <c r="F112" s="58"/>
       <c r="I112" s="18">
         <f t="shared" si="12"/>
         <v>6.8137254901960776E-7</v>
@@ -16990,19 +17383,19 @@
       </c>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A113" s="6" t="s">
+      <c r="A113" s="5" t="s">
         <v>83</v>
       </c>
       <c r="B113" s="6">
         <v>3.9E-2</v>
       </c>
-      <c r="C113" s="41"/>
-      <c r="D113" s="42"/>
-      <c r="E113" s="39">
+      <c r="C113" s="48"/>
+      <c r="D113" s="56"/>
+      <c r="E113" s="57">
         <f t="shared" si="10"/>
         <v>2.1519607843137254</v>
       </c>
-      <c r="F113" s="39"/>
+      <c r="F113" s="58"/>
       <c r="I113" s="18">
         <f t="shared" si="12"/>
         <v>2.1519607843137253E-6</v>
@@ -17016,20 +17409,20 @@
         <v>3.881805852941176E-2</v>
       </c>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A114" s="6" t="s">
+    <row r="114" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A114" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="B114" s="6">
+      <c r="B114" s="8">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="C114" s="41"/>
-      <c r="D114" s="42"/>
-      <c r="E114" s="39">
+      <c r="C114" s="52"/>
+      <c r="D114" s="59"/>
+      <c r="E114" s="60">
         <f t="shared" si="10"/>
         <v>0.53431372549019607</v>
       </c>
-      <c r="F114" s="39"/>
+      <c r="F114" s="61"/>
       <c r="I114" s="18">
         <f t="shared" si="12"/>
         <v>5.3431372549019611E-7</v>
@@ -17043,37 +17436,71 @@
         <v>9.6381967647058819E-3</v>
       </c>
     </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="I118" t="s">
+        <v>25</v>
+      </c>
+      <c r="K118">
+        <v>62.005400000000002</v>
+      </c>
+    </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.25">
       <c r="H119" s="24"/>
-    </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A120" s="46" t="s">
+      <c r="I119" t="s">
+        <v>16</v>
+      </c>
+      <c r="K119">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A120" s="70" t="s">
         <v>27</v>
       </c>
-      <c r="B120" s="46"/>
-      <c r="C120" s="46"/>
-      <c r="D120" s="46"/>
-      <c r="E120" s="46"/>
-      <c r="F120" s="46"/>
-      <c r="G120" s="46"/>
-      <c r="H120" s="46"/>
+      <c r="B120" s="70"/>
+      <c r="C120" s="70"/>
+      <c r="D120" s="70"/>
+      <c r="E120" s="70"/>
+      <c r="F120" s="70"/>
+      <c r="G120" s="70"/>
+      <c r="H120" s="70"/>
+    </row>
+    <row r="121" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I121" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="J121" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K121" s="20" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="122" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="2" t="s">
+      <c r="A122" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B122" s="2" t="s">
+      <c r="B122" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C122" s="2" t="s">
+      <c r="C122" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="D122" s="2"/>
-      <c r="E122" s="2" t="s">
+      <c r="D122" s="29"/>
+      <c r="E122" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="F122" s="2"/>
-      <c r="G122" s="37"/>
+      <c r="F122" s="30"/>
+      <c r="G122" s="35"/>
+      <c r="I122" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="J122" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="K122" s="17" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A123" s="3" t="s">
@@ -17082,15 +17509,27 @@
       <c r="B123" s="4">
         <v>0</v>
       </c>
-      <c r="C123" s="56">
+      <c r="C123" s="62">
         <v>2.5</v>
       </c>
-      <c r="D123" s="57"/>
-      <c r="E123" s="51">
+      <c r="D123" s="63"/>
+      <c r="E123" s="68">
         <v>0</v>
       </c>
-      <c r="F123" s="52"/>
-      <c r="G123" s="36"/>
+      <c r="F123" s="69"/>
+      <c r="G123" s="35"/>
+      <c r="I123" s="16">
+        <f t="shared" ref="I123:I130" si="15">C123/1000000</f>
+        <v>2.5000000000000002E-6</v>
+      </c>
+      <c r="J123" s="16">
+        <f>$K$118*I123</f>
+        <v>1.5501350000000002E-4</v>
+      </c>
+      <c r="K123" s="23">
+        <f>J123*1000</f>
+        <v>0.15501350000000003</v>
+      </c>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A124" s="31" t="s">
@@ -17099,16 +17538,28 @@
       <c r="B124" s="2">
         <v>1E-3</v>
       </c>
-      <c r="C124" s="58">
+      <c r="C124" s="66">
         <v>5</v>
       </c>
-      <c r="D124" s="59"/>
-      <c r="E124" s="44">
-        <f t="shared" ref="E124:E138" si="15">(B124+0.0067)/0.0019</f>
+      <c r="D124" s="67"/>
+      <c r="E124" s="50">
+        <f t="shared" ref="E124:E138" si="16">(B124+0.0067)/0.0019</f>
         <v>4.0526315789473681</v>
       </c>
-      <c r="F124" s="45"/>
-      <c r="G124" s="36"/>
+      <c r="F124" s="51"/>
+      <c r="G124" s="35"/>
+      <c r="I124" s="18">
+        <f t="shared" si="15"/>
+        <v>5.0000000000000004E-6</v>
+      </c>
+      <c r="J124" s="18">
+        <f>$K$118*I124</f>
+        <v>3.1002700000000005E-4</v>
+      </c>
+      <c r="K124" s="21">
+        <f t="shared" ref="K124:K130" si="17">J124*1000</f>
+        <v>0.31002700000000005</v>
+      </c>
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A125" s="5" t="s">
@@ -17117,16 +17568,28 @@
       <c r="B125" s="6">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="C125" s="41">
+      <c r="C125" s="48">
         <v>10</v>
       </c>
-      <c r="D125" s="43"/>
-      <c r="E125" s="44">
+      <c r="D125" s="49"/>
+      <c r="E125" s="50">
+        <f t="shared" si="16"/>
+        <v>7.7368421052631584</v>
+      </c>
+      <c r="F125" s="51"/>
+      <c r="G125" s="35"/>
+      <c r="I125" s="18">
         <f t="shared" si="15"/>
-        <v>7.7368421052631584</v>
-      </c>
-      <c r="F125" s="45"/>
-      <c r="G125" s="36"/>
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="J125" s="18">
+        <f t="shared" ref="J125:J130" si="18">$K$118*I125</f>
+        <v>6.2005400000000009E-4</v>
+      </c>
+      <c r="K125" s="21">
+        <f t="shared" si="17"/>
+        <v>0.62005400000000011</v>
+      </c>
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A126" s="5" t="s">
@@ -17135,16 +17598,28 @@
       <c r="B126" s="6">
         <v>4.1000000000000002E-2</v>
       </c>
-      <c r="C126" s="41">
+      <c r="C126" s="48">
         <v>25</v>
       </c>
-      <c r="D126" s="43"/>
-      <c r="E126" s="44">
+      <c r="D126" s="49"/>
+      <c r="E126" s="50">
+        <f t="shared" si="16"/>
+        <v>25.105263157894736</v>
+      </c>
+      <c r="F126" s="51"/>
+      <c r="G126" s="35"/>
+      <c r="I126" s="18">
         <f t="shared" si="15"/>
-        <v>25.105263157894736</v>
-      </c>
-      <c r="F126" s="45"/>
-      <c r="G126" s="36"/>
+        <v>2.5000000000000001E-5</v>
+      </c>
+      <c r="J126" s="18">
+        <f t="shared" si="18"/>
+        <v>1.550135E-3</v>
+      </c>
+      <c r="K126" s="21">
+        <f t="shared" si="17"/>
+        <v>1.550135</v>
+      </c>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A127" s="5" t="s">
@@ -17153,16 +17628,28 @@
       <c r="B127" s="6">
         <v>8.3000000000000004E-2</v>
       </c>
-      <c r="C127" s="41">
+      <c r="C127" s="48">
         <v>50</v>
       </c>
-      <c r="D127" s="43"/>
-      <c r="E127" s="44">
+      <c r="D127" s="49"/>
+      <c r="E127" s="50">
+        <f t="shared" si="16"/>
+        <v>47.210526315789473</v>
+      </c>
+      <c r="F127" s="51"/>
+      <c r="G127" s="35"/>
+      <c r="I127" s="18">
         <f t="shared" si="15"/>
-        <v>47.210526315789473</v>
-      </c>
-      <c r="F127" s="45"/>
-      <c r="G127" s="36"/>
+        <v>5.0000000000000002E-5</v>
+      </c>
+      <c r="J127" s="18">
+        <f t="shared" si="18"/>
+        <v>3.10027E-3</v>
+      </c>
+      <c r="K127" s="21">
+        <f t="shared" si="17"/>
+        <v>3.1002700000000001</v>
+      </c>
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A128" s="5" t="s">
@@ -17171,176 +17658,308 @@
       <c r="B128" s="6">
         <v>0.17499999999999999</v>
       </c>
-      <c r="C128" s="41">
+      <c r="C128" s="48">
         <v>100</v>
       </c>
-      <c r="D128" s="43"/>
-      <c r="E128" s="44">
+      <c r="D128" s="49"/>
+      <c r="E128" s="50">
+        <f t="shared" si="16"/>
+        <v>95.631578947368425</v>
+      </c>
+      <c r="F128" s="51"/>
+      <c r="G128" s="35"/>
+      <c r="I128" s="18">
         <f t="shared" si="15"/>
-        <v>95.631578947368425</v>
-      </c>
-      <c r="F128" s="45"/>
-      <c r="G128" s="36"/>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+        <v>1E-4</v>
+      </c>
+      <c r="J128" s="18">
+        <f t="shared" si="18"/>
+        <v>6.20054E-3</v>
+      </c>
+      <c r="K128" s="21">
+        <f t="shared" si="17"/>
+        <v>6.2005400000000002</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A129" s="5" t="s">
         <v>5</v>
       </c>
       <c r="B129" s="6">
         <v>0.375</v>
       </c>
-      <c r="C129" s="41">
+      <c r="C129" s="48">
         <v>200</v>
       </c>
-      <c r="D129" s="43"/>
-      <c r="E129" s="44">
+      <c r="D129" s="49"/>
+      <c r="E129" s="50">
+        <f t="shared" si="16"/>
+        <v>200.89473684210526</v>
+      </c>
+      <c r="F129" s="51"/>
+      <c r="G129" s="35"/>
+      <c r="I129" s="18">
         <f t="shared" si="15"/>
-        <v>200.89473684210526</v>
-      </c>
-      <c r="F129" s="45"/>
-      <c r="G129" s="36"/>
-    </row>
-    <row r="130" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="J129" s="18">
+        <f t="shared" si="18"/>
+        <v>1.240108E-2</v>
+      </c>
+      <c r="K129" s="21">
+        <f t="shared" si="17"/>
+        <v>12.40108</v>
+      </c>
+    </row>
+    <row r="130" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A130" s="7" t="s">
         <v>6</v>
       </c>
       <c r="B130" s="8">
         <v>0.91500000000000004</v>
       </c>
-      <c r="C130" s="47">
+      <c r="C130" s="52">
         <v>500</v>
       </c>
-      <c r="D130" s="48"/>
-      <c r="E130" s="62">
+      <c r="D130" s="53"/>
+      <c r="E130" s="54">
+        <f t="shared" si="16"/>
+        <v>485.1052631578948</v>
+      </c>
+      <c r="F130" s="55"/>
+      <c r="G130" s="35"/>
+      <c r="I130" s="19">
         <f t="shared" si="15"/>
-        <v>485.1052631578948</v>
-      </c>
-      <c r="F130" s="63"/>
-      <c r="G130" s="36"/>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A131" s="9" t="s">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="J130" s="19">
+        <f t="shared" si="18"/>
+        <v>3.1002700000000001E-2</v>
+      </c>
+      <c r="K130" s="22">
+        <f t="shared" si="17"/>
+        <v>31.002700000000001</v>
+      </c>
+    </row>
+    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A131" s="41" t="s">
         <v>77</v>
       </c>
       <c r="B131" s="9">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="C131" s="49"/>
-      <c r="D131" s="60"/>
+      <c r="C131" s="72"/>
+      <c r="D131" s="78"/>
       <c r="E131" s="64">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>9.3157894736842106</v>
       </c>
       <c r="F131" s="65"/>
-      <c r="G131" s="36"/>
-    </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A132" s="6" t="s">
+      <c r="G131" s="35"/>
+      <c r="I131" s="18">
+        <f>E131/1000000</f>
+        <v>9.3157894736842104E-6</v>
+      </c>
+      <c r="J131" s="18">
+        <f>$K$118*I131*$K$119</f>
+        <v>5.776292526315789E-7</v>
+      </c>
+      <c r="K131" s="21">
+        <f t="shared" ref="K131:K138" si="19">J131*1000000</f>
+        <v>0.57762925263157894</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A132" s="5" t="s">
         <v>78</v>
       </c>
       <c r="B132" s="6">
         <v>0</v>
       </c>
-      <c r="C132" s="41"/>
-      <c r="D132" s="43"/>
-      <c r="E132" s="44">
+      <c r="C132" s="48"/>
+      <c r="D132" s="49"/>
+      <c r="E132" s="50">
         <v>0</v>
       </c>
-      <c r="F132" s="61"/>
-      <c r="G132" s="36"/>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A133" s="6" t="s">
+      <c r="F132" s="51"/>
+      <c r="G132" s="35"/>
+      <c r="I132" s="18">
+        <f>E132/1000000</f>
+        <v>0</v>
+      </c>
+      <c r="J132" s="18">
+        <f t="shared" ref="J132:J138" si="20">$K$118*I132*$K$119</f>
+        <v>0</v>
+      </c>
+      <c r="K132" s="21">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A133" s="5" t="s">
         <v>79</v>
       </c>
       <c r="B133" s="6">
         <v>0</v>
       </c>
-      <c r="C133" s="41"/>
-      <c r="D133" s="43"/>
-      <c r="E133" s="44">
+      <c r="C133" s="48"/>
+      <c r="D133" s="49"/>
+      <c r="E133" s="50">
         <v>0</v>
       </c>
-      <c r="F133" s="61"/>
-      <c r="G133" s="36"/>
-    </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A134" s="6" t="s">
+      <c r="F133" s="51"/>
+      <c r="G133" s="35"/>
+      <c r="I133" s="18">
+        <f t="shared" ref="I133:I138" si="21">E133/1000000</f>
+        <v>0</v>
+      </c>
+      <c r="J133" s="18">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="K133" s="21">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A134" s="5" t="s">
         <v>80</v>
       </c>
       <c r="B134" s="6">
         <v>0</v>
       </c>
-      <c r="C134" s="41"/>
-      <c r="D134" s="43"/>
-      <c r="E134" s="44">
+      <c r="C134" s="48"/>
+      <c r="D134" s="49"/>
+      <c r="E134" s="50">
         <v>0</v>
       </c>
-      <c r="F134" s="61"/>
-      <c r="G134" s="36"/>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A135" s="6" t="s">
+      <c r="F134" s="51"/>
+      <c r="G134" s="35"/>
+      <c r="I134" s="18">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="J134" s="18">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="K134" s="21">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A135" s="5" t="s">
         <v>81</v>
       </c>
       <c r="B135" s="6">
         <v>0</v>
       </c>
-      <c r="C135" s="41"/>
-      <c r="D135" s="43"/>
-      <c r="E135" s="44">
+      <c r="C135" s="48"/>
+      <c r="D135" s="49"/>
+      <c r="E135" s="50">
         <v>0</v>
       </c>
-      <c r="F135" s="61"/>
-      <c r="G135" s="36"/>
-    </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A136" s="6" t="s">
+      <c r="F135" s="51"/>
+      <c r="G135" s="35"/>
+      <c r="I135" s="18">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="J135" s="18">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="K135" s="21">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A136" s="5" t="s">
         <v>82</v>
       </c>
       <c r="B136" s="6">
         <v>1.7999999999999999E-2</v>
       </c>
-      <c r="C136" s="41"/>
-      <c r="D136" s="43"/>
-      <c r="E136" s="44">
-        <f t="shared" si="15"/>
+      <c r="C136" s="48"/>
+      <c r="D136" s="49"/>
+      <c r="E136" s="50">
+        <f t="shared" si="16"/>
         <v>13</v>
       </c>
-      <c r="F136" s="61"/>
-      <c r="G136" s="36"/>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A137" s="6" t="s">
+      <c r="F136" s="51"/>
+      <c r="G136" s="35"/>
+      <c r="I136" s="18">
+        <f t="shared" si="21"/>
+        <v>1.2999999999999999E-5</v>
+      </c>
+      <c r="J136" s="18">
+        <f t="shared" si="20"/>
+        <v>8.060702E-7</v>
+      </c>
+      <c r="K136" s="21">
+        <f t="shared" si="19"/>
+        <v>0.80607019999999996</v>
+      </c>
+    </row>
+    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A137" s="5" t="s">
         <v>83</v>
       </c>
       <c r="B137" s="6">
         <v>2.8000000000000001E-2</v>
       </c>
-      <c r="C137" s="41"/>
-      <c r="D137" s="43"/>
-      <c r="E137" s="44">
-        <f t="shared" si="15"/>
+      <c r="C137" s="48"/>
+      <c r="D137" s="49"/>
+      <c r="E137" s="50">
+        <f t="shared" si="16"/>
         <v>18.263157894736842</v>
       </c>
-      <c r="F137" s="61"/>
-      <c r="G137" s="36"/>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A138" s="6" t="s">
+      <c r="F137" s="51"/>
+      <c r="G137" s="35"/>
+      <c r="I137" s="18">
+        <f t="shared" si="21"/>
+        <v>1.8263157894736844E-5</v>
+      </c>
+      <c r="J137" s="18">
+        <f t="shared" si="20"/>
+        <v>1.1324144105263159E-6</v>
+      </c>
+      <c r="K137" s="21">
+        <f t="shared" si="19"/>
+        <v>1.1324144105263159</v>
+      </c>
+    </row>
+    <row r="138" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A138" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="B138" s="6">
+      <c r="B138" s="8">
         <v>2.7E-2</v>
       </c>
-      <c r="C138" s="41"/>
-      <c r="D138" s="43"/>
-      <c r="E138" s="44">
-        <f t="shared" si="15"/>
+      <c r="C138" s="52"/>
+      <c r="D138" s="53"/>
+      <c r="E138" s="54">
+        <f t="shared" si="16"/>
         <v>17.736842105263158</v>
       </c>
-      <c r="F138" s="61"/>
-      <c r="G138" s="36"/>
+      <c r="F138" s="55"/>
+      <c r="G138" s="35"/>
+      <c r="I138" s="18">
+        <f t="shared" si="21"/>
+        <v>1.7736842105263157E-5</v>
+      </c>
+      <c r="J138" s="18">
+        <f t="shared" si="20"/>
+        <v>1.0997799894736841E-6</v>
+      </c>
+      <c r="K138" s="21">
+        <f t="shared" si="19"/>
+        <v>1.0997799894736842</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="88">
@@ -17454,16 +18073,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="70" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
       <c r="I1" s="1"/>
     </row>
     <row r="2" spans="1:9" s="25" customFormat="1" x14ac:dyDescent="0.25">
@@ -17646,7 +18265,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="28" t="s">
         <v>0</v>
       </c>
@@ -17668,18 +18287,18 @@
       <c r="J55" s="16"/>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A56" s="5" t="s">
+      <c r="A56" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B56" s="6"/>
-      <c r="C56" s="38">
+      <c r="B56" s="4"/>
+      <c r="C56" s="77">
         <v>1</v>
       </c>
-      <c r="D56" s="38"/>
-      <c r="E56" s="39">
+      <c r="D56" s="77"/>
+      <c r="E56" s="68">
         <v>0</v>
       </c>
-      <c r="F56" s="40"/>
+      <c r="F56" s="69"/>
       <c r="H56" s="18"/>
       <c r="I56" s="27"/>
       <c r="J56" s="18"/>
@@ -17689,15 +18308,15 @@
         <v>35</v>
       </c>
       <c r="B57" s="6"/>
-      <c r="C57" s="38">
+      <c r="C57" s="76">
         <v>2.5</v>
       </c>
-      <c r="D57" s="38"/>
-      <c r="E57" s="39">
+      <c r="D57" s="76"/>
+      <c r="E57" s="57">
         <f>(B57+0.0048)/0.0096</f>
         <v>0.5</v>
       </c>
-      <c r="F57" s="40"/>
+      <c r="F57" s="58"/>
       <c r="H57" s="18"/>
       <c r="I57" s="27"/>
       <c r="J57" s="18"/>
@@ -17709,15 +18328,15 @@
       <c r="B58" s="6">
         <v>3.5999999999999997E-2</v>
       </c>
-      <c r="C58" s="38">
+      <c r="C58" s="76">
         <v>5</v>
       </c>
-      <c r="D58" s="38"/>
-      <c r="E58" s="39">
+      <c r="D58" s="76"/>
+      <c r="E58" s="57">
         <f>(B58+0.0048)/0.0096</f>
         <v>4.25</v>
       </c>
-      <c r="F58" s="40"/>
+      <c r="F58" s="58"/>
       <c r="H58" s="18">
         <f>C58/1000000</f>
         <v>5.0000000000000004E-6</v>
@@ -17738,15 +18357,15 @@
       <c r="B59" s="6">
         <v>0.08</v>
       </c>
-      <c r="C59" s="38">
+      <c r="C59" s="76">
         <v>10</v>
       </c>
-      <c r="D59" s="38"/>
-      <c r="E59" s="39">
+      <c r="D59" s="76"/>
+      <c r="E59" s="57">
         <f t="shared" ref="E59:E62" si="0">(B59+0.0048)/0.0096</f>
         <v>8.8333333333333339</v>
       </c>
-      <c r="F59" s="40"/>
+      <c r="F59" s="58"/>
       <c r="H59" s="18">
         <f>C59/1000000</f>
         <v>1.0000000000000001E-5</v>
@@ -17765,15 +18384,15 @@
         <v>36</v>
       </c>
       <c r="B60" s="6"/>
-      <c r="C60" s="38">
+      <c r="C60" s="76">
         <v>25</v>
       </c>
-      <c r="D60" s="38"/>
-      <c r="E60" s="39">
+      <c r="D60" s="76"/>
+      <c r="E60" s="57">
         <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
-      <c r="F60" s="40"/>
+      <c r="F60" s="58"/>
       <c r="H60" s="18"/>
       <c r="I60" s="18"/>
       <c r="J60" s="21"/>
@@ -17785,15 +18404,15 @@
       <c r="B61" s="6">
         <v>0.48399999999999999</v>
       </c>
-      <c r="C61" s="38">
+      <c r="C61" s="76">
         <v>50</v>
       </c>
-      <c r="D61" s="38"/>
-      <c r="E61" s="39">
+      <c r="D61" s="76"/>
+      <c r="E61" s="57">
         <f t="shared" si="0"/>
         <v>50.916666666666671</v>
       </c>
-      <c r="F61" s="40"/>
+      <c r="F61" s="58"/>
       <c r="H61" s="18">
         <f>C61/1000000</f>
         <v>5.0000000000000002E-5</v>
@@ -17814,15 +18433,15 @@
       <c r="B62" s="6">
         <v>0.97299999999999998</v>
       </c>
-      <c r="C62" s="38">
+      <c r="C62" s="76">
         <v>100</v>
       </c>
-      <c r="D62" s="38"/>
-      <c r="E62" s="39">
+      <c r="D62" s="76"/>
+      <c r="E62" s="57">
         <f t="shared" si="0"/>
         <v>101.85416666666667</v>
       </c>
-      <c r="F62" s="40"/>
+      <c r="F62" s="58"/>
       <c r="H62" s="18">
         <f>C62/1000000</f>
         <v>1E-4</v>
@@ -17843,15 +18462,15 @@
       <c r="B63" s="8">
         <v>1.899</v>
       </c>
-      <c r="C63" s="47">
+      <c r="C63" s="52">
         <v>200</v>
       </c>
-      <c r="D63" s="48"/>
-      <c r="E63" s="53">
+      <c r="D63" s="53"/>
+      <c r="E63" s="60">
         <f t="shared" ref="E63" si="3">(B63+0.0048)/0.0096</f>
         <v>198.3125</v>
       </c>
-      <c r="F63" s="54"/>
+      <c r="F63" s="61"/>
       <c r="H63" s="19">
         <f>C63/1000000</f>
         <v>2.0000000000000001E-4</v>
@@ -17866,19 +18485,19 @@
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A64" s="9" t="s">
+      <c r="A64" s="41" t="s">
         <v>69</v>
       </c>
       <c r="B64" s="9">
         <v>1.25</v>
       </c>
-      <c r="C64" s="49"/>
-      <c r="D64" s="50"/>
-      <c r="E64" s="55">
+      <c r="C64" s="72"/>
+      <c r="D64" s="73"/>
+      <c r="E64" s="74">
         <f t="shared" ref="E64" si="4">(B64+0.0048)/0.0096</f>
         <v>130.70833333333334</v>
       </c>
-      <c r="F64" s="68"/>
+      <c r="F64" s="75"/>
       <c r="H64" s="18">
         <f t="shared" ref="H64:H71" si="5">E64/1000000</f>
         <v>1.3070833333333334E-4</v>
@@ -17893,19 +18512,19 @@
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A65" s="6" t="s">
+      <c r="A65" s="5" t="s">
         <v>70</v>
       </c>
       <c r="B65" s="6">
         <v>1E-3</v>
       </c>
-      <c r="C65" s="41"/>
-      <c r="D65" s="42"/>
-      <c r="E65" s="55">
+      <c r="C65" s="48"/>
+      <c r="D65" s="56"/>
+      <c r="E65" s="74">
         <f t="shared" ref="E65:E71" si="6">(B65+0.0048)/0.0096</f>
         <v>0.60416666666666663</v>
       </c>
-      <c r="F65" s="68"/>
+      <c r="F65" s="75"/>
       <c r="H65" s="18">
         <f t="shared" si="5"/>
         <v>6.0416666666666667E-7</v>
@@ -17920,19 +18539,19 @@
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A66" s="6" t="s">
+      <c r="A66" s="5" t="s">
         <v>71</v>
       </c>
       <c r="B66" s="6">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="C66" s="41"/>
-      <c r="D66" s="42"/>
-      <c r="E66" s="55">
+      <c r="C66" s="48"/>
+      <c r="D66" s="56"/>
+      <c r="E66" s="74">
         <f t="shared" si="6"/>
         <v>1.0208333333333335</v>
       </c>
-      <c r="F66" s="68"/>
+      <c r="F66" s="75"/>
       <c r="H66" s="18">
         <f t="shared" si="5"/>
         <v>1.0208333333333334E-6</v>
@@ -17947,19 +18566,19 @@
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A67" s="6" t="s">
+      <c r="A67" s="5" t="s">
         <v>72</v>
       </c>
       <c r="B67" s="6">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="C67" s="41"/>
-      <c r="D67" s="42"/>
-      <c r="E67" s="55">
+      <c r="C67" s="48"/>
+      <c r="D67" s="56"/>
+      <c r="E67" s="74">
         <f t="shared" si="6"/>
         <v>1.3333333333333333</v>
       </c>
-      <c r="F67" s="68"/>
+      <c r="F67" s="75"/>
       <c r="H67" s="18">
         <f t="shared" si="5"/>
         <v>1.3333333333333332E-6</v>
@@ -17974,19 +18593,19 @@
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A68" s="6" t="s">
+      <c r="A68" s="5" t="s">
         <v>73</v>
       </c>
       <c r="B68" s="6">
         <v>1.4E-2</v>
       </c>
-      <c r="C68" s="41"/>
-      <c r="D68" s="42"/>
-      <c r="E68" s="55">
+      <c r="C68" s="48"/>
+      <c r="D68" s="56"/>
+      <c r="E68" s="74">
         <f t="shared" si="6"/>
         <v>1.9583333333333335</v>
       </c>
-      <c r="F68" s="68"/>
+      <c r="F68" s="75"/>
       <c r="H68" s="18">
         <f t="shared" si="5"/>
         <v>1.9583333333333334E-6</v>
@@ -18001,19 +18620,19 @@
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A69" s="6" t="s">
+      <c r="A69" s="5" t="s">
         <v>74</v>
       </c>
       <c r="B69" s="6">
         <v>2.4E-2</v>
       </c>
-      <c r="C69" s="41"/>
-      <c r="D69" s="42"/>
-      <c r="E69" s="55">
+      <c r="C69" s="48"/>
+      <c r="D69" s="56"/>
+      <c r="E69" s="74">
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="F69" s="68"/>
+      <c r="F69" s="75"/>
       <c r="H69" s="18">
         <f t="shared" si="5"/>
         <v>3.0000000000000001E-6</v>
@@ -18028,19 +18647,19 @@
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A70" s="6" t="s">
+      <c r="A70" s="5" t="s">
         <v>75</v>
       </c>
       <c r="B70" s="6">
         <v>4.1000000000000002E-2</v>
       </c>
-      <c r="C70" s="41"/>
-      <c r="D70" s="42"/>
-      <c r="E70" s="55">
+      <c r="C70" s="48"/>
+      <c r="D70" s="56"/>
+      <c r="E70" s="74">
         <f t="shared" si="6"/>
         <v>4.7708333333333339</v>
       </c>
-      <c r="F70" s="68"/>
+      <c r="F70" s="75"/>
       <c r="H70" s="18">
         <f t="shared" si="5"/>
         <v>4.7708333333333335E-6</v>
@@ -18054,20 +18673,20 @@
         <v>8.605848625000001E-2</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A71" s="6" t="s">
+    <row r="71" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="B71" s="6">
+      <c r="B71" s="8">
         <v>0.311</v>
       </c>
-      <c r="C71" s="41"/>
-      <c r="D71" s="42"/>
-      <c r="E71" s="55">
+      <c r="C71" s="52"/>
+      <c r="D71" s="59"/>
+      <c r="E71" s="81">
         <f t="shared" si="6"/>
         <v>32.895833333333336</v>
       </c>
-      <c r="F71" s="68"/>
+      <c r="F71" s="82"/>
       <c r="H71" s="18">
         <f t="shared" si="5"/>
         <v>3.2895833333333338E-5</v>
@@ -18105,7 +18724,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="I100" s="16" t="s">
         <v>22</v>
       </c>
@@ -18117,21 +18736,20 @@
       </c>
     </row>
     <row r="101" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="2" t="s">
+      <c r="A101" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B101" s="2" t="s">
+      <c r="B101" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C101" s="2" t="s">
+      <c r="C101" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="D101" s="2"/>
-      <c r="E101" s="2" t="s">
+      <c r="D101" s="29"/>
+      <c r="E101" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="F101" s="2"/>
-      <c r="G101" s="35"/>
+      <c r="F101" s="30"/>
       <c r="I101" s="17" t="s">
         <v>15</v>
       </c>
@@ -18153,11 +18771,11 @@
         <v>0.5</v>
       </c>
       <c r="D102" s="11"/>
-      <c r="E102" s="51">
+      <c r="E102" s="68">
         <f>(B102+0.001)/0.0211</f>
         <v>0.56872037914691942</v>
       </c>
-      <c r="F102" s="52"/>
+      <c r="F102" s="69"/>
       <c r="I102" s="16">
         <f t="shared" ref="I102:I107" si="9">C102/1000000</f>
         <v>4.9999999999999998E-7</v>
@@ -18182,11 +18800,11 @@
         <v>1</v>
       </c>
       <c r="D103" s="13"/>
-      <c r="E103" s="39">
+      <c r="E103" s="57">
         <f t="shared" ref="E103:E107" si="11">(B103+0.001)/0.0211</f>
         <v>1.0426540284360191</v>
       </c>
-      <c r="F103" s="40"/>
+      <c r="F103" s="58"/>
       <c r="I103" s="18">
         <f t="shared" si="9"/>
         <v>9.9999999999999995E-7</v>
@@ -18211,11 +18829,11 @@
         <v>5</v>
       </c>
       <c r="D104" s="13"/>
-      <c r="E104" s="39">
+      <c r="E104" s="57">
         <f t="shared" si="11"/>
         <v>5.0236966824644549</v>
       </c>
-      <c r="F104" s="40"/>
+      <c r="F104" s="58"/>
       <c r="I104" s="18">
         <f t="shared" si="9"/>
         <v>5.0000000000000004E-6</v>
@@ -18240,11 +18858,11 @@
         <v>10</v>
       </c>
       <c r="D105" s="13"/>
-      <c r="E105" s="39">
+      <c r="E105" s="57">
         <f t="shared" si="11"/>
         <v>10.284360189573459</v>
       </c>
-      <c r="F105" s="40"/>
+      <c r="F105" s="58"/>
       <c r="I105" s="18">
         <f t="shared" si="9"/>
         <v>1.0000000000000001E-5</v>
@@ -18269,11 +18887,11 @@
         <v>25</v>
       </c>
       <c r="D106" s="33"/>
-      <c r="E106" s="39">
+      <c r="E106" s="57">
         <f t="shared" si="11"/>
         <v>24.976303317535546</v>
       </c>
-      <c r="F106" s="40"/>
+      <c r="F106" s="58"/>
       <c r="I106" s="19">
         <f t="shared" si="9"/>
         <v>2.5000000000000001E-5</v>
@@ -18298,11 +18916,11 @@
         <v>50</v>
       </c>
       <c r="D107" s="15"/>
-      <c r="E107" s="53">
+      <c r="E107" s="60">
         <f t="shared" si="11"/>
         <v>78.436018957345965</v>
       </c>
-      <c r="F107" s="54"/>
+      <c r="F107" s="61"/>
       <c r="I107" s="18">
         <f t="shared" si="9"/>
         <v>5.0000000000000002E-5</v>
@@ -18317,19 +18935,19 @@
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A108" s="9" t="s">
+      <c r="A108" s="41" t="s">
         <v>69</v>
       </c>
       <c r="B108" s="9">
         <v>0</v>
       </c>
-      <c r="C108" s="49"/>
-      <c r="D108" s="50"/>
-      <c r="E108" s="55">
+      <c r="C108" s="72"/>
+      <c r="D108" s="73"/>
+      <c r="E108" s="74">
         <f t="shared" ref="E108:E115" si="13">(B108+0.001)/0.0211</f>
         <v>4.7393364928909949E-2</v>
       </c>
-      <c r="F108" s="55"/>
+      <c r="F108" s="75"/>
       <c r="I108" s="18">
         <f>E108/1000000</f>
         <v>4.7393364928909948E-8</v>
@@ -18344,19 +18962,19 @@
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A109" s="6" t="s">
+      <c r="A109" s="5" t="s">
         <v>70</v>
       </c>
       <c r="B109" s="6">
         <v>0</v>
       </c>
-      <c r="C109" s="41"/>
-      <c r="D109" s="42"/>
-      <c r="E109" s="39">
+      <c r="C109" s="48"/>
+      <c r="D109" s="56"/>
+      <c r="E109" s="57">
         <f t="shared" si="13"/>
         <v>4.7393364928909949E-2</v>
       </c>
-      <c r="F109" s="39"/>
+      <c r="F109" s="58"/>
       <c r="I109" s="18">
         <f t="shared" ref="I109:I115" si="14">E109/1000000</f>
         <v>4.7393364928909948E-8</v>
@@ -18371,19 +18989,19 @@
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A110" s="6" t="s">
+      <c r="A110" s="5" t="s">
         <v>71</v>
       </c>
       <c r="B110" s="6">
         <v>0</v>
       </c>
-      <c r="C110" s="41"/>
-      <c r="D110" s="42"/>
-      <c r="E110" s="39">
+      <c r="C110" s="48"/>
+      <c r="D110" s="56"/>
+      <c r="E110" s="57">
         <f t="shared" si="13"/>
         <v>4.7393364928909949E-2</v>
       </c>
-      <c r="F110" s="39"/>
+      <c r="F110" s="58"/>
       <c r="I110" s="18">
         <f t="shared" si="14"/>
         <v>4.7393364928909948E-8</v>
@@ -18398,19 +19016,19 @@
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A111" s="6" t="s">
+      <c r="A111" s="5" t="s">
         <v>72</v>
       </c>
       <c r="B111" s="6">
         <v>0</v>
       </c>
-      <c r="C111" s="41"/>
-      <c r="D111" s="42"/>
-      <c r="E111" s="39">
+      <c r="C111" s="48"/>
+      <c r="D111" s="56"/>
+      <c r="E111" s="57">
         <f t="shared" si="13"/>
         <v>4.7393364928909949E-2</v>
       </c>
-      <c r="F111" s="39"/>
+      <c r="F111" s="58"/>
       <c r="I111" s="18">
         <f t="shared" si="14"/>
         <v>4.7393364928909948E-8</v>
@@ -18425,19 +19043,19 @@
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A112" s="6" t="s">
+      <c r="A112" s="5" t="s">
         <v>73</v>
       </c>
       <c r="B112" s="6">
         <v>1.4E-2</v>
       </c>
-      <c r="C112" s="41"/>
-      <c r="D112" s="42"/>
-      <c r="E112" s="39">
+      <c r="C112" s="48"/>
+      <c r="D112" s="56"/>
+      <c r="E112" s="57">
         <f t="shared" si="13"/>
         <v>0.71090047393364919</v>
       </c>
-      <c r="F112" s="39"/>
+      <c r="F112" s="58"/>
       <c r="I112" s="18">
         <f t="shared" si="14"/>
         <v>7.1090047393364923E-7</v>
@@ -18452,19 +19070,19 @@
       </c>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A113" s="6" t="s">
+      <c r="A113" s="5" t="s">
         <v>74</v>
       </c>
       <c r="B113" s="6">
         <v>8.9999999999999993E-3</v>
       </c>
-      <c r="C113" s="41"/>
-      <c r="D113" s="42"/>
-      <c r="E113" s="39">
+      <c r="C113" s="48"/>
+      <c r="D113" s="56"/>
+      <c r="E113" s="57">
         <f t="shared" si="13"/>
         <v>0.47393364928909942</v>
       </c>
-      <c r="F113" s="39"/>
+      <c r="F113" s="58"/>
       <c r="I113" s="18">
         <f t="shared" si="14"/>
         <v>4.7393364928909945E-7</v>
@@ -18479,19 +19097,19 @@
       </c>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A114" s="6" t="s">
+      <c r="A114" s="5" t="s">
         <v>75</v>
       </c>
       <c r="B114" s="6">
         <v>3.9E-2</v>
       </c>
-      <c r="C114" s="41"/>
-      <c r="D114" s="42"/>
-      <c r="E114" s="39">
+      <c r="C114" s="48"/>
+      <c r="D114" s="56"/>
+      <c r="E114" s="57">
         <f t="shared" si="13"/>
         <v>1.8957345971563981</v>
       </c>
-      <c r="F114" s="39"/>
+      <c r="F114" s="58"/>
       <c r="I114" s="18">
         <f t="shared" si="14"/>
         <v>1.8957345971563982E-6</v>
@@ -18505,20 +19123,20 @@
         <v>3.4196132701421807E-2</v>
       </c>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A115" s="6" t="s">
+    <row r="115" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A115" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="B115" s="6">
+      <c r="B115" s="8">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="C115" s="41"/>
-      <c r="D115" s="42"/>
-      <c r="E115" s="39">
+      <c r="C115" s="52"/>
+      <c r="D115" s="59"/>
+      <c r="E115" s="60">
         <f t="shared" si="13"/>
         <v>0.33175355450236965</v>
       </c>
-      <c r="F115" s="39"/>
+      <c r="F115" s="61"/>
       <c r="I115" s="18">
         <f t="shared" si="14"/>
         <v>3.3175355450236965E-7</v>
@@ -18532,68 +19150,128 @@
         <v>5.9843232227488148E-3</v>
       </c>
     </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="I118" t="s">
+        <v>25</v>
+      </c>
+      <c r="K118">
+        <v>62.005400000000002</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="I119" t="s">
+        <v>16</v>
+      </c>
+      <c r="K119">
+        <v>1E-3</v>
+      </c>
+    </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.25">
       <c r="H120" s="24"/>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A121" s="46" t="s">
+    <row r="121" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A121" s="70" t="s">
         <v>27</v>
       </c>
-      <c r="B121" s="46"/>
-      <c r="C121" s="46"/>
-      <c r="D121" s="46"/>
-      <c r="E121" s="46"/>
-      <c r="F121" s="46"/>
-      <c r="G121" s="46"/>
-      <c r="H121" s="46"/>
+      <c r="B121" s="70"/>
+      <c r="C121" s="70"/>
+      <c r="D121" s="70"/>
+      <c r="E121" s="70"/>
+      <c r="F121" s="70"/>
+      <c r="G121" s="70"/>
+      <c r="H121" s="70"/>
+    </row>
+    <row r="122" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I122" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="J122" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K122" s="20" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="123" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="2" t="s">
+      <c r="A123" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B123" s="2" t="s">
+      <c r="B123" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C123" s="2" t="s">
+      <c r="C123" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="D123" s="2"/>
-      <c r="E123" s="2" t="s">
+      <c r="D123" s="29"/>
+      <c r="E123" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="F123" s="2"/>
-      <c r="G123" s="37"/>
+      <c r="F123" s="30"/>
+      <c r="G123" s="35"/>
+      <c r="I123" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="J123" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="K123" s="17" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A124" s="3" t="s">
         <v>56</v>
       </c>
       <c r="B124" s="4"/>
-      <c r="C124" s="56">
+      <c r="C124" s="62">
         <v>2.5</v>
       </c>
-      <c r="D124" s="57"/>
-      <c r="E124" s="51">
+      <c r="D124" s="63"/>
+      <c r="E124" s="68">
         <v>0</v>
       </c>
-      <c r="F124" s="52"/>
-      <c r="G124" s="36"/>
+      <c r="F124" s="69"/>
+      <c r="G124" s="35"/>
+      <c r="I124" s="16">
+        <f t="shared" ref="I124:I131" si="17">C124/1000000</f>
+        <v>2.5000000000000002E-6</v>
+      </c>
+      <c r="J124" s="16">
+        <f t="shared" ref="J124:J131" si="18">$K$118*I124</f>
+        <v>1.5501350000000002E-4</v>
+      </c>
+      <c r="K124" s="23">
+        <f>J124*1000</f>
+        <v>0.15501350000000003</v>
+      </c>
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A125" s="31" t="s">
         <v>11</v>
       </c>
       <c r="B125" s="2"/>
-      <c r="C125" s="58">
+      <c r="C125" s="66">
         <v>5</v>
       </c>
-      <c r="D125" s="59"/>
-      <c r="E125" s="44">
+      <c r="D125" s="67"/>
+      <c r="E125" s="50">
         <f>(B125+0.0053)/0.0019</f>
         <v>2.7894736842105265</v>
       </c>
-      <c r="F125" s="45"/>
-      <c r="G125" s="36"/>
+      <c r="F125" s="51"/>
+      <c r="G125" s="35"/>
+      <c r="I125" s="18">
+        <f t="shared" si="17"/>
+        <v>5.0000000000000004E-6</v>
+      </c>
+      <c r="J125" s="18">
+        <f t="shared" si="18"/>
+        <v>3.1002700000000005E-4</v>
+      </c>
+      <c r="K125" s="21">
+        <f t="shared" ref="K125:K131" si="19">J125*1000</f>
+        <v>0.31002700000000005</v>
+      </c>
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A126" s="5" t="s">
@@ -18602,32 +19280,56 @@
       <c r="B126" s="6">
         <v>2.3E-2</v>
       </c>
-      <c r="C126" s="41">
+      <c r="C126" s="48">
         <v>10</v>
       </c>
-      <c r="D126" s="43"/>
-      <c r="E126" s="44">
-        <f t="shared" ref="E126:E131" si="17">(B126+0.0053)/0.0019</f>
+      <c r="D126" s="49"/>
+      <c r="E126" s="50">
+        <f t="shared" ref="E126:E131" si="20">(B126+0.0053)/0.0019</f>
         <v>14.894736842105262</v>
       </c>
-      <c r="F126" s="45"/>
-      <c r="G126" s="36"/>
+      <c r="F126" s="51"/>
+      <c r="G126" s="35"/>
+      <c r="I126" s="18">
+        <f t="shared" si="17"/>
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="J126" s="18">
+        <f t="shared" si="18"/>
+        <v>6.2005400000000009E-4</v>
+      </c>
+      <c r="K126" s="21">
+        <f t="shared" si="19"/>
+        <v>0.62005400000000011</v>
+      </c>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A127" s="5" t="s">
         <v>12</v>
       </c>
       <c r="B127" s="6"/>
-      <c r="C127" s="41">
+      <c r="C127" s="48">
         <v>25</v>
       </c>
-      <c r="D127" s="43"/>
-      <c r="E127" s="44">
+      <c r="D127" s="49"/>
+      <c r="E127" s="50">
+        <f t="shared" si="20"/>
+        <v>2.7894736842105265</v>
+      </c>
+      <c r="F127" s="51"/>
+      <c r="G127" s="35"/>
+      <c r="I127" s="18">
         <f t="shared" si="17"/>
-        <v>2.7894736842105265</v>
-      </c>
-      <c r="F127" s="45"/>
-      <c r="G127" s="36"/>
+        <v>2.5000000000000001E-5</v>
+      </c>
+      <c r="J127" s="18">
+        <f t="shared" si="18"/>
+        <v>1.550135E-3</v>
+      </c>
+      <c r="K127" s="21">
+        <f t="shared" si="19"/>
+        <v>1.550135</v>
+      </c>
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A128" s="5" t="s">
@@ -18636,198 +19338,342 @@
       <c r="B128" s="6">
         <v>9.6000000000000002E-2</v>
       </c>
-      <c r="C128" s="41">
+      <c r="C128" s="48">
         <v>50</v>
       </c>
-      <c r="D128" s="43"/>
-      <c r="E128" s="44">
+      <c r="D128" s="49"/>
+      <c r="E128" s="50">
+        <f t="shared" si="20"/>
+        <v>53.315789473684212</v>
+      </c>
+      <c r="F128" s="51"/>
+      <c r="G128" s="35"/>
+      <c r="I128" s="18">
         <f t="shared" si="17"/>
-        <v>53.315789473684212</v>
-      </c>
-      <c r="F128" s="45"/>
-      <c r="G128" s="36"/>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+        <v>5.0000000000000002E-5</v>
+      </c>
+      <c r="J128" s="18">
+        <f t="shared" si="18"/>
+        <v>3.10027E-3</v>
+      </c>
+      <c r="K128" s="21">
+        <f t="shared" si="19"/>
+        <v>3.1002700000000001</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A129" s="5" t="s">
         <v>4</v>
       </c>
       <c r="B129" s="6">
         <v>0.20499999999999999</v>
       </c>
-      <c r="C129" s="41">
+      <c r="C129" s="48">
         <v>100</v>
       </c>
-      <c r="D129" s="43"/>
-      <c r="E129" s="44">
+      <c r="D129" s="49"/>
+      <c r="E129" s="50">
+        <f t="shared" si="20"/>
+        <v>110.68421052631578</v>
+      </c>
+      <c r="F129" s="51"/>
+      <c r="G129" s="35"/>
+      <c r="I129" s="18">
         <f t="shared" si="17"/>
-        <v>110.68421052631578</v>
-      </c>
-      <c r="F129" s="45"/>
-      <c r="G129" s="36"/>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+        <v>1E-4</v>
+      </c>
+      <c r="J129" s="18">
+        <f t="shared" si="18"/>
+        <v>6.20054E-3</v>
+      </c>
+      <c r="K129" s="21">
+        <f t="shared" si="19"/>
+        <v>6.2005400000000002</v>
+      </c>
+    </row>
+    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A130" s="5" t="s">
         <v>5</v>
       </c>
       <c r="B130" s="6">
         <v>0.39500000000000002</v>
       </c>
-      <c r="C130" s="41">
+      <c r="C130" s="48">
         <v>200</v>
       </c>
-      <c r="D130" s="43"/>
-      <c r="E130" s="44">
+      <c r="D130" s="49"/>
+      <c r="E130" s="50">
+        <f t="shared" si="20"/>
+        <v>210.68421052631581</v>
+      </c>
+      <c r="F130" s="51"/>
+      <c r="G130" s="35"/>
+      <c r="I130" s="18">
         <f t="shared" si="17"/>
-        <v>210.68421052631581</v>
-      </c>
-      <c r="F130" s="45"/>
-      <c r="G130" s="36"/>
-    </row>
-    <row r="131" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="J130" s="18">
+        <f t="shared" si="18"/>
+        <v>1.240108E-2</v>
+      </c>
+      <c r="K130" s="21">
+        <f t="shared" si="19"/>
+        <v>12.40108</v>
+      </c>
+    </row>
+    <row r="131" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A131" s="7" t="s">
         <v>6</v>
       </c>
       <c r="B131" s="8">
         <v>0.97</v>
       </c>
-      <c r="C131" s="47">
+      <c r="C131" s="52">
         <v>500</v>
       </c>
-      <c r="D131" s="48"/>
-      <c r="E131" s="62">
+      <c r="D131" s="53"/>
+      <c r="E131" s="54">
+        <f t="shared" si="20"/>
+        <v>513.31578947368416</v>
+      </c>
+      <c r="F131" s="55"/>
+      <c r="G131" s="35"/>
+      <c r="I131" s="19">
         <f t="shared" si="17"/>
-        <v>513.31578947368416</v>
-      </c>
-      <c r="F131" s="63"/>
-      <c r="G131" s="36"/>
-    </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A132" s="9" t="s">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="J131" s="19">
+        <f t="shared" si="18"/>
+        <v>3.1002700000000001E-2</v>
+      </c>
+      <c r="K131" s="22">
+        <f t="shared" si="19"/>
+        <v>31.002700000000001</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A132" s="41" t="s">
         <v>69</v>
       </c>
       <c r="B132" s="9">
         <v>1.4E-2</v>
       </c>
-      <c r="C132" s="49"/>
-      <c r="D132" s="60"/>
-      <c r="E132" s="66">
-        <f t="shared" ref="E132" si="18">(B132+0.0053)/0.0019</f>
+      <c r="C132" s="72"/>
+      <c r="D132" s="78"/>
+      <c r="E132" s="79">
+        <f t="shared" ref="E132" si="21">(B132+0.0053)/0.0019</f>
         <v>10.157894736842106</v>
       </c>
-      <c r="F132" s="67"/>
-      <c r="G132" s="36"/>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A133" s="6" t="s">
+      <c r="F132" s="80"/>
+      <c r="G132" s="35"/>
+      <c r="I132" s="18">
+        <f>E132/1000000</f>
+        <v>1.0157894736842106E-5</v>
+      </c>
+      <c r="J132" s="18">
+        <f t="shared" ref="J132:J139" si="22">$K$118*I132*$K$119</f>
+        <v>6.2984432631578961E-7</v>
+      </c>
+      <c r="K132" s="21">
+        <f t="shared" ref="K132:K139" si="23">J132*1000000</f>
+        <v>0.62984432631578957</v>
+      </c>
+    </row>
+    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A133" s="5" t="s">
         <v>70</v>
       </c>
       <c r="B133" s="6">
         <v>8.9999999999999993E-3</v>
       </c>
-      <c r="C133" s="41"/>
-      <c r="D133" s="43"/>
-      <c r="E133" s="44">
-        <f t="shared" ref="E133" si="19">(B133+0.0053)/0.0019</f>
+      <c r="C133" s="48"/>
+      <c r="D133" s="49"/>
+      <c r="E133" s="50">
+        <f t="shared" ref="E133" si="24">(B133+0.0053)/0.0019</f>
         <v>7.5263157894736841</v>
       </c>
-      <c r="F133" s="45"/>
-      <c r="G133" s="36"/>
-    </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A134" s="6" t="s">
+      <c r="F133" s="51"/>
+      <c r="G133" s="35"/>
+      <c r="I133" s="18">
+        <f>E133/1000000</f>
+        <v>7.5263157894736844E-6</v>
+      </c>
+      <c r="J133" s="18">
+        <f t="shared" si="22"/>
+        <v>4.666722210526316E-7</v>
+      </c>
+      <c r="K133" s="21">
+        <f t="shared" si="23"/>
+        <v>0.46667222105263162</v>
+      </c>
+    </row>
+    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A134" s="5" t="s">
         <v>71</v>
       </c>
       <c r="B134" s="6">
         <v>2E-3</v>
       </c>
-      <c r="C134" s="41"/>
-      <c r="D134" s="43"/>
-      <c r="E134" s="44">
-        <f t="shared" ref="E134:E139" si="20">(B134+0.0053)/0.0019</f>
+      <c r="C134" s="48"/>
+      <c r="D134" s="49"/>
+      <c r="E134" s="50">
+        <f t="shared" ref="E134:E139" si="25">(B134+0.0053)/0.0019</f>
         <v>3.8421052631578947</v>
       </c>
-      <c r="F134" s="45"/>
-      <c r="G134" s="36"/>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A135" s="6" t="s">
+      <c r="F134" s="51"/>
+      <c r="G134" s="35"/>
+      <c r="I134" s="18">
+        <f t="shared" ref="I134:I139" si="26">E134/1000000</f>
+        <v>3.8421052631578947E-6</v>
+      </c>
+      <c r="J134" s="18">
+        <f t="shared" si="22"/>
+        <v>2.3823127368421055E-7</v>
+      </c>
+      <c r="K134" s="21">
+        <f t="shared" si="23"/>
+        <v>0.23823127368421054</v>
+      </c>
+    </row>
+    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A135" s="5" t="s">
         <v>72</v>
       </c>
       <c r="B135" s="6">
         <v>0</v>
       </c>
-      <c r="C135" s="41"/>
-      <c r="D135" s="43"/>
-      <c r="E135" s="44">
-        <f t="shared" si="20"/>
+      <c r="C135" s="48"/>
+      <c r="D135" s="49"/>
+      <c r="E135" s="50">
+        <f t="shared" si="25"/>
         <v>2.7894736842105265</v>
       </c>
-      <c r="F135" s="45"/>
-      <c r="G135" s="36"/>
-    </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A136" s="6" t="s">
+      <c r="F135" s="51"/>
+      <c r="G135" s="35"/>
+      <c r="I135" s="18">
+        <f t="shared" si="26"/>
+        <v>2.7894736842105266E-6</v>
+      </c>
+      <c r="J135" s="18">
+        <f t="shared" si="22"/>
+        <v>1.729624315789474E-7</v>
+      </c>
+      <c r="K135" s="21">
+        <f t="shared" si="23"/>
+        <v>0.17296243157894739</v>
+      </c>
+    </row>
+    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A136" s="5" t="s">
         <v>73</v>
       </c>
       <c r="B136" s="6">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="C136" s="41"/>
-      <c r="D136" s="43"/>
-      <c r="E136" s="44">
-        <f t="shared" si="20"/>
+      <c r="C136" s="48"/>
+      <c r="D136" s="49"/>
+      <c r="E136" s="50">
+        <f t="shared" si="25"/>
         <v>5.9473684210526319</v>
       </c>
-      <c r="F136" s="45"/>
-      <c r="G136" s="36"/>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A137" s="6" t="s">
+      <c r="F136" s="51"/>
+      <c r="G136" s="35"/>
+      <c r="I136" s="18">
+        <f t="shared" si="26"/>
+        <v>5.9473684210526318E-6</v>
+      </c>
+      <c r="J136" s="18">
+        <f t="shared" si="22"/>
+        <v>3.6876895789473685E-7</v>
+      </c>
+      <c r="K136" s="21">
+        <f t="shared" si="23"/>
+        <v>0.36876895789473685</v>
+      </c>
+    </row>
+    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A137" s="5" t="s">
         <v>74</v>
       </c>
       <c r="B137" s="6">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="C137" s="41"/>
-      <c r="D137" s="43"/>
-      <c r="E137" s="44">
-        <f t="shared" si="20"/>
+      <c r="C137" s="48"/>
+      <c r="D137" s="49"/>
+      <c r="E137" s="50">
+        <f t="shared" si="25"/>
         <v>15.947368421052632</v>
       </c>
-      <c r="F137" s="45"/>
-      <c r="G137" s="36"/>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A138" s="6" t="s">
+      <c r="F137" s="51"/>
+      <c r="G137" s="35"/>
+      <c r="I137" s="18">
+        <f t="shared" si="26"/>
+        <v>1.5947368421052633E-5</v>
+      </c>
+      <c r="J137" s="18">
+        <f t="shared" si="22"/>
+        <v>9.8882295789473691E-7</v>
+      </c>
+      <c r="K137" s="21">
+        <f t="shared" si="23"/>
+        <v>0.98882295789473695</v>
+      </c>
+    </row>
+    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A138" s="5" t="s">
         <v>75</v>
       </c>
       <c r="B138" s="6">
         <v>1.2999999999999999E-2</v>
       </c>
-      <c r="C138" s="41"/>
-      <c r="D138" s="43"/>
-      <c r="E138" s="44">
-        <f t="shared" si="20"/>
+      <c r="C138" s="48"/>
+      <c r="D138" s="49"/>
+      <c r="E138" s="50">
+        <f t="shared" si="25"/>
         <v>9.6315789473684212</v>
       </c>
-      <c r="F138" s="45"/>
-      <c r="G138" s="36"/>
-    </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A139" s="6" t="s">
+      <c r="F138" s="51"/>
+      <c r="G138" s="35"/>
+      <c r="I138" s="18">
+        <f t="shared" si="26"/>
+        <v>9.6315789473684206E-6</v>
+      </c>
+      <c r="J138" s="18">
+        <f t="shared" si="22"/>
+        <v>5.972099052631579E-7</v>
+      </c>
+      <c r="K138" s="21">
+        <f t="shared" si="23"/>
+        <v>0.59720990526315787</v>
+      </c>
+    </row>
+    <row r="139" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A139" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="B139" s="6">
+      <c r="B139" s="8">
         <v>1.4E-2</v>
       </c>
-      <c r="C139" s="41"/>
-      <c r="D139" s="43"/>
-      <c r="E139" s="44">
-        <f t="shared" si="20"/>
+      <c r="C139" s="52"/>
+      <c r="D139" s="53"/>
+      <c r="E139" s="54">
+        <f t="shared" si="25"/>
         <v>10.157894736842106</v>
       </c>
-      <c r="F139" s="45"/>
-      <c r="G139" s="36"/>
+      <c r="F139" s="55"/>
+      <c r="G139" s="35"/>
+      <c r="I139" s="18">
+        <f t="shared" si="26"/>
+        <v>1.0157894736842106E-5</v>
+      </c>
+      <c r="J139" s="18">
+        <f t="shared" si="22"/>
+        <v>6.2984432631578961E-7</v>
+      </c>
+      <c r="K139" s="21">
+        <f t="shared" si="23"/>
+        <v>0.62984432631578957</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="88">
@@ -18941,16 +19787,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="70" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
       <c r="I1" s="1"/>
     </row>
     <row r="2" spans="1:9" s="25" customFormat="1" x14ac:dyDescent="0.25">
@@ -19165,14 +20011,14 @@
       <c r="B57" s="6">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="C57" s="38">
+      <c r="C57" s="76">
         <v>1</v>
       </c>
-      <c r="D57" s="38"/>
-      <c r="E57" s="39">
+      <c r="D57" s="76"/>
+      <c r="E57" s="57">
         <v>0</v>
       </c>
-      <c r="F57" s="40"/>
+      <c r="F57" s="58"/>
       <c r="H57" s="18"/>
       <c r="I57" s="27"/>
       <c r="J57" s="18"/>
@@ -19184,15 +20030,15 @@
       <c r="B58" s="6">
         <v>1.7999999999999999E-2</v>
       </c>
-      <c r="C58" s="38">
+      <c r="C58" s="76">
         <v>2.5</v>
       </c>
-      <c r="D58" s="38"/>
-      <c r="E58" s="39">
+      <c r="D58" s="76"/>
+      <c r="E58" s="57">
         <f>(B58-0.0099)/0.0098</f>
         <v>0.82653061224489777</v>
       </c>
-      <c r="F58" s="40"/>
+      <c r="F58" s="58"/>
       <c r="H58" s="18"/>
       <c r="I58" s="27"/>
       <c r="J58" s="18"/>
@@ -19204,15 +20050,15 @@
       <c r="B59" s="6">
         <v>4.2999999999999997E-2</v>
       </c>
-      <c r="C59" s="38">
+      <c r="C59" s="76">
         <v>5</v>
       </c>
-      <c r="D59" s="38"/>
-      <c r="E59" s="39">
+      <c r="D59" s="76"/>
+      <c r="E59" s="57">
         <f t="shared" ref="E59:E64" si="0">(B59-0.0099)/0.0098</f>
         <v>3.3775510204081631</v>
       </c>
-      <c r="F59" s="40"/>
+      <c r="F59" s="58"/>
       <c r="H59" s="18">
         <f>C59/1000000</f>
         <v>5.0000000000000004E-6</v>
@@ -19233,15 +20079,15 @@
       <c r="B60" s="6">
         <v>9.4E-2</v>
       </c>
-      <c r="C60" s="38">
+      <c r="C60" s="76">
         <v>10</v>
       </c>
-      <c r="D60" s="38"/>
-      <c r="E60" s="39">
+      <c r="D60" s="76"/>
+      <c r="E60" s="57">
         <f t="shared" si="0"/>
         <v>8.5816326530612237</v>
       </c>
-      <c r="F60" s="40"/>
+      <c r="F60" s="58"/>
       <c r="H60" s="18">
         <f>C60/1000000</f>
         <v>1.0000000000000001E-5</v>
@@ -19262,15 +20108,15 @@
       <c r="B61" s="6">
         <v>0.25</v>
       </c>
-      <c r="C61" s="38">
+      <c r="C61" s="76">
         <v>25</v>
       </c>
-      <c r="D61" s="38"/>
-      <c r="E61" s="39">
+      <c r="D61" s="76"/>
+      <c r="E61" s="57">
         <f t="shared" si="0"/>
         <v>24.5</v>
       </c>
-      <c r="F61" s="40"/>
+      <c r="F61" s="58"/>
       <c r="H61" s="18"/>
       <c r="I61" s="18"/>
       <c r="J61" s="21"/>
@@ -19282,15 +20128,15 @@
       <c r="B62" s="6">
         <v>0.52</v>
       </c>
-      <c r="C62" s="38">
+      <c r="C62" s="76">
         <v>50</v>
       </c>
-      <c r="D62" s="38"/>
-      <c r="E62" s="39">
+      <c r="D62" s="76"/>
+      <c r="E62" s="57">
         <f t="shared" si="0"/>
         <v>52.051020408163268</v>
       </c>
-      <c r="F62" s="40"/>
+      <c r="F62" s="58"/>
       <c r="H62" s="18">
         <f>C62/1000000</f>
         <v>5.0000000000000002E-5</v>
@@ -19311,15 +20157,15 @@
       <c r="B63" s="6">
         <v>1.028</v>
       </c>
-      <c r="C63" s="38">
+      <c r="C63" s="76">
         <v>100</v>
       </c>
-      <c r="D63" s="38"/>
-      <c r="E63" s="39">
+      <c r="D63" s="76"/>
+      <c r="E63" s="57">
         <f t="shared" si="0"/>
         <v>103.88775510204081</v>
       </c>
-      <c r="F63" s="40"/>
+      <c r="F63" s="58"/>
       <c r="H63" s="18">
         <f>C63/1000000</f>
         <v>1E-4</v>
@@ -19340,15 +20186,15 @@
       <c r="B64" s="8">
         <v>1.95</v>
       </c>
-      <c r="C64" s="47">
+      <c r="C64" s="52">
         <v>200</v>
       </c>
-      <c r="D64" s="48"/>
-      <c r="E64" s="39">
+      <c r="D64" s="53"/>
+      <c r="E64" s="57">
         <f t="shared" si="0"/>
         <v>197.96938775510205</v>
       </c>
-      <c r="F64" s="40"/>
+      <c r="F64" s="58"/>
       <c r="H64" s="19">
         <f>C64/1000000</f>
         <v>2.0000000000000001E-4</v>
@@ -19369,13 +20215,13 @@
       <c r="B65" s="9">
         <v>0.224</v>
       </c>
-      <c r="C65" s="49"/>
-      <c r="D65" s="50"/>
-      <c r="E65" s="39">
+      <c r="C65" s="72"/>
+      <c r="D65" s="73"/>
+      <c r="E65" s="57">
         <f t="shared" ref="E65:E73" si="3">(B65-0.0099)/0.0098</f>
         <v>21.846938775510207</v>
       </c>
-      <c r="F65" s="40"/>
+      <c r="F65" s="58"/>
       <c r="H65" s="18">
         <f t="shared" ref="H65:H73" si="4">E65/1000000</f>
         <v>2.1846938775510207E-5</v>
@@ -19396,13 +20242,13 @@
       <c r="B66" s="6">
         <v>2.9000000000000001E-2</v>
       </c>
-      <c r="C66" s="41"/>
-      <c r="D66" s="42"/>
-      <c r="E66" s="39">
+      <c r="C66" s="48"/>
+      <c r="D66" s="56"/>
+      <c r="E66" s="57">
         <f t="shared" si="3"/>
         <v>1.9489795918367347</v>
       </c>
-      <c r="F66" s="40"/>
+      <c r="F66" s="58"/>
       <c r="H66" s="18">
         <f t="shared" si="4"/>
         <v>1.9489795918367348E-6</v>
@@ -19423,13 +20269,13 @@
       <c r="B67" s="6">
         <v>2.4E-2</v>
       </c>
-      <c r="C67" s="41"/>
-      <c r="D67" s="42"/>
-      <c r="E67" s="39">
+      <c r="C67" s="48"/>
+      <c r="D67" s="56"/>
+      <c r="E67" s="57">
         <f t="shared" si="3"/>
         <v>1.4387755102040816</v>
       </c>
-      <c r="F67" s="40"/>
+      <c r="F67" s="58"/>
       <c r="H67" s="18">
         <f t="shared" si="4"/>
         <v>1.4387755102040816E-6</v>
@@ -19450,13 +20296,13 @@
       <c r="B68" s="6">
         <v>7.9000000000000001E-2</v>
       </c>
-      <c r="C68" s="41"/>
-      <c r="D68" s="42"/>
-      <c r="E68" s="39">
+      <c r="C68" s="48"/>
+      <c r="D68" s="56"/>
+      <c r="E68" s="57">
         <f t="shared" si="3"/>
         <v>7.0510204081632653</v>
       </c>
-      <c r="F68" s="40"/>
+      <c r="F68" s="58"/>
       <c r="H68" s="18">
         <f t="shared" si="4"/>
         <v>7.051020408163265E-6</v>
@@ -19477,13 +20323,13 @@
       <c r="B69" s="6">
         <v>4.1000000000000002E-2</v>
       </c>
-      <c r="C69" s="41"/>
-      <c r="D69" s="42"/>
-      <c r="E69" s="39">
+      <c r="C69" s="48"/>
+      <c r="D69" s="56"/>
+      <c r="E69" s="57">
         <f t="shared" si="3"/>
         <v>3.1734693877551026</v>
       </c>
-      <c r="F69" s="40"/>
+      <c r="F69" s="58"/>
       <c r="H69" s="18">
         <f t="shared" si="4"/>
         <v>3.1734693877551026E-6</v>
@@ -19504,13 +20350,13 @@
       <c r="B70" s="6">
         <v>0.224</v>
       </c>
-      <c r="C70" s="41"/>
-      <c r="D70" s="42"/>
-      <c r="E70" s="39">
+      <c r="C70" s="48"/>
+      <c r="D70" s="56"/>
+      <c r="E70" s="57">
         <f t="shared" si="3"/>
         <v>21.846938775510207</v>
       </c>
-      <c r="F70" s="40"/>
+      <c r="F70" s="58"/>
       <c r="H70" s="18">
         <f t="shared" si="4"/>
         <v>2.1846938775510207E-5</v>
@@ -19531,13 +20377,13 @@
       <c r="B71" s="6">
         <v>0.221</v>
       </c>
-      <c r="C71" s="41"/>
-      <c r="D71" s="42"/>
-      <c r="E71" s="39">
+      <c r="C71" s="48"/>
+      <c r="D71" s="56"/>
+      <c r="E71" s="57">
         <f t="shared" si="3"/>
         <v>21.540816326530614</v>
       </c>
-      <c r="F71" s="40"/>
+      <c r="F71" s="58"/>
       <c r="H71" s="18">
         <f t="shared" si="4"/>
         <v>2.1540816326530614E-5</v>
@@ -19558,13 +20404,13 @@
       <c r="B72" s="6">
         <v>0.11700000000000001</v>
       </c>
-      <c r="C72" s="41"/>
-      <c r="D72" s="42"/>
-      <c r="E72" s="39">
+      <c r="C72" s="48"/>
+      <c r="D72" s="56"/>
+      <c r="E72" s="57">
         <f t="shared" si="3"/>
         <v>10.928571428571429</v>
       </c>
-      <c r="F72" s="40"/>
+      <c r="F72" s="58"/>
       <c r="H72" s="18">
         <f t="shared" si="4"/>
         <v>1.0928571428571429E-5</v>
@@ -19585,13 +20431,13 @@
       <c r="B73" s="6">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="C73" s="41"/>
-      <c r="D73" s="42"/>
-      <c r="E73" s="39">
+      <c r="C73" s="48"/>
+      <c r="D73" s="56"/>
+      <c r="E73" s="57">
         <f t="shared" si="3"/>
         <v>2.5612244897959191</v>
       </c>
-      <c r="F73" s="40"/>
+      <c r="F73" s="58"/>
       <c r="H73" s="18">
         <f t="shared" si="4"/>
         <v>2.5612244897959191E-6</v>
@@ -19629,7 +20475,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="I101" s="16" t="s">
         <v>22</v>
       </c>
@@ -19641,21 +20487,20 @@
       </c>
     </row>
     <row r="102" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="2" t="s">
+      <c r="A102" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B102" s="2" t="s">
+      <c r="B102" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C102" s="2" t="s">
+      <c r="C102" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="D102" s="2"/>
-      <c r="E102" s="2" t="s">
+      <c r="D102" s="29"/>
+      <c r="E102" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="F102" s="2"/>
-      <c r="G102" s="35"/>
+      <c r="F102" s="30"/>
       <c r="I102" s="17" t="s">
         <v>15</v>
       </c>
@@ -19677,11 +20522,11 @@
         <v>0.5</v>
       </c>
       <c r="D103" s="11"/>
-      <c r="E103" s="51">
+      <c r="E103" s="68">
         <f>(B103+0.001)/0.0201</f>
         <v>4.975124378109453E-2</v>
       </c>
-      <c r="F103" s="52"/>
+      <c r="F103" s="69"/>
       <c r="I103" s="16">
         <f t="shared" ref="I103:I108" si="7">C103/1000000</f>
         <v>4.9999999999999998E-7</v>
@@ -19706,11 +20551,11 @@
         <v>1</v>
       </c>
       <c r="D104" s="13"/>
-      <c r="E104" s="39">
+      <c r="E104" s="57">
         <f t="shared" ref="E104:E108" si="9">(B104+0.001)/0.0201</f>
         <v>0.54726368159203975</v>
       </c>
-      <c r="F104" s="40"/>
+      <c r="F104" s="58"/>
       <c r="I104" s="18">
         <f t="shared" si="7"/>
         <v>9.9999999999999995E-7</v>
@@ -19735,11 +20580,11 @@
         <v>5</v>
       </c>
       <c r="D105" s="13"/>
-      <c r="E105" s="39">
+      <c r="E105" s="57">
         <f t="shared" si="9"/>
         <v>4.1293532338308463</v>
       </c>
-      <c r="F105" s="40"/>
+      <c r="F105" s="58"/>
       <c r="I105" s="18">
         <f t="shared" si="7"/>
         <v>5.0000000000000004E-6</v>
@@ -19764,11 +20609,11 @@
         <v>10</v>
       </c>
       <c r="D106" s="13"/>
-      <c r="E106" s="39">
+      <c r="E106" s="57">
         <f t="shared" si="9"/>
         <v>10.149253731343284</v>
       </c>
-      <c r="F106" s="40"/>
+      <c r="F106" s="58"/>
       <c r="I106" s="18">
         <f t="shared" si="7"/>
         <v>1.0000000000000001E-5</v>
@@ -19793,11 +20638,11 @@
         <v>25</v>
       </c>
       <c r="D107" s="33"/>
-      <c r="E107" s="39">
+      <c r="E107" s="57">
         <f t="shared" si="9"/>
         <v>24.427860696517413</v>
       </c>
-      <c r="F107" s="40"/>
+      <c r="F107" s="58"/>
       <c r="I107" s="19">
         <f t="shared" si="7"/>
         <v>2.5000000000000001E-5</v>
@@ -19820,11 +20665,11 @@
         <v>50</v>
       </c>
       <c r="D108" s="15"/>
-      <c r="E108" s="53">
+      <c r="E108" s="60">
         <f t="shared" si="9"/>
         <v>4.975124378109453E-2</v>
       </c>
-      <c r="F108" s="54"/>
+      <c r="F108" s="61"/>
       <c r="I108" s="18">
         <f t="shared" si="7"/>
         <v>5.0000000000000002E-5</v>
@@ -19839,19 +20684,19 @@
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A109" s="9" t="s">
+      <c r="A109" s="41" t="s">
         <v>93</v>
       </c>
       <c r="B109" s="9">
         <v>0</v>
       </c>
-      <c r="C109" s="49"/>
-      <c r="D109" s="50"/>
-      <c r="E109" s="55">
+      <c r="C109" s="72"/>
+      <c r="D109" s="73"/>
+      <c r="E109" s="74">
         <f t="shared" ref="E109" si="11">(B109+0.001)/0.0201</f>
         <v>4.975124378109453E-2</v>
       </c>
-      <c r="F109" s="55"/>
+      <c r="F109" s="75"/>
       <c r="I109" s="18">
         <f>E109/1000000</f>
         <v>4.9751243781094531E-8</v>
@@ -19866,19 +20711,19 @@
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A110" s="6" t="s">
+      <c r="A110" s="5" t="s">
         <v>94</v>
       </c>
       <c r="B110" s="6">
         <v>0</v>
       </c>
-      <c r="C110" s="41"/>
-      <c r="D110" s="42"/>
-      <c r="E110" s="39">
+      <c r="C110" s="48"/>
+      <c r="D110" s="56"/>
+      <c r="E110" s="57">
         <f t="shared" ref="E110:E117" si="12">(B110+0.001)/0.0201</f>
         <v>4.975124378109453E-2</v>
       </c>
-      <c r="F110" s="39"/>
+      <c r="F110" s="58"/>
       <c r="I110" s="18">
         <f t="shared" ref="I110:I117" si="13">E110/1000000</f>
         <v>4.9751243781094531E-8</v>
@@ -19893,19 +20738,19 @@
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A111" s="6" t="s">
+      <c r="A111" s="5" t="s">
         <v>95</v>
       </c>
       <c r="B111" s="6">
         <v>0</v>
       </c>
-      <c r="C111" s="41"/>
-      <c r="D111" s="42"/>
-      <c r="E111" s="39">
+      <c r="C111" s="48"/>
+      <c r="D111" s="56"/>
+      <c r="E111" s="57">
         <f t="shared" si="12"/>
         <v>4.975124378109453E-2</v>
       </c>
-      <c r="F111" s="39"/>
+      <c r="F111" s="58"/>
       <c r="I111" s="18">
         <f t="shared" si="13"/>
         <v>4.9751243781094531E-8</v>
@@ -19920,19 +20765,19 @@
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A112" s="6" t="s">
+      <c r="A112" s="5" t="s">
         <v>96</v>
       </c>
       <c r="B112" s="6">
         <v>0</v>
       </c>
-      <c r="C112" s="41"/>
-      <c r="D112" s="42"/>
-      <c r="E112" s="39">
+      <c r="C112" s="48"/>
+      <c r="D112" s="56"/>
+      <c r="E112" s="57">
         <f t="shared" si="12"/>
         <v>4.975124378109453E-2</v>
       </c>
-      <c r="F112" s="39"/>
+      <c r="F112" s="58"/>
       <c r="I112" s="18">
         <f t="shared" si="13"/>
         <v>4.9751243781094531E-8</v>
@@ -19947,19 +20792,19 @@
       </c>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A113" s="6" t="s">
+      <c r="A113" s="5" t="s">
         <v>97</v>
       </c>
       <c r="B113" s="6">
         <v>0</v>
       </c>
-      <c r="C113" s="41"/>
-      <c r="D113" s="42"/>
-      <c r="E113" s="39">
+      <c r="C113" s="48"/>
+      <c r="D113" s="56"/>
+      <c r="E113" s="57">
         <f t="shared" si="12"/>
         <v>4.975124378109453E-2</v>
       </c>
-      <c r="F113" s="39"/>
+      <c r="F113" s="58"/>
       <c r="I113" s="18">
         <f t="shared" si="13"/>
         <v>4.9751243781094531E-8</v>
@@ -19974,19 +20819,19 @@
       </c>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A114" s="6" t="s">
+      <c r="A114" s="5" t="s">
         <v>98</v>
       </c>
       <c r="B114" s="6">
         <v>2E-3</v>
       </c>
-      <c r="C114" s="41"/>
-      <c r="D114" s="42"/>
-      <c r="E114" s="39">
+      <c r="C114" s="48"/>
+      <c r="D114" s="56"/>
+      <c r="E114" s="57">
         <f t="shared" si="12"/>
         <v>0.1492537313432836</v>
       </c>
-      <c r="F114" s="39"/>
+      <c r="F114" s="58"/>
       <c r="I114" s="18">
         <f t="shared" si="13"/>
         <v>1.492537313432836E-7</v>
@@ -20001,19 +20846,19 @@
       </c>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A115" s="6" t="s">
+      <c r="A115" s="5" t="s">
         <v>99</v>
       </c>
       <c r="B115" s="6">
         <v>0.01</v>
       </c>
-      <c r="C115" s="41"/>
-      <c r="D115" s="42"/>
-      <c r="E115" s="39">
+      <c r="C115" s="48"/>
+      <c r="D115" s="56"/>
+      <c r="E115" s="57">
         <f t="shared" si="12"/>
         <v>0.54726368159203975</v>
       </c>
-      <c r="F115" s="39"/>
+      <c r="F115" s="58"/>
       <c r="I115" s="18">
         <f t="shared" si="13"/>
         <v>5.4726368159203972E-7</v>
@@ -20028,19 +20873,19 @@
       </c>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A116" s="6" t="s">
+      <c r="A116" s="5" t="s">
         <v>100</v>
       </c>
       <c r="B116" s="6">
         <v>0</v>
       </c>
-      <c r="C116" s="41"/>
-      <c r="D116" s="42"/>
-      <c r="E116" s="39">
+      <c r="C116" s="48"/>
+      <c r="D116" s="56"/>
+      <c r="E116" s="57">
         <f t="shared" si="12"/>
         <v>4.975124378109453E-2</v>
       </c>
-      <c r="F116" s="39"/>
+      <c r="F116" s="58"/>
       <c r="I116" s="18">
         <f t="shared" si="13"/>
         <v>4.9751243781094531E-8</v>
@@ -20054,20 +20899,20 @@
         <v>8.9743582089552249E-4</v>
       </c>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A117" s="6" t="s">
+    <row r="117" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A117" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="B117" s="6">
+      <c r="B117" s="8">
         <v>0</v>
       </c>
-      <c r="C117" s="41"/>
-      <c r="D117" s="42"/>
-      <c r="E117" s="39">
+      <c r="C117" s="52"/>
+      <c r="D117" s="59"/>
+      <c r="E117" s="60">
         <f t="shared" si="12"/>
         <v>4.975124378109453E-2</v>
       </c>
-      <c r="F117" s="39"/>
+      <c r="F117" s="61"/>
       <c r="I117" s="18">
         <f t="shared" si="13"/>
         <v>4.9751243781094531E-8</v>
@@ -20081,68 +20926,126 @@
         <v>8.9743582089552249E-4</v>
       </c>
     </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="I120" t="s">
+        <v>25</v>
+      </c>
+      <c r="K120">
+        <v>62.005400000000002</v>
+      </c>
+    </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.25">
       <c r="H121" s="24"/>
-    </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A122" s="46" t="s">
+      <c r="I121" t="s">
+        <v>16</v>
+      </c>
+      <c r="K121">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A122" s="70" t="s">
         <v>27</v>
       </c>
-      <c r="B122" s="46"/>
-      <c r="C122" s="46"/>
-      <c r="D122" s="46"/>
-      <c r="E122" s="46"/>
-      <c r="F122" s="46"/>
-      <c r="G122" s="46"/>
-      <c r="H122" s="46"/>
+      <c r="B122" s="70"/>
+      <c r="C122" s="70"/>
+      <c r="D122" s="70"/>
+      <c r="E122" s="70"/>
+      <c r="F122" s="70"/>
+      <c r="G122" s="70"/>
+      <c r="H122" s="70"/>
+    </row>
+    <row r="123" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I123" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="J123" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K123" s="20" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="124" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="2" t="s">
+      <c r="A124" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B124" s="2" t="s">
+      <c r="B124" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="C124" s="2" t="s">
+      <c r="C124" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="D124" s="2"/>
-      <c r="E124" s="2" t="s">
+      <c r="D124" s="39"/>
+      <c r="E124" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="F124" s="2"/>
-      <c r="G124" s="37"/>
+      <c r="F124" s="40"/>
+      <c r="G124" s="35"/>
+      <c r="I124" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="J124" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="K124" s="17" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A125" s="3" t="s">
         <v>56</v>
       </c>
       <c r="B125" s="4"/>
-      <c r="C125" s="56">
+      <c r="C125" s="62">
         <v>2.5</v>
       </c>
-      <c r="D125" s="57"/>
-      <c r="E125" s="51">
+      <c r="D125" s="63"/>
+      <c r="E125" s="68">
         <v>0</v>
       </c>
-      <c r="F125" s="52"/>
-      <c r="G125" s="36"/>
+      <c r="F125" s="69"/>
+      <c r="G125" s="35"/>
+      <c r="I125" s="16">
+        <f t="shared" ref="I125:I132" si="16">C125/1000000</f>
+        <v>2.5000000000000002E-6</v>
+      </c>
+      <c r="J125" s="16">
+        <f>$K$120*I125</f>
+        <v>1.5501350000000002E-4</v>
+      </c>
+      <c r="K125" s="23">
+        <f>J125*1000</f>
+        <v>0.15501350000000003</v>
+      </c>
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A126" s="31" t="s">
         <v>11</v>
       </c>
       <c r="B126" s="2"/>
-      <c r="C126" s="58">
+      <c r="C126" s="66">
         <v>5</v>
       </c>
-      <c r="D126" s="59"/>
-      <c r="E126" s="44">
+      <c r="D126" s="67"/>
+      <c r="E126" s="50">
         <f>(B126-0.0011)/0.0019</f>
         <v>-0.57894736842105265</v>
       </c>
-      <c r="F126" s="45"/>
-      <c r="G126" s="36"/>
+      <c r="F126" s="51"/>
+      <c r="G126" s="35"/>
+      <c r="I126" s="18">
+        <f t="shared" si="16"/>
+        <v>5.0000000000000004E-6</v>
+      </c>
+      <c r="J126" s="18">
+        <f>$K$120*I126</f>
+        <v>3.1002700000000005E-4</v>
+      </c>
+      <c r="K126" s="21">
+        <f t="shared" ref="K126:K132" si="17">J126*1000</f>
+        <v>0.31002700000000005</v>
+      </c>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A127" s="5" t="s">
@@ -20151,247 +21054,427 @@
       <c r="B127" s="6">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="C127" s="41">
+      <c r="C127" s="48">
         <v>10</v>
       </c>
-      <c r="D127" s="43"/>
-      <c r="E127" s="44">
-        <f t="shared" ref="E127:E141" si="16">(B127-0.0011)/0.0019</f>
+      <c r="D127" s="49"/>
+      <c r="E127" s="50">
+        <f t="shared" ref="E127:E141" si="18">(B127-0.0011)/0.0019</f>
         <v>11</v>
       </c>
-      <c r="F127" s="45"/>
-      <c r="G127" s="36"/>
+      <c r="F127" s="51"/>
+      <c r="G127" s="35"/>
+      <c r="I127" s="18">
+        <f t="shared" si="16"/>
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="J127" s="18">
+        <f t="shared" ref="J127:J132" si="19">$K$120*I127</f>
+        <v>6.2005400000000009E-4</v>
+      </c>
+      <c r="K127" s="21">
+        <f t="shared" si="17"/>
+        <v>0.62005400000000011</v>
+      </c>
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A128" s="5" t="s">
         <v>12</v>
       </c>
       <c r="B128" s="6"/>
-      <c r="C128" s="41">
+      <c r="C128" s="48">
         <v>25</v>
       </c>
-      <c r="D128" s="43"/>
-      <c r="E128" s="44">
+      <c r="D128" s="49"/>
+      <c r="E128" s="50">
+        <f t="shared" si="18"/>
+        <v>-0.57894736842105265</v>
+      </c>
+      <c r="F128" s="51"/>
+      <c r="G128" s="35"/>
+      <c r="I128" s="18">
         <f t="shared" si="16"/>
-        <v>-0.57894736842105265</v>
-      </c>
-      <c r="F128" s="45"/>
-      <c r="G128" s="36"/>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2.5000000000000001E-5</v>
+      </c>
+      <c r="J128" s="18">
+        <f t="shared" si="19"/>
+        <v>1.550135E-3</v>
+      </c>
+      <c r="K128" s="21">
+        <f t="shared" si="17"/>
+        <v>1.550135</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A129" s="5" t="s">
         <v>3</v>
       </c>
       <c r="B129" s="6">
         <v>0.10199999999999999</v>
       </c>
-      <c r="C129" s="41">
+      <c r="C129" s="48">
         <v>50</v>
       </c>
-      <c r="D129" s="43"/>
-      <c r="E129" s="44">
+      <c r="D129" s="49"/>
+      <c r="E129" s="50">
+        <f t="shared" si="18"/>
+        <v>53.105263157894733</v>
+      </c>
+      <c r="F129" s="51"/>
+      <c r="G129" s="35"/>
+      <c r="I129" s="18">
         <f t="shared" si="16"/>
-        <v>53.105263157894733</v>
-      </c>
-      <c r="F129" s="45"/>
-      <c r="G129" s="36"/>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+        <v>5.0000000000000002E-5</v>
+      </c>
+      <c r="J129" s="18">
+        <f t="shared" si="19"/>
+        <v>3.10027E-3</v>
+      </c>
+      <c r="K129" s="21">
+        <f t="shared" si="17"/>
+        <v>3.1002700000000001</v>
+      </c>
+    </row>
+    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A130" s="5" t="s">
         <v>4</v>
       </c>
       <c r="B130" s="6">
         <v>0.19400000000000001</v>
       </c>
-      <c r="C130" s="41">
+      <c r="C130" s="48">
         <v>100</v>
       </c>
-      <c r="D130" s="43"/>
-      <c r="E130" s="44">
+      <c r="D130" s="49"/>
+      <c r="E130" s="50">
+        <f t="shared" si="18"/>
+        <v>101.5263157894737</v>
+      </c>
+      <c r="F130" s="51"/>
+      <c r="G130" s="35"/>
+      <c r="I130" s="18">
         <f t="shared" si="16"/>
-        <v>101.5263157894737</v>
-      </c>
-      <c r="F130" s="45"/>
-      <c r="G130" s="36"/>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+        <v>1E-4</v>
+      </c>
+      <c r="J130" s="18">
+        <f t="shared" si="19"/>
+        <v>6.20054E-3</v>
+      </c>
+      <c r="K130" s="21">
+        <f t="shared" si="17"/>
+        <v>6.2005400000000002</v>
+      </c>
+    </row>
+    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A131" s="5" t="s">
         <v>5</v>
       </c>
       <c r="B131" s="6">
         <v>0.376</v>
       </c>
-      <c r="C131" s="41">
+      <c r="C131" s="48">
         <v>200</v>
       </c>
-      <c r="D131" s="43"/>
-      <c r="E131" s="44">
+      <c r="D131" s="49"/>
+      <c r="E131" s="50">
+        <f t="shared" si="18"/>
+        <v>197.31578947368422</v>
+      </c>
+      <c r="F131" s="51"/>
+      <c r="G131" s="35"/>
+      <c r="I131" s="18">
         <f t="shared" si="16"/>
-        <v>197.31578947368422</v>
-      </c>
-      <c r="F131" s="45"/>
-      <c r="G131" s="36"/>
-    </row>
-    <row r="132" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="J131" s="18">
+        <f t="shared" si="19"/>
+        <v>1.240108E-2</v>
+      </c>
+      <c r="K131" s="21">
+        <f t="shared" si="17"/>
+        <v>12.40108</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A132" s="7" t="s">
         <v>6</v>
       </c>
       <c r="B132" s="8">
         <v>0.96699999999999997</v>
       </c>
-      <c r="C132" s="47">
+      <c r="C132" s="52">
         <v>500</v>
       </c>
-      <c r="D132" s="48"/>
-      <c r="E132" s="44">
+      <c r="D132" s="53"/>
+      <c r="E132" s="54">
+        <f t="shared" si="18"/>
+        <v>508.36842105263156</v>
+      </c>
+      <c r="F132" s="55"/>
+      <c r="G132" s="35"/>
+      <c r="I132" s="19">
         <f t="shared" si="16"/>
-        <v>508.36842105263156</v>
-      </c>
-      <c r="F132" s="45"/>
-      <c r="G132" s="36"/>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A133" s="9" t="s">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="J132" s="19">
+        <f t="shared" si="19"/>
+        <v>3.1002700000000001E-2</v>
+      </c>
+      <c r="K132" s="22">
+        <f t="shared" si="17"/>
+        <v>31.002700000000001</v>
+      </c>
+    </row>
+    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A133" s="41" t="s">
         <v>93</v>
       </c>
       <c r="B133" s="9">
         <v>8.9999999999999993E-3</v>
       </c>
-      <c r="C133" s="49"/>
-      <c r="D133" s="60"/>
-      <c r="E133" s="44">
-        <f t="shared" si="16"/>
+      <c r="C133" s="72"/>
+      <c r="D133" s="78"/>
+      <c r="E133" s="79">
+        <f t="shared" si="18"/>
         <v>4.1578947368421044</v>
       </c>
-      <c r="F133" s="45"/>
-      <c r="G133" s="36"/>
-    </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A134" s="6" t="s">
+      <c r="F133" s="80"/>
+      <c r="G133" s="35"/>
+      <c r="I133" s="18">
+        <f>E133/1000000</f>
+        <v>4.1578947368421041E-6</v>
+      </c>
+      <c r="J133" s="18">
+        <f>$K$120*I133*$K$121</f>
+        <v>2.578119263157894E-7</v>
+      </c>
+      <c r="K133" s="21">
+        <f t="shared" ref="K133:K141" si="20">J133*1000000</f>
+        <v>0.25781192631578942</v>
+      </c>
+    </row>
+    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A134" s="5" t="s">
         <v>94</v>
       </c>
       <c r="B134" s="6">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="C134" s="41"/>
-      <c r="D134" s="43"/>
-      <c r="E134" s="44">
-        <f t="shared" si="16"/>
+      <c r="C134" s="48"/>
+      <c r="D134" s="49"/>
+      <c r="E134" s="50">
+        <f t="shared" si="18"/>
         <v>2.5789473684210527</v>
       </c>
-      <c r="F134" s="45"/>
-      <c r="G134" s="36"/>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A135" s="6" t="s">
+      <c r="F134" s="51"/>
+      <c r="G134" s="35"/>
+      <c r="I134" s="18">
+        <f>E134/1000000</f>
+        <v>2.5789473684210527E-6</v>
+      </c>
+      <c r="J134" s="18">
+        <f t="shared" ref="J134:J141" si="21">$K$120*I134*$K$121</f>
+        <v>1.5990866315789475E-7</v>
+      </c>
+      <c r="K134" s="21">
+        <f t="shared" si="20"/>
+        <v>0.15990866315789476</v>
+      </c>
+    </row>
+    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A135" s="5" t="s">
         <v>95</v>
       </c>
       <c r="B135" s="6">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="C135" s="41"/>
-      <c r="D135" s="43"/>
-      <c r="E135" s="44">
-        <f t="shared" si="16"/>
+      <c r="C135" s="48"/>
+      <c r="D135" s="49"/>
+      <c r="E135" s="50">
+        <f t="shared" si="18"/>
         <v>5.2105263157894735</v>
       </c>
-      <c r="F135" s="45"/>
-      <c r="G135" s="36"/>
-    </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A136" s="6" t="s">
+      <c r="F135" s="51"/>
+      <c r="G135" s="35"/>
+      <c r="I135" s="18">
+        <f t="shared" ref="I135:I141" si="22">E135/1000000</f>
+        <v>5.2105263157894739E-6</v>
+      </c>
+      <c r="J135" s="18">
+        <f t="shared" si="21"/>
+        <v>3.2308076842105265E-7</v>
+      </c>
+      <c r="K135" s="21">
+        <f t="shared" si="20"/>
+        <v>0.32308076842105266</v>
+      </c>
+    </row>
+    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A136" s="5" t="s">
         <v>96</v>
       </c>
       <c r="B136" s="6">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="C136" s="41"/>
-      <c r="D136" s="43"/>
-      <c r="E136" s="44">
-        <f t="shared" si="16"/>
+      <c r="C136" s="48"/>
+      <c r="D136" s="49"/>
+      <c r="E136" s="50">
+        <f t="shared" si="18"/>
         <v>3.1052631578947367</v>
       </c>
-      <c r="F136" s="45"/>
-      <c r="G136" s="36"/>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A137" s="6" t="s">
+      <c r="F136" s="51"/>
+      <c r="G136" s="35"/>
+      <c r="I136" s="18">
+        <f t="shared" si="22"/>
+        <v>3.1052631578947368E-6</v>
+      </c>
+      <c r="J136" s="18">
+        <f t="shared" si="21"/>
+        <v>1.9254308421052633E-7</v>
+      </c>
+      <c r="K136" s="21">
+        <f t="shared" si="20"/>
+        <v>0.19254308421052632</v>
+      </c>
+    </row>
+    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A137" s="5" t="s">
         <v>97</v>
       </c>
       <c r="B137" s="6">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="C137" s="41"/>
-      <c r="D137" s="43"/>
-      <c r="E137" s="44">
-        <f t="shared" si="16"/>
+      <c r="C137" s="48"/>
+      <c r="D137" s="49"/>
+      <c r="E137" s="50">
+        <f t="shared" si="18"/>
         <v>2.5789473684210527</v>
       </c>
-      <c r="F137" s="45"/>
-      <c r="G137" s="36"/>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A138" s="6" t="s">
+      <c r="F137" s="51"/>
+      <c r="G137" s="35"/>
+      <c r="I137" s="18">
+        <f t="shared" si="22"/>
+        <v>2.5789473684210527E-6</v>
+      </c>
+      <c r="J137" s="18">
+        <f t="shared" si="21"/>
+        <v>1.5990866315789475E-7</v>
+      </c>
+      <c r="K137" s="21">
+        <f t="shared" si="20"/>
+        <v>0.15990866315789476</v>
+      </c>
+    </row>
+    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A138" s="5" t="s">
         <v>98</v>
       </c>
       <c r="B138" s="6">
         <v>4.4999999999999998E-2</v>
       </c>
-      <c r="C138" s="41"/>
-      <c r="D138" s="43"/>
-      <c r="E138" s="44">
-        <f t="shared" si="16"/>
+      <c r="C138" s="48"/>
+      <c r="D138" s="49"/>
+      <c r="E138" s="50">
+        <f t="shared" si="18"/>
         <v>23.105263157894736</v>
       </c>
-      <c r="F138" s="45"/>
-      <c r="G138" s="36"/>
-    </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A139" s="6" t="s">
+      <c r="F138" s="51"/>
+      <c r="G138" s="35"/>
+      <c r="I138" s="18">
+        <f t="shared" si="22"/>
+        <v>2.3105263157894737E-5</v>
+      </c>
+      <c r="J138" s="18">
+        <f t="shared" si="21"/>
+        <v>1.4326510842105265E-6</v>
+      </c>
+      <c r="K138" s="21">
+        <f t="shared" si="20"/>
+        <v>1.4326510842105264</v>
+      </c>
+    </row>
+    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A139" s="5" t="s">
         <v>99</v>
       </c>
       <c r="B139" s="6">
         <v>3.5999999999999997E-2</v>
       </c>
-      <c r="C139" s="41"/>
-      <c r="D139" s="43"/>
-      <c r="E139" s="44">
-        <f t="shared" si="16"/>
+      <c r="C139" s="48"/>
+      <c r="D139" s="49"/>
+      <c r="E139" s="50">
+        <f t="shared" si="18"/>
         <v>18.368421052631579</v>
       </c>
-      <c r="F139" s="45"/>
-      <c r="G139" s="36"/>
-    </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A140" s="6" t="s">
+      <c r="F139" s="51"/>
+      <c r="G139" s="35"/>
+      <c r="I139" s="18">
+        <f t="shared" si="22"/>
+        <v>1.8368421052631577E-5</v>
+      </c>
+      <c r="J139" s="18">
+        <f t="shared" si="21"/>
+        <v>1.1389412947368421E-6</v>
+      </c>
+      <c r="K139" s="21">
+        <f t="shared" si="20"/>
+        <v>1.138941294736842</v>
+      </c>
+    </row>
+    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A140" s="5" t="s">
         <v>100</v>
       </c>
       <c r="B140" s="6">
         <v>2.5999999999999999E-2</v>
       </c>
-      <c r="C140" s="41"/>
-      <c r="D140" s="43"/>
-      <c r="E140" s="44">
-        <f t="shared" si="16"/>
+      <c r="C140" s="48"/>
+      <c r="D140" s="49"/>
+      <c r="E140" s="50">
+        <f t="shared" si="18"/>
         <v>13.105263157894736</v>
       </c>
-      <c r="F140" s="45"/>
-      <c r="G140" s="36"/>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A141" s="6" t="s">
+      <c r="F140" s="51"/>
+      <c r="G140" s="35"/>
+      <c r="I140" s="18">
+        <f t="shared" si="22"/>
+        <v>1.3105263157894736E-5</v>
+      </c>
+      <c r="J140" s="18">
+        <f t="shared" si="21"/>
+        <v>8.125970842105263E-7</v>
+      </c>
+      <c r="K140" s="21">
+        <f t="shared" si="20"/>
+        <v>0.81259708421052634</v>
+      </c>
+    </row>
+    <row r="141" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A141" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="B141" s="6">
+      <c r="B141" s="8">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="C141" s="41"/>
-      <c r="D141" s="43"/>
-      <c r="E141" s="44">
-        <f t="shared" si="16"/>
+      <c r="C141" s="52"/>
+      <c r="D141" s="53"/>
+      <c r="E141" s="54">
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
-      <c r="F141" s="45"/>
+      <c r="F141" s="55"/>
+      <c r="I141" s="18">
+        <f t="shared" si="22"/>
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="J141" s="18">
+        <f t="shared" si="21"/>
+        <v>6.20054E-8</v>
+      </c>
+      <c r="K141" s="21">
+        <f t="shared" si="20"/>
+        <v>6.2005400000000002E-2</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="94">
@@ -20494,4 +21577,2029 @@
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90F586EF-906E-4D10-BA9A-6359CCC6DFA0}">
+  <dimension ref="A1:E37"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="43" t="s">
+        <v>111</v>
+      </c>
+      <c r="B1" s="43" t="s">
+        <v>108</v>
+      </c>
+      <c r="C1" s="43" t="s">
+        <v>109</v>
+      </c>
+      <c r="D1" s="45" t="s">
+        <v>110</v>
+      </c>
+      <c r="E1" s="43" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="44">
+        <v>45834</v>
+      </c>
+      <c r="B2" s="42" t="s">
+        <v>105</v>
+      </c>
+      <c r="C2" s="6">
+        <v>1</v>
+      </c>
+      <c r="D2" s="46" t="str">
+        <f>B2&amp;C2</f>
+        <v>MT1</v>
+      </c>
+      <c r="E2" s="47">
+        <v>0.17960875225806455</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="44">
+        <v>45834</v>
+      </c>
+      <c r="B3" s="42" t="s">
+        <v>105</v>
+      </c>
+      <c r="C3" s="6">
+        <v>2</v>
+      </c>
+      <c r="D3" s="46" t="str">
+        <f t="shared" ref="D3:D10" si="0">B3&amp;C3</f>
+        <v>MT2</v>
+      </c>
+      <c r="E3" s="47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="44">
+        <v>45834</v>
+      </c>
+      <c r="B4" s="42" t="s">
+        <v>107</v>
+      </c>
+      <c r="C4" s="6">
+        <v>1</v>
+      </c>
+      <c r="D4" s="46" t="str">
+        <f t="shared" si="0"/>
+        <v>MN1</v>
+      </c>
+      <c r="E4" s="47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="44">
+        <v>45834</v>
+      </c>
+      <c r="B5" s="42" t="s">
+        <v>107</v>
+      </c>
+      <c r="C5" s="6">
+        <v>2</v>
+      </c>
+      <c r="D5" s="46" t="str">
+        <f t="shared" si="0"/>
+        <v>MN2</v>
+      </c>
+      <c r="E5" s="47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="44">
+        <v>45834</v>
+      </c>
+      <c r="B6" s="42" t="s">
+        <v>107</v>
+      </c>
+      <c r="C6" s="6">
+        <v>3</v>
+      </c>
+      <c r="D6" s="46" t="str">
+        <f t="shared" si="0"/>
+        <v>MN3</v>
+      </c>
+      <c r="E6" s="47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="44">
+        <v>45834</v>
+      </c>
+      <c r="B7" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="6">
+        <v>1</v>
+      </c>
+      <c r="D7" s="46" t="str">
+        <f t="shared" si="0"/>
+        <v>L1</v>
+      </c>
+      <c r="E7" s="47">
+        <v>5.9352352258064525E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="44">
+        <v>45834</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="6">
+        <v>2</v>
+      </c>
+      <c r="D8" s="46" t="str">
+        <f t="shared" si="0"/>
+        <v>L2</v>
+      </c>
+      <c r="E8" s="47">
+        <v>1.7390627135483876</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="44">
+        <v>45834</v>
+      </c>
+      <c r="B9" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="6">
+        <v>3</v>
+      </c>
+      <c r="D9" s="46" t="str">
+        <f t="shared" si="0"/>
+        <v>L3</v>
+      </c>
+      <c r="E9" s="47">
+        <v>0.66645321032258065</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="44">
+        <v>45834</v>
+      </c>
+      <c r="B10" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="6">
+        <v>4</v>
+      </c>
+      <c r="D10" s="46" t="str">
+        <f t="shared" si="0"/>
+        <v>L4</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="44">
+        <v>45861</v>
+      </c>
+      <c r="B11" s="42" t="s">
+        <v>105</v>
+      </c>
+      <c r="C11" s="6">
+        <v>1</v>
+      </c>
+      <c r="D11" s="46" t="str">
+        <f>B11&amp;C11</f>
+        <v>MT1</v>
+      </c>
+      <c r="E11" s="47">
+        <v>0.17960875225806455</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="44">
+        <v>45861</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>105</v>
+      </c>
+      <c r="C12" s="6">
+        <v>2</v>
+      </c>
+      <c r="D12" s="46" t="str">
+        <f t="shared" ref="D12:D19" si="1">B12&amp;C12</f>
+        <v>MT2</v>
+      </c>
+      <c r="E12" s="47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="44">
+        <v>45861</v>
+      </c>
+      <c r="B13" s="42" t="s">
+        <v>107</v>
+      </c>
+      <c r="C13" s="6">
+        <v>1</v>
+      </c>
+      <c r="D13" s="46" t="str">
+        <f t="shared" si="1"/>
+        <v>MN1</v>
+      </c>
+      <c r="E13" s="47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="44">
+        <v>45861</v>
+      </c>
+      <c r="B14" s="42" t="s">
+        <v>107</v>
+      </c>
+      <c r="C14" s="6">
+        <v>2</v>
+      </c>
+      <c r="D14" s="46" t="str">
+        <f t="shared" si="1"/>
+        <v>MN2</v>
+      </c>
+      <c r="E14" s="47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="44">
+        <v>45861</v>
+      </c>
+      <c r="B15" s="42" t="s">
+        <v>107</v>
+      </c>
+      <c r="C15" s="6">
+        <v>3</v>
+      </c>
+      <c r="D15" s="46" t="str">
+        <f t="shared" si="1"/>
+        <v>MN3</v>
+      </c>
+      <c r="E15" s="47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="44">
+        <v>45861</v>
+      </c>
+      <c r="B16" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="6">
+        <v>1</v>
+      </c>
+      <c r="D16" s="46" t="str">
+        <f t="shared" si="1"/>
+        <v>L1</v>
+      </c>
+      <c r="E16" s="47">
+        <v>5.9352352258064525E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="44">
+        <v>45861</v>
+      </c>
+      <c r="B17" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="6">
+        <v>2</v>
+      </c>
+      <c r="D17" s="46" t="str">
+        <f t="shared" si="1"/>
+        <v>L2</v>
+      </c>
+      <c r="E17" s="47">
+        <v>1.7390627135483876</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="44">
+        <v>45861</v>
+      </c>
+      <c r="B18" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="6">
+        <v>3</v>
+      </c>
+      <c r="D18" s="46" t="str">
+        <f t="shared" si="1"/>
+        <v>L3</v>
+      </c>
+      <c r="E18" s="47">
+        <v>0.66645321032258065</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="44">
+        <v>45861</v>
+      </c>
+      <c r="B19" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="6">
+        <v>4</v>
+      </c>
+      <c r="D19" s="46" t="str">
+        <f t="shared" si="1"/>
+        <v>L4</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="44">
+        <v>45900</v>
+      </c>
+      <c r="B20" s="42" t="s">
+        <v>105</v>
+      </c>
+      <c r="C20" s="6">
+        <v>1</v>
+      </c>
+      <c r="D20" s="46" t="str">
+        <f>B20&amp;C20</f>
+        <v>MT1</v>
+      </c>
+      <c r="E20" s="47">
+        <v>3.5325317500000009E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="44">
+        <v>45900</v>
+      </c>
+      <c r="B21" s="42" t="s">
+        <v>105</v>
+      </c>
+      <c r="C21" s="6">
+        <v>2</v>
+      </c>
+      <c r="D21" s="46" t="str">
+        <f t="shared" ref="D21:D28" si="2">B21&amp;C21</f>
+        <v>MT2</v>
+      </c>
+      <c r="E21" s="47">
+        <v>2.3577770425000004</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="44">
+        <v>45900</v>
+      </c>
+      <c r="B22" s="42" t="s">
+        <v>107</v>
+      </c>
+      <c r="C22" s="6">
+        <v>1</v>
+      </c>
+      <c r="D22" s="46" t="str">
+        <f t="shared" si="2"/>
+        <v>MN1</v>
+      </c>
+      <c r="E22" s="47">
+        <v>2.4051280000000001E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="44">
+        <v>45900</v>
+      </c>
+      <c r="B23" s="42" t="s">
+        <v>107</v>
+      </c>
+      <c r="C23" s="6">
+        <v>2</v>
+      </c>
+      <c r="D23" s="46" t="str">
+        <f t="shared" si="2"/>
+        <v>MN2</v>
+      </c>
+      <c r="E23" s="47">
+        <v>1.089823625E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="44">
+        <v>45900</v>
+      </c>
+      <c r="B24" s="42" t="s">
+        <v>107</v>
+      </c>
+      <c r="C24" s="6">
+        <v>3</v>
+      </c>
+      <c r="D24" s="46" t="str">
+        <f t="shared" si="2"/>
+        <v>MN3</v>
+      </c>
+      <c r="E24" s="47">
+        <v>1.8414261250000005E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="44">
+        <v>45900</v>
+      </c>
+      <c r="B25" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25" s="6">
+        <v>1</v>
+      </c>
+      <c r="D25" s="46" t="str">
+        <f t="shared" si="2"/>
+        <v>L1</v>
+      </c>
+      <c r="E25" s="47">
+        <v>0.59339017375000014</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="44">
+        <v>45900</v>
+      </c>
+      <c r="B26" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26" s="6">
+        <v>2</v>
+      </c>
+      <c r="D26" s="46" t="str">
+        <f t="shared" si="2"/>
+        <v>L2</v>
+      </c>
+      <c r="E26" s="47">
+        <v>8.605848625000001E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="44">
+        <v>45900</v>
+      </c>
+      <c r="B27" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27" s="6">
+        <v>3</v>
+      </c>
+      <c r="D27" s="46" t="str">
+        <f t="shared" si="2"/>
+        <v>L3</v>
+      </c>
+      <c r="E27" s="47">
+        <v>5.4115380000000005E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="44">
+        <v>45900</v>
+      </c>
+      <c r="B28" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="C28" s="6">
+        <v>4</v>
+      </c>
+      <c r="D28" s="46" t="str">
+        <f t="shared" si="2"/>
+        <v>L4</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="44">
+        <v>45924</v>
+      </c>
+      <c r="B29" s="42" t="s">
+        <v>105</v>
+      </c>
+      <c r="C29" s="6">
+        <v>1</v>
+      </c>
+      <c r="D29" s="46" t="str">
+        <f>B29&amp;C29</f>
+        <v>MT1</v>
+      </c>
+      <c r="E29" s="47">
+        <v>5.7244500612244911E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="44">
+        <v>45924</v>
+      </c>
+      <c r="B30" s="42" t="s">
+        <v>105</v>
+      </c>
+      <c r="C30" s="6">
+        <v>2</v>
+      </c>
+      <c r="D30" s="46" t="str">
+        <f t="shared" ref="D30:D37" si="3">B30&amp;C30</f>
+        <v>MT2</v>
+      </c>
+      <c r="E30" s="47">
+        <v>0.39408513122448985</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="44">
+        <v>45924</v>
+      </c>
+      <c r="B31" s="42" t="s">
+        <v>107</v>
+      </c>
+      <c r="C31" s="6">
+        <v>1</v>
+      </c>
+      <c r="D31" s="46" t="str">
+        <f t="shared" si="3"/>
+        <v>MN1</v>
+      </c>
+      <c r="E31" s="47">
+        <v>0.12718954959183673</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="44">
+        <v>45924</v>
+      </c>
+      <c r="B32" s="42" t="s">
+        <v>107</v>
+      </c>
+      <c r="C32" s="6">
+        <v>2</v>
+      </c>
+      <c r="D32" s="46" t="str">
+        <f t="shared" si="3"/>
+        <v>MN2</v>
+      </c>
+      <c r="E32" s="47">
+        <v>3.5156590408163269E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="44">
+        <v>45924</v>
+      </c>
+      <c r="B33" s="42" t="s">
+        <v>107</v>
+      </c>
+      <c r="C33" s="6">
+        <v>3</v>
+      </c>
+      <c r="D33" s="46" t="str">
+        <f t="shared" si="3"/>
+        <v>MN3</v>
+      </c>
+      <c r="E33" s="47">
+        <v>2.5953294489795921E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="44">
+        <v>45924</v>
+      </c>
+      <c r="B34" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="6">
+        <v>1</v>
+      </c>
+      <c r="D34" s="46" t="str">
+        <f t="shared" si="3"/>
+        <v>L1</v>
+      </c>
+      <c r="E34" s="47">
+        <v>0.19713459857142859</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="44">
+        <v>45924</v>
+      </c>
+      <c r="B35" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="C35" s="6">
+        <v>2</v>
+      </c>
+      <c r="D35" s="46" t="str">
+        <f t="shared" si="3"/>
+        <v>L2</v>
+      </c>
+      <c r="E35" s="47">
+        <v>0.38856315367346944</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="44">
+        <v>45924</v>
+      </c>
+      <c r="B36" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="C36" s="6">
+        <v>3</v>
+      </c>
+      <c r="D36" s="46" t="str">
+        <f t="shared" si="3"/>
+        <v>L3</v>
+      </c>
+      <c r="E36" s="47">
+        <v>0.39408513122448985</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="44">
+        <v>45924</v>
+      </c>
+      <c r="B37" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="C37" s="6">
+        <v>4</v>
+      </c>
+      <c r="D37" s="46" t="str">
+        <f t="shared" si="3"/>
+        <v>L4</v>
+      </c>
+      <c r="E37" s="47">
+        <v>4.6200545510204097E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4198991-18A6-470D-B4B1-E513F9C4E059}">
+  <dimension ref="A1:E37"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="43" t="s">
+        <v>111</v>
+      </c>
+      <c r="B1" s="43" t="s">
+        <v>108</v>
+      </c>
+      <c r="C1" s="43" t="s">
+        <v>109</v>
+      </c>
+      <c r="D1" s="45" t="s">
+        <v>110</v>
+      </c>
+      <c r="E1" s="43" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="44">
+        <v>45834</v>
+      </c>
+      <c r="B2" s="42" t="s">
+        <v>105</v>
+      </c>
+      <c r="C2" s="6">
+        <v>1</v>
+      </c>
+      <c r="D2" s="46" t="str">
+        <f>B2&amp;C2</f>
+        <v>MT1</v>
+      </c>
+      <c r="E2" s="47">
+        <v>1.6712102647058826E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="44">
+        <v>45834</v>
+      </c>
+      <c r="B3" s="42" t="s">
+        <v>105</v>
+      </c>
+      <c r="C3" s="6">
+        <v>2</v>
+      </c>
+      <c r="D3" s="46" t="str">
+        <f t="shared" ref="D3:D10" si="0">B3&amp;C3</f>
+        <v>MT2</v>
+      </c>
+      <c r="E3" s="47">
+        <v>4.3327673529411775E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="44">
+        <v>45834</v>
+      </c>
+      <c r="B4" s="42" t="s">
+        <v>107</v>
+      </c>
+      <c r="C4" s="6">
+        <v>1</v>
+      </c>
+      <c r="D4" s="46" t="str">
+        <f t="shared" si="0"/>
+        <v>MN1</v>
+      </c>
+      <c r="E4" s="47">
+        <v>4.3327673529411775E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="44">
+        <v>45834</v>
+      </c>
+      <c r="B5" s="42" t="s">
+        <v>107</v>
+      </c>
+      <c r="C5" s="6">
+        <v>2</v>
+      </c>
+      <c r="D5" s="46" t="str">
+        <f t="shared" si="0"/>
+        <v>MN2</v>
+      </c>
+      <c r="E5" s="47">
+        <v>4.3327673529411775E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="44">
+        <v>45834</v>
+      </c>
+      <c r="B6" s="42" t="s">
+        <v>107</v>
+      </c>
+      <c r="C6" s="6">
+        <v>3</v>
+      </c>
+      <c r="D6" s="46" t="str">
+        <f t="shared" si="0"/>
+        <v>MN3</v>
+      </c>
+      <c r="E6" s="47">
+        <v>4.3327673529411775E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="44">
+        <v>45834</v>
+      </c>
+      <c r="B7" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="6">
+        <v>1</v>
+      </c>
+      <c r="D7" s="46" t="str">
+        <f t="shared" si="0"/>
+        <v>L1</v>
+      </c>
+      <c r="E7" s="47">
+        <v>9.6381967647058819E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="44">
+        <v>45834</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="6">
+        <v>2</v>
+      </c>
+      <c r="D8" s="46" t="str">
+        <f t="shared" si="0"/>
+        <v>L2</v>
+      </c>
+      <c r="E8" s="47">
+        <v>3.881805852941176E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="44">
+        <v>45834</v>
+      </c>
+      <c r="B9" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="6">
+        <v>3</v>
+      </c>
+      <c r="D9" s="46" t="str">
+        <f t="shared" si="0"/>
+        <v>L3</v>
+      </c>
+      <c r="E9" s="47">
+        <v>1.2290911470588233E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="44">
+        <v>45834</v>
+      </c>
+      <c r="B10" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="6">
+        <v>4</v>
+      </c>
+      <c r="D10" s="46" t="str">
+        <f t="shared" si="0"/>
+        <v>L4</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="44">
+        <v>45861</v>
+      </c>
+      <c r="B11" s="42" t="s">
+        <v>105</v>
+      </c>
+      <c r="C11" s="6">
+        <v>1</v>
+      </c>
+      <c r="D11" s="46" t="str">
+        <f>B11&amp;C11</f>
+        <v>MT1</v>
+      </c>
+      <c r="E11" s="47">
+        <v>1.6712102647058826E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="44">
+        <v>45861</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>105</v>
+      </c>
+      <c r="C12" s="6">
+        <v>2</v>
+      </c>
+      <c r="D12" s="46" t="str">
+        <f t="shared" ref="D12:D19" si="1">B12&amp;C12</f>
+        <v>MT2</v>
+      </c>
+      <c r="E12" s="47">
+        <v>4.3327673529411775E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="44">
+        <v>45861</v>
+      </c>
+      <c r="B13" s="42" t="s">
+        <v>107</v>
+      </c>
+      <c r="C13" s="6">
+        <v>1</v>
+      </c>
+      <c r="D13" s="46" t="str">
+        <f t="shared" si="1"/>
+        <v>MN1</v>
+      </c>
+      <c r="E13" s="47">
+        <v>4.3327673529411775E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="44">
+        <v>45861</v>
+      </c>
+      <c r="B14" s="42" t="s">
+        <v>107</v>
+      </c>
+      <c r="C14" s="6">
+        <v>2</v>
+      </c>
+      <c r="D14" s="46" t="str">
+        <f t="shared" si="1"/>
+        <v>MN2</v>
+      </c>
+      <c r="E14" s="47">
+        <v>4.3327673529411775E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="44">
+        <v>45861</v>
+      </c>
+      <c r="B15" s="42" t="s">
+        <v>107</v>
+      </c>
+      <c r="C15" s="6">
+        <v>3</v>
+      </c>
+      <c r="D15" s="46" t="str">
+        <f t="shared" si="1"/>
+        <v>MN3</v>
+      </c>
+      <c r="E15" s="47">
+        <v>4.3327673529411775E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="44">
+        <v>45861</v>
+      </c>
+      <c r="B16" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="6">
+        <v>1</v>
+      </c>
+      <c r="D16" s="46" t="str">
+        <f t="shared" si="1"/>
+        <v>L1</v>
+      </c>
+      <c r="E16" s="47">
+        <v>9.6381967647058819E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="44">
+        <v>45861</v>
+      </c>
+      <c r="B17" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="6">
+        <v>2</v>
+      </c>
+      <c r="D17" s="46" t="str">
+        <f t="shared" si="1"/>
+        <v>L2</v>
+      </c>
+      <c r="E17" s="47">
+        <v>3.881805852941176E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="44">
+        <v>45861</v>
+      </c>
+      <c r="B18" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="6">
+        <v>3</v>
+      </c>
+      <c r="D18" s="46" t="str">
+        <f t="shared" si="1"/>
+        <v>L3</v>
+      </c>
+      <c r="E18" s="47">
+        <v>1.2290911470588233E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="44">
+        <v>45861</v>
+      </c>
+      <c r="B19" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="6">
+        <v>4</v>
+      </c>
+      <c r="D19" s="46" t="str">
+        <f t="shared" si="1"/>
+        <v>L4</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="44">
+        <v>45900</v>
+      </c>
+      <c r="B20" s="42" t="s">
+        <v>105</v>
+      </c>
+      <c r="C20" s="6">
+        <v>1</v>
+      </c>
+      <c r="D20" s="46" t="str">
+        <f>B20&amp;C20</f>
+        <v>MT1</v>
+      </c>
+      <c r="E20" s="47">
+        <v>1.2823549763033177E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="44">
+        <v>45900</v>
+      </c>
+      <c r="B21" s="42" t="s">
+        <v>105</v>
+      </c>
+      <c r="C21" s="6">
+        <v>2</v>
+      </c>
+      <c r="D21" s="46" t="str">
+        <f t="shared" ref="D21:D28" si="2">B21&amp;C21</f>
+        <v>MT2</v>
+      </c>
+      <c r="E21" s="47">
+        <v>8.5490331753554491E-4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="44">
+        <v>45900</v>
+      </c>
+      <c r="B22" s="42" t="s">
+        <v>107</v>
+      </c>
+      <c r="C22" s="6">
+        <v>1</v>
+      </c>
+      <c r="D22" s="46" t="str">
+        <f t="shared" si="2"/>
+        <v>MN1</v>
+      </c>
+      <c r="E22" s="47">
+        <v>8.5490331753554491E-4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="44">
+        <v>45900</v>
+      </c>
+      <c r="B23" s="42" t="s">
+        <v>107</v>
+      </c>
+      <c r="C23" s="6">
+        <v>2</v>
+      </c>
+      <c r="D23" s="46" t="str">
+        <f t="shared" si="2"/>
+        <v>MN2</v>
+      </c>
+      <c r="E23" s="47">
+        <v>8.5490331753554491E-4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="44">
+        <v>45900</v>
+      </c>
+      <c r="B24" s="42" t="s">
+        <v>107</v>
+      </c>
+      <c r="C24" s="6">
+        <v>3</v>
+      </c>
+      <c r="D24" s="46" t="str">
+        <f t="shared" si="2"/>
+        <v>MN3</v>
+      </c>
+      <c r="E24" s="47">
+        <v>8.5490331753554491E-4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="44">
+        <v>45900</v>
+      </c>
+      <c r="B25" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25" s="6">
+        <v>1</v>
+      </c>
+      <c r="D25" s="46" t="str">
+        <f t="shared" si="2"/>
+        <v>L1</v>
+      </c>
+      <c r="E25" s="47">
+        <v>5.9843232227488148E-3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="44">
+        <v>45900</v>
+      </c>
+      <c r="B26" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26" s="6">
+        <v>2</v>
+      </c>
+      <c r="D26" s="46" t="str">
+        <f t="shared" si="2"/>
+        <v>L2</v>
+      </c>
+      <c r="E26" s="47">
+        <v>3.4196132701421807E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="44">
+        <v>45900</v>
+      </c>
+      <c r="B27" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27" s="6">
+        <v>3</v>
+      </c>
+      <c r="D27" s="46" t="str">
+        <f t="shared" si="2"/>
+        <v>L3</v>
+      </c>
+      <c r="E27" s="47">
+        <v>8.5490331753554482E-3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="44">
+        <v>45900</v>
+      </c>
+      <c r="B28" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="C28" s="6">
+        <v>4</v>
+      </c>
+      <c r="D28" s="46" t="str">
+        <f t="shared" si="2"/>
+        <v>L4</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="44">
+        <v>45924</v>
+      </c>
+      <c r="B29" s="42" t="s">
+        <v>105</v>
+      </c>
+      <c r="C29" s="6">
+        <v>1</v>
+      </c>
+      <c r="D29" s="46" t="str">
+        <f>B29&amp;C29</f>
+        <v>MT1</v>
+      </c>
+      <c r="E29" s="47">
+        <v>8.9743582089552249E-4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="44">
+        <v>45924</v>
+      </c>
+      <c r="B30" s="42" t="s">
+        <v>105</v>
+      </c>
+      <c r="C30" s="6">
+        <v>2</v>
+      </c>
+      <c r="D30" s="46" t="str">
+        <f t="shared" ref="D30:D37" si="3">B30&amp;C30</f>
+        <v>MT2</v>
+      </c>
+      <c r="E30" s="47">
+        <v>8.9743582089552249E-4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="44">
+        <v>45924</v>
+      </c>
+      <c r="B31" s="42" t="s">
+        <v>107</v>
+      </c>
+      <c r="C31" s="6">
+        <v>1</v>
+      </c>
+      <c r="D31" s="46" t="str">
+        <f t="shared" si="3"/>
+        <v>MN1</v>
+      </c>
+      <c r="E31" s="47">
+        <v>8.9743582089552249E-4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="44">
+        <v>45924</v>
+      </c>
+      <c r="B32" s="42" t="s">
+        <v>107</v>
+      </c>
+      <c r="C32" s="6">
+        <v>2</v>
+      </c>
+      <c r="D32" s="46" t="str">
+        <f t="shared" si="3"/>
+        <v>MN2</v>
+      </c>
+      <c r="E32" s="47">
+        <v>8.9743582089552249E-4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="44">
+        <v>45924</v>
+      </c>
+      <c r="B33" s="42" t="s">
+        <v>107</v>
+      </c>
+      <c r="C33" s="6">
+        <v>3</v>
+      </c>
+      <c r="D33" s="46" t="str">
+        <f t="shared" si="3"/>
+        <v>MN3</v>
+      </c>
+      <c r="E33" s="47">
+        <v>8.9743582089552249E-4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="44">
+        <v>45924</v>
+      </c>
+      <c r="B34" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="6">
+        <v>1</v>
+      </c>
+      <c r="D34" s="46" t="str">
+        <f t="shared" si="3"/>
+        <v>L1</v>
+      </c>
+      <c r="E34" s="47">
+        <v>8.9743582089552249E-4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="44">
+        <v>45924</v>
+      </c>
+      <c r="B35" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="C35" s="6">
+        <v>2</v>
+      </c>
+      <c r="D35" s="46" t="str">
+        <f t="shared" si="3"/>
+        <v>L2</v>
+      </c>
+      <c r="E35" s="47">
+        <v>9.8717940298507466E-3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="44">
+        <v>45924</v>
+      </c>
+      <c r="B36" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="C36" s="6">
+        <v>3</v>
+      </c>
+      <c r="D36" s="46" t="str">
+        <f t="shared" si="3"/>
+        <v>L3</v>
+      </c>
+      <c r="E36" s="47">
+        <v>2.692307462686568E-3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="44">
+        <v>45924</v>
+      </c>
+      <c r="B37" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="C37" s="6">
+        <v>4</v>
+      </c>
+      <c r="D37" s="46" t="str">
+        <f t="shared" si="3"/>
+        <v>L4</v>
+      </c>
+      <c r="E37" s="47">
+        <v>8.9743582089552249E-4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C626FBD5-5D51-4CED-9AA1-67FFA0EF7910}">
+  <dimension ref="A1:E37"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="43" t="s">
+        <v>111</v>
+      </c>
+      <c r="B1" s="43" t="s">
+        <v>108</v>
+      </c>
+      <c r="C1" s="43" t="s">
+        <v>109</v>
+      </c>
+      <c r="D1" s="45" t="s">
+        <v>110</v>
+      </c>
+      <c r="E1" s="43" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="44">
+        <v>45834</v>
+      </c>
+      <c r="B2" s="42" t="s">
+        <v>105</v>
+      </c>
+      <c r="C2" s="6">
+        <v>1</v>
+      </c>
+      <c r="D2" s="46" t="str">
+        <f>B2&amp;C2</f>
+        <v>MT1</v>
+      </c>
+      <c r="E2" s="47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="44">
+        <v>45834</v>
+      </c>
+      <c r="B3" s="42" t="s">
+        <v>105</v>
+      </c>
+      <c r="C3" s="6">
+        <v>2</v>
+      </c>
+      <c r="D3" s="46" t="str">
+        <f t="shared" ref="D3:D10" si="0">B3&amp;C3</f>
+        <v>MT2</v>
+      </c>
+      <c r="E3" s="47">
+        <v>0.57762925263157894</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="44">
+        <v>45834</v>
+      </c>
+      <c r="B4" s="42" t="s">
+        <v>107</v>
+      </c>
+      <c r="C4" s="6">
+        <v>1</v>
+      </c>
+      <c r="D4" s="46" t="str">
+        <f t="shared" si="0"/>
+        <v>MN1</v>
+      </c>
+      <c r="E4" s="47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="44">
+        <v>45834</v>
+      </c>
+      <c r="B5" s="42" t="s">
+        <v>107</v>
+      </c>
+      <c r="C5" s="6">
+        <v>2</v>
+      </c>
+      <c r="D5" s="46" t="str">
+        <f t="shared" si="0"/>
+        <v>MN2</v>
+      </c>
+      <c r="E5" s="47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="44">
+        <v>45834</v>
+      </c>
+      <c r="B6" s="42" t="s">
+        <v>107</v>
+      </c>
+      <c r="C6" s="6">
+        <v>3</v>
+      </c>
+      <c r="D6" s="46" t="str">
+        <f t="shared" si="0"/>
+        <v>MN3</v>
+      </c>
+      <c r="E6" s="47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="44">
+        <v>45834</v>
+      </c>
+      <c r="B7" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="6">
+        <v>1</v>
+      </c>
+      <c r="D7" s="46" t="str">
+        <f t="shared" si="0"/>
+        <v>L1</v>
+      </c>
+      <c r="E7" s="47">
+        <v>1.0997799894736842</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="44">
+        <v>45834</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="6">
+        <v>2</v>
+      </c>
+      <c r="D8" s="46" t="str">
+        <f t="shared" si="0"/>
+        <v>L2</v>
+      </c>
+      <c r="E8" s="47">
+        <v>1.1324144105263159</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="44">
+        <v>45834</v>
+      </c>
+      <c r="B9" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="6">
+        <v>3</v>
+      </c>
+      <c r="D9" s="46" t="str">
+        <f t="shared" si="0"/>
+        <v>L3</v>
+      </c>
+      <c r="E9" s="47">
+        <v>0.80607019999999996</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="44">
+        <v>45834</v>
+      </c>
+      <c r="B10" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="6">
+        <v>4</v>
+      </c>
+      <c r="D10" s="46" t="str">
+        <f t="shared" si="0"/>
+        <v>L4</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="44">
+        <v>45861</v>
+      </c>
+      <c r="B11" s="42" t="s">
+        <v>105</v>
+      </c>
+      <c r="C11" s="6">
+        <v>1</v>
+      </c>
+      <c r="D11" s="46" t="str">
+        <f>B11&amp;C11</f>
+        <v>MT1</v>
+      </c>
+      <c r="E11" s="47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="44">
+        <v>45861</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>105</v>
+      </c>
+      <c r="C12" s="6">
+        <v>2</v>
+      </c>
+      <c r="D12" s="46" t="str">
+        <f t="shared" ref="D12:D19" si="1">B12&amp;C12</f>
+        <v>MT2</v>
+      </c>
+      <c r="E12" s="47">
+        <v>0.57762925263157894</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="44">
+        <v>45861</v>
+      </c>
+      <c r="B13" s="42" t="s">
+        <v>107</v>
+      </c>
+      <c r="C13" s="6">
+        <v>1</v>
+      </c>
+      <c r="D13" s="46" t="str">
+        <f t="shared" si="1"/>
+        <v>MN1</v>
+      </c>
+      <c r="E13" s="47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="44">
+        <v>45861</v>
+      </c>
+      <c r="B14" s="42" t="s">
+        <v>107</v>
+      </c>
+      <c r="C14" s="6">
+        <v>2</v>
+      </c>
+      <c r="D14" s="46" t="str">
+        <f t="shared" si="1"/>
+        <v>MN2</v>
+      </c>
+      <c r="E14" s="47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="44">
+        <v>45861</v>
+      </c>
+      <c r="B15" s="42" t="s">
+        <v>107</v>
+      </c>
+      <c r="C15" s="6">
+        <v>3</v>
+      </c>
+      <c r="D15" s="46" t="str">
+        <f t="shared" si="1"/>
+        <v>MN3</v>
+      </c>
+      <c r="E15" s="47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="44">
+        <v>45861</v>
+      </c>
+      <c r="B16" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="6">
+        <v>1</v>
+      </c>
+      <c r="D16" s="46" t="str">
+        <f t="shared" si="1"/>
+        <v>L1</v>
+      </c>
+      <c r="E16" s="47">
+        <v>1.0997799894736842</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="44">
+        <v>45861</v>
+      </c>
+      <c r="B17" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="6">
+        <v>2</v>
+      </c>
+      <c r="D17" s="46" t="str">
+        <f t="shared" si="1"/>
+        <v>L2</v>
+      </c>
+      <c r="E17" s="47">
+        <v>1.1324144105263159</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="44">
+        <v>45861</v>
+      </c>
+      <c r="B18" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="6">
+        <v>3</v>
+      </c>
+      <c r="D18" s="46" t="str">
+        <f t="shared" si="1"/>
+        <v>L3</v>
+      </c>
+      <c r="E18" s="47">
+        <v>0.80607019999999996</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="44">
+        <v>45861</v>
+      </c>
+      <c r="B19" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="6">
+        <v>4</v>
+      </c>
+      <c r="D19" s="46" t="str">
+        <f t="shared" si="1"/>
+        <v>L4</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="44">
+        <v>45900</v>
+      </c>
+      <c r="B20" s="42" t="s">
+        <v>105</v>
+      </c>
+      <c r="C20" s="6">
+        <v>1</v>
+      </c>
+      <c r="D20" s="46" t="str">
+        <f>B20&amp;C20</f>
+        <v>MT1</v>
+      </c>
+      <c r="E20" s="47">
+        <v>0.36876895789473685</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="44">
+        <v>45900</v>
+      </c>
+      <c r="B21" s="42" t="s">
+        <v>105</v>
+      </c>
+      <c r="C21" s="6">
+        <v>2</v>
+      </c>
+      <c r="D21" s="46" t="str">
+        <f t="shared" ref="D21:D28" si="2">B21&amp;C21</f>
+        <v>MT2</v>
+      </c>
+      <c r="E21" s="47">
+        <v>0.62984432631578957</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="44">
+        <v>45900</v>
+      </c>
+      <c r="B22" s="42" t="s">
+        <v>107</v>
+      </c>
+      <c r="C22" s="6">
+        <v>1</v>
+      </c>
+      <c r="D22" s="46" t="str">
+        <f t="shared" si="2"/>
+        <v>MN1</v>
+      </c>
+      <c r="E22" s="47">
+        <v>0.17296243157894739</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="44">
+        <v>45900</v>
+      </c>
+      <c r="B23" s="42" t="s">
+        <v>107</v>
+      </c>
+      <c r="C23" s="6">
+        <v>2</v>
+      </c>
+      <c r="D23" s="46" t="str">
+        <f t="shared" si="2"/>
+        <v>MN2</v>
+      </c>
+      <c r="E23" s="47">
+        <v>0.46667222105263162</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="44">
+        <v>45900</v>
+      </c>
+      <c r="B24" s="42" t="s">
+        <v>107</v>
+      </c>
+      <c r="C24" s="6">
+        <v>3</v>
+      </c>
+      <c r="D24" s="46" t="str">
+        <f t="shared" si="2"/>
+        <v>MN3</v>
+      </c>
+      <c r="E24" s="47">
+        <v>0.23823127368421054</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="44">
+        <v>45900</v>
+      </c>
+      <c r="B25" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25" s="6">
+        <v>1</v>
+      </c>
+      <c r="D25" s="46" t="str">
+        <f t="shared" si="2"/>
+        <v>L1</v>
+      </c>
+      <c r="E25" s="47">
+        <v>0.62984432631578957</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="44">
+        <v>45900</v>
+      </c>
+      <c r="B26" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26" s="6">
+        <v>2</v>
+      </c>
+      <c r="D26" s="46" t="str">
+        <f t="shared" si="2"/>
+        <v>L2</v>
+      </c>
+      <c r="E26" s="47">
+        <v>0.59720990526315787</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="44">
+        <v>45900</v>
+      </c>
+      <c r="B27" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27" s="6">
+        <v>3</v>
+      </c>
+      <c r="D27" s="46" t="str">
+        <f t="shared" si="2"/>
+        <v>L3</v>
+      </c>
+      <c r="E27" s="47">
+        <v>0.98882295789473695</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="44">
+        <v>45900</v>
+      </c>
+      <c r="B28" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="C28" s="6">
+        <v>4</v>
+      </c>
+      <c r="D28" s="46" t="str">
+        <f t="shared" si="2"/>
+        <v>L4</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="44">
+        <v>45924</v>
+      </c>
+      <c r="B29" s="42" t="s">
+        <v>105</v>
+      </c>
+      <c r="C29" s="6">
+        <v>1</v>
+      </c>
+      <c r="D29" s="46" t="str">
+        <f>B29&amp;C29</f>
+        <v>MT1</v>
+      </c>
+      <c r="E29" s="47">
+        <v>0.15990866315789476</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="44">
+        <v>45924</v>
+      </c>
+      <c r="B30" s="42" t="s">
+        <v>105</v>
+      </c>
+      <c r="C30" s="6">
+        <v>2</v>
+      </c>
+      <c r="D30" s="46" t="str">
+        <f t="shared" ref="D30:D37" si="3">B30&amp;C30</f>
+        <v>MT2</v>
+      </c>
+      <c r="E30" s="47">
+        <v>0.25781192631578942</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="44">
+        <v>45924</v>
+      </c>
+      <c r="B31" s="42" t="s">
+        <v>107</v>
+      </c>
+      <c r="C31" s="6">
+        <v>1</v>
+      </c>
+      <c r="D31" s="46" t="str">
+        <f t="shared" si="3"/>
+        <v>MN1</v>
+      </c>
+      <c r="E31" s="47">
+        <v>0.19254308421052632</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="44">
+        <v>45924</v>
+      </c>
+      <c r="B32" s="42" t="s">
+        <v>107</v>
+      </c>
+      <c r="C32" s="6">
+        <v>2</v>
+      </c>
+      <c r="D32" s="46" t="str">
+        <f t="shared" si="3"/>
+        <v>MN2</v>
+      </c>
+      <c r="E32" s="47">
+        <v>0.15990866315789476</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="44">
+        <v>45924</v>
+      </c>
+      <c r="B33" s="42" t="s">
+        <v>107</v>
+      </c>
+      <c r="C33" s="6">
+        <v>3</v>
+      </c>
+      <c r="D33" s="46" t="str">
+        <f t="shared" si="3"/>
+        <v>MN3</v>
+      </c>
+      <c r="E33" s="47">
+        <v>0.32308076842105266</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="44">
+        <v>45924</v>
+      </c>
+      <c r="B34" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="6">
+        <v>1</v>
+      </c>
+      <c r="D34" s="46" t="str">
+        <f t="shared" si="3"/>
+        <v>L1</v>
+      </c>
+      <c r="E34" s="47">
+        <v>0.81259708421052634</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="44">
+        <v>45924</v>
+      </c>
+      <c r="B35" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="C35" s="6">
+        <v>2</v>
+      </c>
+      <c r="D35" s="46" t="str">
+        <f t="shared" si="3"/>
+        <v>L2</v>
+      </c>
+      <c r="E35" s="47">
+        <v>1.138941294736842</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="44">
+        <v>45924</v>
+      </c>
+      <c r="B36" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="C36" s="6">
+        <v>3</v>
+      </c>
+      <c r="D36" s="46" t="str">
+        <f t="shared" si="3"/>
+        <v>L3</v>
+      </c>
+      <c r="E36" s="47">
+        <v>1.4326510842105264</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="44">
+        <v>45924</v>
+      </c>
+      <c r="B37" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="C37" s="6">
+        <v>4</v>
+      </c>
+      <c r="D37" s="46" t="str">
+        <f t="shared" si="3"/>
+        <v>L4</v>
+      </c>
+      <c r="E37" s="47">
+        <v>6.2005400000000002E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
 </file>